--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17159\Downloads\yuemei-main (1)\yuemei-main\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06132F5B-4100-4C6B-B92C-2518BB296E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9264" yWindow="684" windowWidth="15828" windowHeight="13596" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -38,6 +32,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3667" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="810">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2430,71 +2426,65 @@
   </si>
   <si>
     <t>姣兰 / 经典玻尿酸</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1ml / 支 / 盒</t>
   </si>
   <si>
-    <t>1ml / 支 / 盒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>姣兰 / Lips 唇部玻尿酸</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>乔雅登天使针</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>冰月岚 / 面部童颜针</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>350mg+10ml / 盒（粉末 + 液体双剂）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>冰月岚 / 黑金少女针</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>冰月岚 / 粉金少女针</t>
   </si>
   <si>
     <t>塑颜萃 Sculptra（欧版）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版含麻深蓝）</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>5ml×5 支 / 盒</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（身体）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>5ml×5 支 / 盒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>50ml+10ml / 盒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2506,6 +2496,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2534,15 +2531,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.5"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2550,27 +2541,160 @@
       <sz val="9.5"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9.5"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2589,8 +2713,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2624,9 +2934,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2639,58 +3191,102 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2975,20 +3571,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D456"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3002,93 +3598,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="9">
         <v>1850</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="9">
         <v>1850</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -3102,7 +3698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
@@ -3116,7 +3712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -3130,7 +3726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
@@ -3144,7 +3740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -3158,7 +3754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -3172,7 +3768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -3186,7 +3782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
@@ -3200,7 +3796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -3214,7 +3810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -3228,7 +3824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
@@ -3242,7 +3838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
@@ -3256,7 +3852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
@@ -3270,7 +3866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
@@ -3284,7 +3880,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
@@ -3298,7 +3894,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>38</v>
       </c>
@@ -3312,7 +3908,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
@@ -3326,7 +3922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>42</v>
       </c>
@@ -3340,7 +3936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
@@ -3354,7 +3950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -3368,7 +3964,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="2" t="s">
         <v>49</v>
       </c>
@@ -3382,7 +3978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="3" t="s">
         <v>51</v>
       </c>
@@ -3396,7 +3992,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
       <c r="A37" s="2" t="s">
         <v>53</v>
       </c>
@@ -3410,7 +4006,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
       <c r="A38" s="3" t="s">
         <v>55</v>
       </c>
@@ -3424,7 +4020,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
       <c r="A39" s="2" t="s">
         <v>58</v>
       </c>
@@ -3438,7 +4034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>60</v>
       </c>
@@ -3452,7 +4048,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
       <c r="A41" s="2" t="s">
         <v>62</v>
       </c>
@@ -3466,7 +4062,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>65</v>
       </c>
@@ -3480,7 +4076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
       <c r="A43" s="2" t="s">
         <v>66</v>
       </c>
@@ -3494,7 +4090,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>69</v>
       </c>
@@ -3508,7 +4104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
       <c r="A45" s="2" t="s">
         <v>71</v>
       </c>
@@ -3522,7 +4118,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>73</v>
       </c>
@@ -3536,7 +4132,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
       <c r="A47" s="2" t="s">
         <v>74</v>
       </c>
@@ -3550,7 +4146,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>76</v>
       </c>
@@ -3564,7 +4160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
       <c r="A49" s="2" t="s">
         <v>78</v>
       </c>
@@ -3578,7 +4174,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
       <c r="A50" s="3" t="s">
         <v>81</v>
       </c>
@@ -3592,7 +4188,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
       <c r="A51" s="2" t="s">
         <v>83</v>
       </c>
@@ -3606,7 +4202,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
       <c r="A52" s="3" t="s">
         <v>85</v>
       </c>
@@ -3620,7 +4216,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
       <c r="A53" s="2" t="s">
         <v>87</v>
       </c>
@@ -3634,7 +4230,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
       <c r="A54" s="3" t="s">
         <v>89</v>
       </c>
@@ -3648,7 +4244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
       <c r="A55" s="2" t="s">
         <v>90</v>
       </c>
@@ -3662,7 +4258,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
       <c r="A56" s="3" t="s">
         <v>91</v>
       </c>
@@ -3676,7 +4272,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
       <c r="A57" s="2" t="s">
         <v>93</v>
       </c>
@@ -3690,7 +4286,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
       <c r="A58" s="3" t="s">
         <v>94</v>
       </c>
@@ -3704,7 +4300,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
       <c r="A59" s="2" t="s">
         <v>97</v>
       </c>
@@ -3718,7 +4314,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
       <c r="A60" s="3" t="s">
         <v>98</v>
       </c>
@@ -3732,7 +4328,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
       <c r="A61" s="2" t="s">
         <v>100</v>
       </c>
@@ -3746,7 +4342,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
       <c r="A62" s="3" t="s">
         <v>102</v>
       </c>
@@ -3760,7 +4356,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
       <c r="A63" s="2" t="s">
         <v>103</v>
       </c>
@@ -3774,7 +4370,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
       <c r="A64" s="3" t="s">
         <v>105</v>
       </c>
@@ -3788,7 +4384,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="22.05" customHeight="1" spans="1:4">
       <c r="A65" s="2" t="s">
         <v>106</v>
       </c>
@@ -3802,7 +4398,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="22.05" customHeight="1" spans="1:4">
       <c r="A66" s="3" t="s">
         <v>107</v>
       </c>
@@ -3816,7 +4412,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="22.05" customHeight="1" spans="1:4">
       <c r="A67" s="2" t="s">
         <v>109</v>
       </c>
@@ -3830,7 +4426,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="22.05" customHeight="1" spans="1:4">
       <c r="A68" s="3" t="s">
         <v>111</v>
       </c>
@@ -3844,7 +4440,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="22.05" customHeight="1" spans="1:4">
       <c r="A69" s="2" t="s">
         <v>111</v>
       </c>
@@ -3858,7 +4454,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="22.05" customHeight="1" spans="1:4">
       <c r="A70" s="3" t="s">
         <v>115</v>
       </c>
@@ -3872,7 +4468,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="22.05" customHeight="1" spans="1:4">
       <c r="A71" s="2" t="s">
         <v>117</v>
       </c>
@@ -3886,7 +4482,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="22.05" customHeight="1" spans="1:4">
       <c r="A72" s="3" t="s">
         <v>118</v>
       </c>
@@ -3900,7 +4496,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="22.05" customHeight="1" spans="1:4">
       <c r="A73" s="2" t="s">
         <v>119</v>
       </c>
@@ -3914,7 +4510,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="22.05" customHeight="1" spans="1:4">
       <c r="A74" s="3" t="s">
         <v>120</v>
       </c>
@@ -3928,7 +4524,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="22.05" customHeight="1" spans="1:4">
       <c r="A75" s="2" t="s">
         <v>121</v>
       </c>
@@ -3942,7 +4538,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="22.05" customHeight="1" spans="1:4">
       <c r="A76" s="3" t="s">
         <v>122</v>
       </c>
@@ -3956,7 +4552,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="22.05" customHeight="1" spans="1:4">
       <c r="A77" s="2" t="s">
         <v>125</v>
       </c>
@@ -3970,7 +4566,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="22.05" customHeight="1" spans="1:4">
       <c r="A78" s="3" t="s">
         <v>127</v>
       </c>
@@ -3984,7 +4580,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="22.05" customHeight="1" spans="1:4">
       <c r="A79" s="2" t="s">
         <v>127</v>
       </c>
@@ -3998,7 +4594,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="22.05" customHeight="1" spans="1:4">
       <c r="A80" s="3" t="s">
         <v>129</v>
       </c>
@@ -4012,7 +4608,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="22.05" customHeight="1" spans="1:4">
       <c r="A81" s="2" t="s">
         <v>130</v>
       </c>
@@ -4026,7 +4622,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="22.05" customHeight="1" spans="1:4">
       <c r="A82" s="3" t="s">
         <v>131</v>
       </c>
@@ -4040,7 +4636,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="22.05" customHeight="1" spans="1:4">
       <c r="A83" s="2" t="s">
         <v>133</v>
       </c>
@@ -4054,7 +4650,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="22.05" customHeight="1" spans="1:4">
       <c r="A84" s="3" t="s">
         <v>134</v>
       </c>
@@ -4068,7 +4664,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="22.05" customHeight="1" spans="1:4">
       <c r="A85" s="2" t="s">
         <v>136</v>
       </c>
@@ -4082,7 +4678,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="22.05" customHeight="1" spans="1:4">
       <c r="A86" s="3" t="s">
         <v>138</v>
       </c>
@@ -4096,7 +4692,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="22.05" customHeight="1" spans="1:4">
       <c r="A87" s="2" t="s">
         <v>140</v>
       </c>
@@ -4110,7 +4706,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="22.05" customHeight="1" spans="1:4">
       <c r="A88" s="3" t="s">
         <v>142</v>
       </c>
@@ -4124,7 +4720,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="22.05" customHeight="1" spans="1:4">
       <c r="A89" s="2" t="s">
         <v>144</v>
       </c>
@@ -4138,7 +4734,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="22.05" customHeight="1" spans="1:4">
       <c r="A90" s="3" t="s">
         <v>146</v>
       </c>
@@ -4152,7 +4748,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="22.05" customHeight="1" spans="1:4">
       <c r="A91" s="2" t="s">
         <v>148</v>
       </c>
@@ -4166,7 +4762,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="22.05" customHeight="1" spans="1:4">
       <c r="A92" s="3" t="s">
         <v>149</v>
       </c>
@@ -4180,7 +4776,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="22.05" customHeight="1" spans="1:4">
       <c r="A93" s="2" t="s">
         <v>152</v>
       </c>
@@ -4194,7 +4790,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="22.05" customHeight="1" spans="1:4">
       <c r="A94" s="3" t="s">
         <v>154</v>
       </c>
@@ -4208,7 +4804,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="22.05" customHeight="1" spans="1:4">
       <c r="A95" s="2" t="s">
         <v>155</v>
       </c>
@@ -4222,7 +4818,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="22.05" customHeight="1" spans="1:4">
       <c r="A96" s="3" t="s">
         <v>157</v>
       </c>
@@ -4236,7 +4832,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="22.05" customHeight="1" spans="1:4">
       <c r="A97" s="2" t="s">
         <v>160</v>
       </c>
@@ -4250,7 +4846,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="22.05" customHeight="1" spans="1:4">
       <c r="A98" s="3" t="s">
         <v>161</v>
       </c>
@@ -4264,7 +4860,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="22.05" customHeight="1" spans="1:4">
       <c r="A99" s="2" t="s">
         <v>162</v>
       </c>
@@ -4278,7 +4874,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="22.05" customHeight="1" spans="1:4">
       <c r="A100" s="3" t="s">
         <v>164</v>
       </c>
@@ -4292,7 +4888,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="22.05" customHeight="1" spans="1:4">
       <c r="A101" s="2" t="s">
         <v>165</v>
       </c>
@@ -4306,7 +4902,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="22.05" customHeight="1" spans="1:4">
       <c r="A102" s="3" t="s">
         <v>166</v>
       </c>
@@ -4320,7 +4916,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="2" t="s">
         <v>167</v>
       </c>
@@ -4334,7 +4930,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="22.05" customHeight="1" spans="1:4">
       <c r="A104" s="3" t="s">
         <v>168</v>
       </c>
@@ -4348,7 +4944,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="22.05" customHeight="1" spans="1:4">
       <c r="A105" s="2" t="s">
         <v>169</v>
       </c>
@@ -4362,7 +4958,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="22.05" customHeight="1" spans="1:4">
       <c r="A106" s="3" t="s">
         <v>170</v>
       </c>
@@ -4376,7 +4972,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="22.05" customHeight="1" spans="1:4">
       <c r="A107" s="2" t="s">
         <v>172</v>
       </c>
@@ -4390,7 +4986,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="22.05" customHeight="1" spans="1:4">
       <c r="A108" s="3" t="s">
         <v>174</v>
       </c>
@@ -4404,7 +5000,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="22.05" customHeight="1" spans="1:4">
       <c r="A109" s="2" t="s">
         <v>177</v>
       </c>
@@ -4418,7 +5014,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="22.05" customHeight="1" spans="1:4">
       <c r="A110" s="3" t="s">
         <v>179</v>
       </c>
@@ -4432,7 +5028,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="22.05" customHeight="1" spans="1:4">
       <c r="A111" s="2" t="s">
         <v>182</v>
       </c>
@@ -4446,7 +5042,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="22.05" customHeight="1" spans="1:4">
       <c r="A112" s="3" t="s">
         <v>185</v>
       </c>
@@ -4460,7 +5056,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="22.05" customHeight="1" spans="1:4">
       <c r="A113" s="2" t="s">
         <v>187</v>
       </c>
@@ -4474,7 +5070,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="22.05" customHeight="1" spans="1:4">
       <c r="A114" s="3" t="s">
         <v>189</v>
       </c>
@@ -4484,11 +5080,11 @@
       <c r="C114" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="D114" s="17" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="22.05" customHeight="1" spans="1:4">
       <c r="A115" s="2" t="s">
         <v>192</v>
       </c>
@@ -4502,7 +5098,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="22.05" customHeight="1" spans="1:4">
       <c r="A116" s="3" t="s">
         <v>193</v>
       </c>
@@ -4516,7 +5112,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="22.05" customHeight="1" spans="1:4">
       <c r="A117" s="2" t="s">
         <v>196</v>
       </c>
@@ -4530,7 +5126,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="22.05" customHeight="1" spans="1:4">
       <c r="A118" s="3" t="s">
         <v>199</v>
       </c>
@@ -4544,7 +5140,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="22.05" customHeight="1" spans="1:4">
       <c r="A119" s="2" t="s">
         <v>202</v>
       </c>
@@ -4558,7 +5154,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="22.05" customHeight="1" spans="1:4">
       <c r="A120" s="3" t="s">
         <v>205</v>
       </c>
@@ -4572,7 +5168,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="22.05" customHeight="1" spans="1:4">
       <c r="A121" s="2" t="s">
         <v>207</v>
       </c>
@@ -4586,7 +5182,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="22.05" customHeight="1" spans="1:4">
       <c r="A122" s="3" t="s">
         <v>209</v>
       </c>
@@ -4600,7 +5196,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="22.05" customHeight="1" spans="1:4">
       <c r="A123" s="2" t="s">
         <v>211</v>
       </c>
@@ -4614,7 +5210,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="22.05" customHeight="1" spans="1:4">
       <c r="A124" s="3" t="s">
         <v>213</v>
       </c>
@@ -4628,7 +5224,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="22.05" customHeight="1" spans="1:4">
       <c r="A125" s="2" t="s">
         <v>216</v>
       </c>
@@ -4642,7 +5238,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="22.05" customHeight="1" spans="1:4">
       <c r="A126" s="3" t="s">
         <v>218</v>
       </c>
@@ -4656,7 +5252,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="22.05" customHeight="1" spans="1:4">
       <c r="A127" s="2" t="s">
         <v>220</v>
       </c>
@@ -4670,7 +5266,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="22.05" customHeight="1" spans="1:4">
       <c r="A128" s="3" t="s">
         <v>223</v>
       </c>
@@ -4684,7 +5280,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="22.05" customHeight="1" spans="1:4">
       <c r="A129" s="2" t="s">
         <v>226</v>
       </c>
@@ -4698,7 +5294,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="22.05" customHeight="1" spans="1:4">
       <c r="A130" s="3" t="s">
         <v>229</v>
       </c>
@@ -4712,7 +5308,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="22.05" customHeight="1" spans="1:4">
       <c r="A131" s="2" t="s">
         <v>232</v>
       </c>
@@ -4726,7 +5322,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="22.05" customHeight="1" spans="1:4">
       <c r="A132" s="3" t="s">
         <v>233</v>
       </c>
@@ -4740,7 +5336,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="22.05" customHeight="1" spans="1:4">
       <c r="A133" s="2" t="s">
         <v>233</v>
       </c>
@@ -4754,7 +5350,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="22.05" customHeight="1" spans="1:4">
       <c r="A134" s="3" t="s">
         <v>233</v>
       </c>
@@ -4768,7 +5364,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="22.05" customHeight="1" spans="1:4">
       <c r="A135" s="2" t="s">
         <v>239</v>
       </c>
@@ -4782,7 +5378,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="22.05" customHeight="1" spans="1:4">
       <c r="A136" s="3" t="s">
         <v>241</v>
       </c>
@@ -4796,7 +5392,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="22.05" customHeight="1" spans="1:4">
       <c r="A137" s="2" t="s">
         <v>244</v>
       </c>
@@ -4810,7 +5406,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="22.05" customHeight="1" spans="1:4">
       <c r="A138" s="3" t="s">
         <v>247</v>
       </c>
@@ -4824,7 +5420,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="22.05" customHeight="1" spans="1:4">
       <c r="A139" s="2" t="s">
         <v>249</v>
       </c>
@@ -4838,7 +5434,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="22.05" customHeight="1" spans="1:4">
       <c r="A140" s="3" t="s">
         <v>251</v>
       </c>
@@ -4852,7 +5448,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="22.05" customHeight="1" spans="1:4">
       <c r="A141" s="2" t="s">
         <v>254</v>
       </c>
@@ -4866,7 +5462,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="22.05" customHeight="1" spans="1:4">
       <c r="A142" s="3" t="s">
         <v>257</v>
       </c>
@@ -4880,7 +5476,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="22.05" customHeight="1" spans="1:4">
       <c r="A143" s="2" t="s">
         <v>259</v>
       </c>
@@ -4894,7 +5490,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="22.05" customHeight="1" spans="1:4">
       <c r="A144" s="3" t="s">
         <v>262</v>
       </c>
@@ -4908,7 +5504,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="22.05" customHeight="1" spans="1:4">
       <c r="A145" s="2" t="s">
         <v>265</v>
       </c>
@@ -4922,7 +5518,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="22.05" customHeight="1" spans="1:4">
       <c r="A146" s="3" t="s">
         <v>268</v>
       </c>
@@ -4936,7 +5532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="22.05" customHeight="1" spans="1:4">
       <c r="A147" s="2" t="s">
         <v>269</v>
       </c>
@@ -4950,7 +5546,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="22.05" customHeight="1" spans="1:4">
       <c r="A148" s="3" t="s">
         <v>271</v>
       </c>
@@ -4964,7 +5560,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="22.05" customHeight="1" spans="1:4">
       <c r="A149" s="2" t="s">
         <v>271</v>
       </c>
@@ -4978,7 +5574,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="22.05" customHeight="1" spans="1:4">
       <c r="A150" s="3" t="s">
         <v>276</v>
       </c>
@@ -4992,7 +5588,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="22.05" customHeight="1" spans="1:4">
       <c r="A151" s="2" t="s">
         <v>276</v>
       </c>
@@ -5006,7 +5602,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="22.05" customHeight="1" spans="1:4">
       <c r="A152" s="3" t="s">
         <v>278</v>
       </c>
@@ -5020,7 +5616,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="22.05" customHeight="1" spans="1:4">
       <c r="A153" s="2" t="s">
         <v>278</v>
       </c>
@@ -5034,7 +5630,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="22.05" customHeight="1" spans="1:4">
       <c r="A154" s="3" t="s">
         <v>281</v>
       </c>
@@ -5048,7 +5644,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="22.05" customHeight="1" spans="1:4">
       <c r="A155" s="2" t="s">
         <v>284</v>
       </c>
@@ -5062,7 +5658,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="22.05" customHeight="1" spans="1:4">
       <c r="A156" s="3" t="s">
         <v>285</v>
       </c>
@@ -5076,7 +5672,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="22.05" customHeight="1" spans="1:4">
       <c r="A157" s="2" t="s">
         <v>288</v>
       </c>
@@ -5090,7 +5686,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="22.05" customHeight="1" spans="1:4">
       <c r="A158" s="3" t="s">
         <v>291</v>
       </c>
@@ -5104,7 +5700,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="22.05" customHeight="1" spans="1:4">
       <c r="A159" s="2" t="s">
         <v>294</v>
       </c>
@@ -5118,7 +5714,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="22.05" customHeight="1" spans="1:4">
       <c r="A160" s="3" t="s">
         <v>296</v>
       </c>
@@ -5132,7 +5728,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="22.05" customHeight="1" spans="1:4">
       <c r="A161" s="2" t="s">
         <v>298</v>
       </c>
@@ -5146,7 +5742,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="22.05" customHeight="1" spans="1:4">
       <c r="A162" s="3" t="s">
         <v>301</v>
       </c>
@@ -5160,7 +5756,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="22.05" customHeight="1" spans="1:4">
       <c r="A163" s="2" t="s">
         <v>303</v>
       </c>
@@ -5174,7 +5770,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="22.05" customHeight="1" spans="1:4">
       <c r="A164" s="3" t="s">
         <v>305</v>
       </c>
@@ -5188,7 +5784,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="22.05" customHeight="1" spans="1:4">
       <c r="A165" s="2" t="s">
         <v>306</v>
       </c>
@@ -5202,7 +5798,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="22.05" customHeight="1" spans="1:4">
       <c r="A166" s="3" t="s">
         <v>307</v>
       </c>
@@ -5216,7 +5812,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="22.05" customHeight="1" spans="1:4">
       <c r="A167" s="2" t="s">
         <v>308</v>
       </c>
@@ -5230,7 +5826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="22.05" customHeight="1" spans="1:4">
       <c r="A168" s="3" t="s">
         <v>310</v>
       </c>
@@ -5244,7 +5840,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="22.05" customHeight="1" spans="1:4">
       <c r="A169" s="2" t="s">
         <v>313</v>
       </c>
@@ -5258,7 +5854,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="22.05" customHeight="1" spans="1:4">
       <c r="A170" s="3" t="s">
         <v>316</v>
       </c>
@@ -5272,7 +5868,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="22.05" customHeight="1" spans="1:4">
       <c r="A171" s="2" t="s">
         <v>317</v>
       </c>
@@ -5286,7 +5882,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="22.05" customHeight="1" spans="1:4">
       <c r="A172" s="3" t="s">
         <v>319</v>
       </c>
@@ -5300,7 +5896,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="22.05" customHeight="1" spans="1:4">
       <c r="A173" s="2" t="s">
         <v>320</v>
       </c>
@@ -5314,7 +5910,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="22.05" customHeight="1" spans="1:4">
       <c r="A174" s="3" t="s">
         <v>321</v>
       </c>
@@ -5328,7 +5924,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="22.05" customHeight="1" spans="1:4">
       <c r="A175" s="2" t="s">
         <v>323</v>
       </c>
@@ -5342,7 +5938,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="22.05" customHeight="1" spans="1:4">
       <c r="A176" s="3" t="s">
         <v>324</v>
       </c>
@@ -5356,7 +5952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="22.05" customHeight="1" spans="1:4">
       <c r="A177" s="2" t="s">
         <v>325</v>
       </c>
@@ -5370,7 +5966,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="22.05" customHeight="1" spans="1:4">
       <c r="A178" s="3" t="s">
         <v>327</v>
       </c>
@@ -5384,7 +5980,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="22.05" customHeight="1" spans="1:4">
       <c r="A179" s="2" t="s">
         <v>330</v>
       </c>
@@ -5398,7 +5994,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="22.05" customHeight="1" spans="1:4">
       <c r="A180" s="3" t="s">
         <v>332</v>
       </c>
@@ -5412,7 +6008,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="22.05" customHeight="1" spans="1:4">
       <c r="A181" s="2" t="s">
         <v>334</v>
       </c>
@@ -5426,7 +6022,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="22.05" customHeight="1" spans="1:4">
       <c r="A182" s="3" t="s">
         <v>337</v>
       </c>
@@ -5440,7 +6036,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="22.05" customHeight="1" spans="1:4">
       <c r="A183" s="2" t="s">
         <v>337</v>
       </c>
@@ -5454,7 +6050,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="22.05" customHeight="1" spans="1:4">
       <c r="A184" s="3" t="s">
         <v>340</v>
       </c>
@@ -5468,7 +6064,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="22.05" customHeight="1" spans="1:4">
       <c r="A185" s="2" t="s">
         <v>341</v>
       </c>
@@ -5482,7 +6078,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="22.05" customHeight="1" spans="1:4">
       <c r="A186" s="3" t="s">
         <v>344</v>
       </c>
@@ -5496,7 +6092,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="22.05" customHeight="1" spans="1:4">
       <c r="A187" s="2" t="s">
         <v>345</v>
       </c>
@@ -5510,7 +6106,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="22.05" customHeight="1" spans="1:4">
       <c r="A188" s="3" t="s">
         <v>346</v>
       </c>
@@ -5524,7 +6120,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="22.05" customHeight="1" spans="1:4">
       <c r="A189" s="2" t="s">
         <v>347</v>
       </c>
@@ -5538,7 +6134,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="22.05" customHeight="1" spans="1:4">
       <c r="A190" s="3" t="s">
         <v>350</v>
       </c>
@@ -5552,7 +6148,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="22.05" customHeight="1" spans="1:4">
       <c r="A191" s="2" t="s">
         <v>351</v>
       </c>
@@ -5566,7 +6162,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="22.05" customHeight="1" spans="1:4">
       <c r="A192" s="3" t="s">
         <v>352</v>
       </c>
@@ -5580,7 +6176,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="22.05" customHeight="1" spans="1:4">
       <c r="A193" s="2" t="s">
         <v>353</v>
       </c>
@@ -5594,7 +6190,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="22.05" customHeight="1" spans="1:4">
       <c r="A194" s="3" t="s">
         <v>355</v>
       </c>
@@ -5608,7 +6204,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="22.05" customHeight="1" spans="1:4">
       <c r="A195" s="2" t="s">
         <v>357</v>
       </c>
@@ -5622,7 +6218,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="22.05" customHeight="1" spans="1:4">
       <c r="A196" s="3" t="s">
         <v>360</v>
       </c>
@@ -5636,7 +6232,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="22.05" customHeight="1" spans="1:4">
       <c r="A197" s="2" t="s">
         <v>362</v>
       </c>
@@ -5650,7 +6246,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="22.05" customHeight="1" spans="1:4">
       <c r="A198" s="3" t="s">
         <v>363</v>
       </c>
@@ -5664,7 +6260,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="22.05" customHeight="1" spans="1:4">
       <c r="A199" s="2" t="s">
         <v>364</v>
       </c>
@@ -5678,7 +6274,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="22.05" customHeight="1" spans="1:4">
       <c r="A200" s="3" t="s">
         <v>366</v>
       </c>
@@ -5692,7 +6288,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="22.05" customHeight="1" spans="1:4">
       <c r="A201" s="2" t="s">
         <v>368</v>
       </c>
@@ -5706,7 +6302,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="22.05" customHeight="1" spans="1:4">
       <c r="A202" s="3" t="s">
         <v>370</v>
       </c>
@@ -5720,7 +6316,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="22.05" customHeight="1" spans="1:4">
       <c r="A203" s="2" t="s">
         <v>373</v>
       </c>
@@ -5734,7 +6330,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="22.05" customHeight="1" spans="1:4">
       <c r="A204" s="3" t="s">
         <v>375</v>
       </c>
@@ -5748,7 +6344,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="22.05" customHeight="1" spans="1:4">
       <c r="A205" s="2" t="s">
         <v>378</v>
       </c>
@@ -5762,7 +6358,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="22.05" customHeight="1" spans="1:4">
       <c r="A206" s="3" t="s">
         <v>380</v>
       </c>
@@ -5776,7 +6372,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="22.05" customHeight="1" spans="1:4">
       <c r="A207" s="2" t="s">
         <v>383</v>
       </c>
@@ -5790,7 +6386,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="22.05" customHeight="1" spans="1:4">
       <c r="A208" s="3" t="s">
         <v>386</v>
       </c>
@@ -5804,7 +6400,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="22.05" customHeight="1" spans="1:4">
       <c r="A209" s="2" t="s">
         <v>387</v>
       </c>
@@ -5818,7 +6414,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="22.05" customHeight="1" spans="1:4">
       <c r="A210" s="3" t="s">
         <v>389</v>
       </c>
@@ -5832,7 +6428,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="22.05" customHeight="1" spans="1:4">
       <c r="A211" s="2" t="s">
         <v>391</v>
       </c>
@@ -5846,7 +6442,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="22.05" customHeight="1" spans="1:4">
       <c r="A212" s="3" t="s">
         <v>393</v>
       </c>
@@ -5860,7 +6456,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="22.05" customHeight="1" spans="1:4">
       <c r="A213" s="2" t="s">
         <v>394</v>
       </c>
@@ -5874,7 +6470,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="22.05" customHeight="1" spans="1:4">
       <c r="A214" s="3" t="s">
         <v>396</v>
       </c>
@@ -5888,7 +6484,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="22.05" customHeight="1" spans="1:4">
       <c r="A215" s="2" t="s">
         <v>168</v>
       </c>
@@ -5902,7 +6498,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="22.05" customHeight="1" spans="1:4">
       <c r="A216" s="3" t="s">
         <v>398</v>
       </c>
@@ -5916,7 +6512,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="22.05" customHeight="1" spans="1:4">
       <c r="A217" s="2" t="s">
         <v>399</v>
       </c>
@@ -5930,7 +6526,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="22.05" customHeight="1" spans="1:4">
       <c r="A218" s="3" t="s">
         <v>401</v>
       </c>
@@ -5944,7 +6540,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="22.05" customHeight="1" spans="1:4">
       <c r="A219" s="2" t="s">
         <v>402</v>
       </c>
@@ -5958,7 +6554,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="22.05" customHeight="1" spans="1:4">
       <c r="A220" s="3" t="s">
         <v>403</v>
       </c>
@@ -5972,7 +6568,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="22.05" customHeight="1" spans="1:4">
       <c r="A221" s="2" t="s">
         <v>405</v>
       </c>
@@ -5986,7 +6582,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="22.05" customHeight="1" spans="1:4">
       <c r="A222" s="3" t="s">
         <v>406</v>
       </c>
@@ -6000,7 +6596,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="22.05" customHeight="1" spans="1:4">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
@@ -6014,7 +6610,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="22.05" customHeight="1" spans="1:4">
       <c r="A224" s="3" t="s">
         <v>408</v>
       </c>
@@ -6028,7 +6624,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="22.05" customHeight="1" spans="1:4">
       <c r="A225" s="2" t="s">
         <v>409</v>
       </c>
@@ -6042,7 +6638,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="22.05" customHeight="1" spans="1:4">
       <c r="A226" s="3" t="s">
         <v>410</v>
       </c>
@@ -6056,7 +6652,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="22.05" customHeight="1" spans="1:4">
       <c r="A227" s="2" t="s">
         <v>411</v>
       </c>
@@ -6070,7 +6666,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="22.05" customHeight="1" spans="1:4">
       <c r="A228" s="3" t="s">
         <v>413</v>
       </c>
@@ -6084,7 +6680,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="22.05" customHeight="1" spans="1:4">
       <c r="A229" s="2" t="s">
         <v>416</v>
       </c>
@@ -6098,7 +6694,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="22.05" customHeight="1" spans="1:4">
       <c r="A230" s="3" t="s">
         <v>417</v>
       </c>
@@ -6112,7 +6708,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="22.05" customHeight="1" spans="1:4">
       <c r="A231" s="2" t="s">
         <v>418</v>
       </c>
@@ -6126,7 +6722,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="22.05" customHeight="1" spans="1:4">
       <c r="A232" s="3" t="s">
         <v>419</v>
       </c>
@@ -6140,7 +6736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="22.05" customHeight="1" spans="1:4">
       <c r="A233" s="2" t="s">
         <v>421</v>
       </c>
@@ -6154,7 +6750,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="22.05" customHeight="1" spans="1:4">
       <c r="A234" s="3" t="s">
         <v>424</v>
       </c>
@@ -6168,7 +6764,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="22.05" customHeight="1" spans="1:4">
       <c r="A235" s="2" t="s">
         <v>425</v>
       </c>
@@ -6182,7 +6778,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="22.05" customHeight="1" spans="1:4">
       <c r="A236" s="3" t="s">
         <v>427</v>
       </c>
@@ -6196,7 +6792,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="22.05" customHeight="1" spans="1:4">
       <c r="A237" s="2" t="s">
         <v>428</v>
       </c>
@@ -6210,7 +6806,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="22.05" customHeight="1" spans="1:4">
       <c r="A238" s="3" t="s">
         <v>431</v>
       </c>
@@ -6224,7 +6820,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="22.05" customHeight="1" spans="1:4">
       <c r="A239" s="2" t="s">
         <v>432</v>
       </c>
@@ -6238,7 +6834,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="22.05" customHeight="1" spans="1:4">
       <c r="A240" s="3" t="s">
         <v>434</v>
       </c>
@@ -6252,7 +6848,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="22.05" customHeight="1" spans="1:4">
       <c r="A241" s="2" t="s">
         <v>436</v>
       </c>
@@ -6266,7 +6862,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="22.05" customHeight="1" spans="1:4">
       <c r="A242" s="3" t="s">
         <v>439</v>
       </c>
@@ -6280,7 +6876,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="22.05" customHeight="1" spans="1:4">
       <c r="A243" s="2" t="s">
         <v>441</v>
       </c>
@@ -6294,7 +6890,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="22.05" customHeight="1" spans="1:4">
       <c r="A244" s="3" t="s">
         <v>444</v>
       </c>
@@ -6308,7 +6904,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="22.05" customHeight="1" spans="1:4">
       <c r="A245" s="2" t="s">
         <v>446</v>
       </c>
@@ -6322,7 +6918,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="22.05" customHeight="1" spans="1:4">
       <c r="A246" s="3" t="s">
         <v>447</v>
       </c>
@@ -6336,7 +6932,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="22.05" customHeight="1" spans="1:4">
       <c r="A247" s="2" t="s">
         <v>448</v>
       </c>
@@ -6350,7 +6946,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="22.05" customHeight="1" spans="1:4">
       <c r="A248" s="3" t="s">
         <v>449</v>
       </c>
@@ -6364,7 +6960,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="22.05" customHeight="1" spans="1:4">
       <c r="A249" s="2" t="s">
         <v>450</v>
       </c>
@@ -6378,7 +6974,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="22.05" customHeight="1" spans="1:4">
       <c r="A250" s="3" t="s">
         <v>452</v>
       </c>
@@ -6392,7 +6988,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="22.05" customHeight="1" spans="1:4">
       <c r="A251" s="2" t="s">
         <v>453</v>
       </c>
@@ -6406,7 +7002,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="22.05" customHeight="1" spans="1:4">
       <c r="A252" s="3" t="s">
         <v>455</v>
       </c>
@@ -6420,7 +7016,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="22.05" customHeight="1" spans="1:4">
       <c r="A253" s="2" t="s">
         <v>456</v>
       </c>
@@ -6434,7 +7030,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="22.05" customHeight="1" spans="1:4">
       <c r="A254" s="3" t="s">
         <v>458</v>
       </c>
@@ -6448,7 +7044,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="22.05" customHeight="1" spans="1:4">
       <c r="A255" s="2" t="s">
         <v>460</v>
       </c>
@@ -6462,7 +7058,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="22.05" customHeight="1" spans="1:4">
       <c r="A256" s="3" t="s">
         <v>462</v>
       </c>
@@ -6476,7 +7072,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="22.05" customHeight="1" spans="1:4">
       <c r="A257" s="2" t="s">
         <v>465</v>
       </c>
@@ -6490,7 +7086,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="22.05" customHeight="1" spans="1:4">
       <c r="A258" s="3" t="s">
         <v>467</v>
       </c>
@@ -6504,7 +7100,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="22.05" customHeight="1" spans="1:4">
       <c r="A259" s="2" t="s">
         <v>470</v>
       </c>
@@ -6518,7 +7114,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="22.05" customHeight="1" spans="1:4">
       <c r="A260" s="3" t="s">
         <v>472</v>
       </c>
@@ -6532,7 +7128,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="22.05" customHeight="1" spans="1:4">
       <c r="A261" s="2" t="s">
         <v>475</v>
       </c>
@@ -6546,7 +7142,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="22.05" customHeight="1" spans="1:4">
       <c r="A262" s="3" t="s">
         <v>477</v>
       </c>
@@ -6560,7 +7156,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="22.05" customHeight="1" spans="1:4">
       <c r="A263" s="2" t="s">
         <v>479</v>
       </c>
@@ -6574,7 +7170,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="22.05" customHeight="1" spans="1:4">
       <c r="A264" s="3" t="s">
         <v>480</v>
       </c>
@@ -6588,7 +7184,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="22.05" customHeight="1" spans="1:4">
       <c r="A265" s="2" t="s">
         <v>481</v>
       </c>
@@ -6602,7 +7198,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="22.05" customHeight="1" spans="1:4">
       <c r="A266" s="3" t="s">
         <v>482</v>
       </c>
@@ -6616,7 +7212,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="22.05" customHeight="1" spans="1:4">
       <c r="A267" s="2" t="s">
         <v>483</v>
       </c>
@@ -6630,7 +7226,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="22.05" customHeight="1" spans="1:4">
       <c r="A268" s="3" t="s">
         <v>484</v>
       </c>
@@ -6644,7 +7240,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="22.05" customHeight="1" spans="1:4">
       <c r="A269" s="2" t="s">
         <v>485</v>
       </c>
@@ -6658,7 +7254,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" ht="22.05" customHeight="1" spans="1:4">
       <c r="A270" s="3" t="s">
         <v>487</v>
       </c>
@@ -6672,7 +7268,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" ht="22.05" customHeight="1" spans="1:4">
       <c r="A271" s="2" t="s">
         <v>488</v>
       </c>
@@ -6686,7 +7282,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" ht="22.05" customHeight="1" spans="1:4">
       <c r="A272" s="3" t="s">
         <v>489</v>
       </c>
@@ -6700,7 +7296,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" ht="22.05" customHeight="1" spans="1:4">
       <c r="A273" s="2" t="s">
         <v>491</v>
       </c>
@@ -6714,7 +7310,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" ht="22.05" customHeight="1" spans="1:4">
       <c r="A274" s="3" t="s">
         <v>492</v>
       </c>
@@ -6728,7 +7324,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" ht="22.05" customHeight="1" spans="1:4">
       <c r="A275" s="2" t="s">
         <v>494</v>
       </c>
@@ -6742,7 +7338,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" ht="22.05" customHeight="1" spans="1:4">
       <c r="A276" s="3" t="s">
         <v>495</v>
       </c>
@@ -6756,7 +7352,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" ht="22.05" customHeight="1" spans="1:4">
       <c r="A277" s="2" t="s">
         <v>496</v>
       </c>
@@ -6770,7 +7366,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" ht="22.05" customHeight="1" spans="1:4">
       <c r="A278" s="3" t="s">
         <v>499</v>
       </c>
@@ -6784,7 +7380,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" ht="22.05" customHeight="1" spans="1:4">
       <c r="A279" s="2" t="s">
         <v>502</v>
       </c>
@@ -6798,7 +7394,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" ht="22.05" customHeight="1" spans="1:4">
       <c r="A280" s="3" t="s">
         <v>505</v>
       </c>
@@ -6812,7 +7408,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" ht="22.05" customHeight="1" spans="1:4">
       <c r="A281" s="2" t="s">
         <v>506</v>
       </c>
@@ -6826,7 +7422,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" ht="22.05" customHeight="1" spans="1:4">
       <c r="A282" s="3" t="s">
         <v>507</v>
       </c>
@@ -6840,7 +7436,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" ht="22.05" customHeight="1" spans="1:4">
       <c r="A283" s="2" t="s">
         <v>508</v>
       </c>
@@ -6854,7 +7450,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" ht="22.05" customHeight="1" spans="1:4">
       <c r="A284" s="3" t="s">
         <v>509</v>
       </c>
@@ -6868,7 +7464,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" ht="22.05" customHeight="1" spans="1:4">
       <c r="A285" s="2" t="s">
         <v>512</v>
       </c>
@@ -6882,7 +7478,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" ht="22.05" customHeight="1" spans="1:4">
       <c r="A286" s="3" t="s">
         <v>514</v>
       </c>
@@ -6896,7 +7492,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" ht="22.05" customHeight="1" spans="1:4">
       <c r="A287" s="2" t="s">
         <v>516</v>
       </c>
@@ -6910,7 +7506,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" ht="22.05" customHeight="1" spans="1:4">
       <c r="A288" s="3" t="s">
         <v>517</v>
       </c>
@@ -6924,7 +7520,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" ht="22.05" customHeight="1" spans="1:4">
       <c r="A289" s="2" t="s">
         <v>518</v>
       </c>
@@ -6938,7 +7534,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" ht="22.05" customHeight="1" spans="1:4">
       <c r="A290" s="3" t="s">
         <v>519</v>
       </c>
@@ -6952,7 +7548,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" ht="22.05" customHeight="1" spans="1:4">
       <c r="A291" s="2" t="s">
         <v>520</v>
       </c>
@@ -6966,7 +7562,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" ht="22.05" customHeight="1" spans="1:4">
       <c r="A292" s="3" t="s">
         <v>522</v>
       </c>
@@ -6980,7 +7576,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" ht="22.05" customHeight="1" spans="1:4">
       <c r="A293" s="2" t="s">
         <v>524</v>
       </c>
@@ -6994,7 +7590,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" ht="22.05" customHeight="1" spans="1:4">
       <c r="A294" s="3" t="s">
         <v>526</v>
       </c>
@@ -7008,7 +7604,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" ht="22.05" customHeight="1" spans="1:4">
       <c r="A295" s="2" t="s">
         <v>529</v>
       </c>
@@ -7022,7 +7618,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" ht="22.05" customHeight="1" spans="1:4">
       <c r="A296" s="3" t="s">
         <v>531</v>
       </c>
@@ -7036,7 +7632,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" ht="22.05" customHeight="1" spans="1:4">
       <c r="A297" s="2" t="s">
         <v>533</v>
       </c>
@@ -7050,7 +7646,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" ht="22.05" customHeight="1" spans="1:4">
       <c r="A298" s="3" t="s">
         <v>534</v>
       </c>
@@ -7064,7 +7660,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" ht="22.05" customHeight="1" spans="1:4">
       <c r="A299" s="2" t="s">
         <v>536</v>
       </c>
@@ -7078,7 +7674,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" ht="22.05" customHeight="1" spans="1:4">
       <c r="A300" s="3" t="s">
         <v>537</v>
       </c>
@@ -7092,7 +7688,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" ht="22.05" customHeight="1" spans="1:4">
       <c r="A301" s="2" t="s">
         <v>539</v>
       </c>
@@ -7106,7 +7702,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" ht="22.05" customHeight="1" spans="1:4">
       <c r="A302" s="3" t="s">
         <v>541</v>
       </c>
@@ -7120,7 +7716,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" ht="22.05" customHeight="1" spans="1:4">
       <c r="A303" s="2" t="s">
         <v>544</v>
       </c>
@@ -7134,7 +7730,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" ht="22.05" customHeight="1" spans="1:4">
       <c r="A304" s="3" t="s">
         <v>547</v>
       </c>
@@ -7148,7 +7744,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" ht="22.05" customHeight="1" spans="1:4">
       <c r="A305" s="2" t="s">
         <v>548</v>
       </c>
@@ -7162,7 +7758,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" ht="22.05" customHeight="1" spans="1:4">
       <c r="A306" s="3" t="s">
         <v>550</v>
       </c>
@@ -7176,7 +7772,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" ht="22.05" customHeight="1" spans="1:4">
       <c r="A307" s="2" t="s">
         <v>552</v>
       </c>
@@ -7190,7 +7786,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" ht="22.05" customHeight="1" spans="1:4">
       <c r="A308" s="3" t="s">
         <v>553</v>
       </c>
@@ -7204,7 +7800,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" ht="22.05" customHeight="1" spans="1:4">
       <c r="A309" s="2" t="s">
         <v>555</v>
       </c>
@@ -7214,11 +7810,11 @@
       <c r="C309" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D309" s="5" t="s">
+      <c r="D309" s="6" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" ht="22.05" customHeight="1" spans="1:4">
       <c r="A310" s="3" t="s">
         <v>558</v>
       </c>
@@ -7232,7 +7828,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" ht="22.05" customHeight="1" spans="1:4">
       <c r="A311" s="2" t="s">
         <v>560</v>
       </c>
@@ -7246,7 +7842,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" ht="22.05" customHeight="1" spans="1:4">
       <c r="A312" s="3" t="s">
         <v>561</v>
       </c>
@@ -7260,7 +7856,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" ht="22.05" customHeight="1" spans="1:4">
       <c r="A313" s="2" t="s">
         <v>562</v>
       </c>
@@ -7274,7 +7870,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" ht="22.05" customHeight="1" spans="1:4">
       <c r="A314" s="3" t="s">
         <v>564</v>
       </c>
@@ -7288,7 +7884,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" ht="22.05" customHeight="1" spans="1:4">
       <c r="A315" s="2" t="s">
         <v>565</v>
       </c>
@@ -7302,7 +7898,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" ht="22.05" customHeight="1" spans="1:4">
       <c r="A316" s="3" t="s">
         <v>567</v>
       </c>
@@ -7316,7 +7912,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" ht="22.05" customHeight="1" spans="1:4">
       <c r="A317" s="2" t="s">
         <v>568</v>
       </c>
@@ -7330,7 +7926,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" ht="22.05" customHeight="1" spans="1:4">
       <c r="A318" s="3" t="s">
         <v>571</v>
       </c>
@@ -7344,7 +7940,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" ht="22.05" customHeight="1" spans="1:4">
       <c r="A319" s="2" t="s">
         <v>572</v>
       </c>
@@ -7358,7 +7954,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" ht="22.05" customHeight="1" spans="1:4">
       <c r="A320" s="3" t="s">
         <v>573</v>
       </c>
@@ -7372,7 +7968,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" ht="22.05" customHeight="1" spans="1:4">
       <c r="A321" s="2" t="s">
         <v>574</v>
       </c>
@@ -7386,7 +7982,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" ht="22.05" customHeight="1" spans="1:4">
       <c r="A322" s="3" t="s">
         <v>575</v>
       </c>
@@ -7400,7 +7996,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" ht="22.05" customHeight="1" spans="1:4">
       <c r="A323" s="2" t="s">
         <v>576</v>
       </c>
@@ -7414,7 +8010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" ht="22.05" customHeight="1" spans="1:4">
       <c r="A324" s="3" t="s">
         <v>577</v>
       </c>
@@ -7428,7 +8024,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" ht="22.05" customHeight="1" spans="1:4">
       <c r="A325" s="2" t="s">
         <v>578</v>
       </c>
@@ -7442,7 +8038,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" ht="22.05" customHeight="1" spans="1:4">
       <c r="A326" s="3" t="s">
         <v>580</v>
       </c>
@@ -7456,7 +8052,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" ht="22.05" customHeight="1" spans="1:4">
       <c r="A327" s="2" t="s">
         <v>581</v>
       </c>
@@ -7470,7 +8066,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" ht="22.05" customHeight="1" spans="1:4">
       <c r="A328" s="3" t="s">
         <v>583</v>
       </c>
@@ -7484,7 +8080,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" ht="22.05" customHeight="1" spans="1:4">
       <c r="A329" s="2" t="s">
         <v>584</v>
       </c>
@@ -7498,7 +8094,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" ht="22.05" customHeight="1" spans="1:4">
       <c r="A330" s="3" t="s">
         <v>586</v>
       </c>
@@ -7512,7 +8108,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" ht="22.05" customHeight="1" spans="1:4">
       <c r="A331" s="2" t="s">
         <v>588</v>
       </c>
@@ -7526,7 +8122,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" ht="22.05" customHeight="1" spans="1:4">
       <c r="A332" s="3" t="s">
         <v>591</v>
       </c>
@@ -7540,7 +8136,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" ht="22.05" customHeight="1" spans="1:4">
       <c r="A333" s="2" t="s">
         <v>592</v>
       </c>
@@ -7554,7 +8150,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" ht="22.05" customHeight="1" spans="1:4">
       <c r="A334" s="3" t="s">
         <v>594</v>
       </c>
@@ -7568,7 +8164,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" ht="22.05" customHeight="1" spans="1:4">
       <c r="A335" s="2" t="s">
         <v>596</v>
       </c>
@@ -7582,7 +8178,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" ht="22.05" customHeight="1" spans="1:4">
       <c r="A336" s="3" t="s">
         <v>597</v>
       </c>
@@ -7596,7 +8192,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" ht="22.05" customHeight="1" spans="1:4">
       <c r="A337" s="2" t="s">
         <v>599</v>
       </c>
@@ -7610,7 +8206,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" ht="22.05" customHeight="1" spans="1:4">
       <c r="A338" s="3" t="s">
         <v>600</v>
       </c>
@@ -7624,7 +8220,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" ht="22.05" customHeight="1" spans="1:4">
       <c r="A339" s="2" t="s">
         <v>601</v>
       </c>
@@ -7638,7 +8234,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" ht="22.05" customHeight="1" spans="1:4">
       <c r="A340" s="3" t="s">
         <v>602</v>
       </c>
@@ -7652,7 +8248,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" ht="22.05" customHeight="1" spans="1:4">
       <c r="A341" s="2" t="s">
         <v>603</v>
       </c>
@@ -7666,7 +8262,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" ht="22.05" customHeight="1" spans="1:4">
       <c r="A342" s="3" t="s">
         <v>604</v>
       </c>
@@ -7680,7 +8276,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" ht="22.05" customHeight="1" spans="1:4">
       <c r="A343" s="2" t="s">
         <v>606</v>
       </c>
@@ -7694,7 +8290,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" ht="22.05" customHeight="1" spans="1:4">
       <c r="A344" s="3" t="s">
         <v>607</v>
       </c>
@@ -7708,7 +8304,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" ht="22.05" customHeight="1" spans="1:4">
       <c r="A345" s="2" t="s">
         <v>608</v>
       </c>
@@ -7722,7 +8318,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" ht="22.05" customHeight="1" spans="1:4">
       <c r="A346" s="3" t="s">
         <v>610</v>
       </c>
@@ -7736,7 +8332,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" ht="22.05" customHeight="1" spans="1:4">
       <c r="A347" s="2" t="s">
         <v>611</v>
       </c>
@@ -7750,7 +8346,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" ht="22.05" customHeight="1" spans="1:4">
       <c r="A348" s="3" t="s">
         <v>613</v>
       </c>
@@ -7764,7 +8360,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" ht="22.05" customHeight="1" spans="1:4">
       <c r="A349" s="2" t="s">
         <v>614</v>
       </c>
@@ -7778,7 +8374,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" ht="22.05" customHeight="1" spans="1:4">
       <c r="A350" s="3" t="s">
         <v>616</v>
       </c>
@@ -7792,7 +8388,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" ht="22.05" customHeight="1" spans="1:4">
       <c r="A351" s="2" t="s">
         <v>617</v>
       </c>
@@ -7806,7 +8402,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" ht="22.05" customHeight="1" spans="1:4">
       <c r="A352" s="3" t="s">
         <v>618</v>
       </c>
@@ -7820,7 +8416,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" ht="22.05" customHeight="1" spans="1:4">
       <c r="A353" s="2" t="s">
         <v>619</v>
       </c>
@@ -7834,7 +8430,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" ht="22.05" customHeight="1" spans="1:4">
       <c r="A354" s="3" t="s">
         <v>620</v>
       </c>
@@ -7848,7 +8444,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" ht="22.05" customHeight="1" spans="1:4">
       <c r="A355" s="2" t="s">
         <v>620</v>
       </c>
@@ -7862,7 +8458,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" ht="22.05" customHeight="1" spans="1:4">
       <c r="A356" s="3" t="s">
         <v>624</v>
       </c>
@@ -7876,7 +8472,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" ht="22.05" customHeight="1" spans="1:4">
       <c r="A357" s="2" t="s">
         <v>625</v>
       </c>
@@ -7890,7 +8486,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" ht="22.05" customHeight="1" spans="1:4">
       <c r="A358" s="3" t="s">
         <v>627</v>
       </c>
@@ -7904,7 +8500,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" ht="22.05" customHeight="1" spans="1:4">
       <c r="A359" s="2" t="s">
         <v>628</v>
       </c>
@@ -7918,7 +8514,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" ht="22.05" customHeight="1" spans="1:4">
       <c r="A360" s="3" t="s">
         <v>629</v>
       </c>
@@ -7932,7 +8528,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" ht="22.05" customHeight="1" spans="1:4">
       <c r="A361" s="2" t="s">
         <v>630</v>
       </c>
@@ -7946,7 +8542,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" ht="22.05" customHeight="1" spans="1:4">
       <c r="A362" s="3" t="s">
         <v>631</v>
       </c>
@@ -7960,7 +8556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" ht="22.05" customHeight="1" spans="1:4">
       <c r="A363" s="2" t="s">
         <v>632</v>
       </c>
@@ -7974,7 +8570,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" ht="22.05" customHeight="1" spans="1:4">
       <c r="A364" s="3" t="s">
         <v>633</v>
       </c>
@@ -7988,7 +8584,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" ht="22.05" customHeight="1" spans="1:4">
       <c r="A365" s="2" t="s">
         <v>634</v>
       </c>
@@ -8002,7 +8598,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" ht="22.05" customHeight="1" spans="1:4">
       <c r="A366" s="3" t="s">
         <v>636</v>
       </c>
@@ -8016,7 +8612,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" ht="22.05" customHeight="1" spans="1:4">
       <c r="A367" s="2" t="s">
         <v>638</v>
       </c>
@@ -8030,7 +8626,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" ht="22.05" customHeight="1" spans="1:4">
       <c r="A368" s="3" t="s">
         <v>639</v>
       </c>
@@ -8044,7 +8640,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" ht="22.05" customHeight="1" spans="1:4">
       <c r="A369" s="2" t="s">
         <v>642</v>
       </c>
@@ -8058,7 +8654,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" ht="22.05" customHeight="1" spans="1:4">
       <c r="A370" s="3" t="s">
         <v>643</v>
       </c>
@@ -8072,7 +8668,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" ht="22.05" customHeight="1" spans="1:4">
       <c r="A371" s="2" t="s">
         <v>645</v>
       </c>
@@ -8086,7 +8682,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" ht="22.05" customHeight="1" spans="1:4">
       <c r="A372" s="3" t="s">
         <v>647</v>
       </c>
@@ -8100,7 +8696,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" ht="22.05" customHeight="1" spans="1:4">
       <c r="A373" s="2" t="s">
         <v>649</v>
       </c>
@@ -8114,7 +8710,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" ht="22.05" customHeight="1" spans="1:4">
       <c r="A374" s="3" t="s">
         <v>652</v>
       </c>
@@ -8128,7 +8724,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" ht="22.05" customHeight="1" spans="1:4">
       <c r="A375" s="2" t="s">
         <v>653</v>
       </c>
@@ -8142,7 +8738,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" ht="22.05" customHeight="1" spans="1:4">
       <c r="A376" s="3" t="s">
         <v>653</v>
       </c>
@@ -8156,7 +8752,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" ht="22.05" customHeight="1" spans="1:4">
       <c r="A377" s="2" t="s">
         <v>653</v>
       </c>
@@ -8170,7 +8766,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" ht="22.05" customHeight="1" spans="1:4">
       <c r="A378" s="3" t="s">
         <v>653</v>
       </c>
@@ -8184,7 +8780,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" ht="22.05" customHeight="1" spans="1:4">
       <c r="A379" s="2" t="s">
         <v>653</v>
       </c>
@@ -8198,7 +8794,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" ht="22.05" customHeight="1" spans="1:4">
       <c r="A380" s="3" t="s">
         <v>653</v>
       </c>
@@ -8212,7 +8808,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" ht="22.05" customHeight="1" spans="1:4">
       <c r="A381" s="2" t="s">
         <v>662</v>
       </c>
@@ -8226,7 +8822,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" ht="22.05" customHeight="1" spans="1:4">
       <c r="A382" s="3" t="s">
         <v>663</v>
       </c>
@@ -8240,7 +8836,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" ht="22.05" customHeight="1" spans="1:4">
       <c r="A383" s="2" t="s">
         <v>665</v>
       </c>
@@ -8254,7 +8850,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" ht="22.05" customHeight="1" spans="1:4">
       <c r="A384" s="3" t="s">
         <v>666</v>
       </c>
@@ -8268,7 +8864,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" ht="22.05" customHeight="1" spans="1:4">
       <c r="A385" s="2" t="s">
         <v>668</v>
       </c>
@@ -8282,7 +8878,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" ht="22.05" customHeight="1" spans="1:4">
       <c r="A386" s="3" t="s">
         <v>669</v>
       </c>
@@ -8296,7 +8892,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" ht="22.05" customHeight="1" spans="1:4">
       <c r="A387" s="2" t="s">
         <v>671</v>
       </c>
@@ -8310,7 +8906,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" ht="22.05" customHeight="1" spans="1:4">
       <c r="A388" s="3" t="s">
         <v>673</v>
       </c>
@@ -8324,7 +8920,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" ht="22.05" customHeight="1" spans="1:4">
       <c r="A389" s="2" t="s">
         <v>675</v>
       </c>
@@ -8338,7 +8934,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" ht="22.05" customHeight="1" spans="1:4">
       <c r="A390" s="3" t="s">
         <v>677</v>
       </c>
@@ -8352,7 +8948,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" ht="22.05" customHeight="1" spans="1:4">
       <c r="A391" s="2" t="s">
         <v>678</v>
       </c>
@@ -8366,7 +8962,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" ht="22.05" customHeight="1" spans="1:4">
       <c r="A392" s="3" t="s">
         <v>680</v>
       </c>
@@ -8380,7 +8976,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" ht="22.05" customHeight="1" spans="1:4">
       <c r="A393" s="2" t="s">
         <v>681</v>
       </c>
@@ -8394,7 +8990,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" ht="22.05" customHeight="1" spans="1:4">
       <c r="A394" s="3" t="s">
         <v>682</v>
       </c>
@@ -8408,7 +9004,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" ht="22.05" customHeight="1" spans="1:4">
       <c r="A395" s="2" t="s">
         <v>683</v>
       </c>
@@ -8422,7 +9018,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" ht="22.05" customHeight="1" spans="1:4">
       <c r="A396" s="3" t="s">
         <v>684</v>
       </c>
@@ -8436,7 +9032,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" ht="22.05" customHeight="1" spans="1:4">
       <c r="A397" s="2" t="s">
         <v>686</v>
       </c>
@@ -8450,7 +9046,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" ht="22.05" customHeight="1" spans="1:4">
       <c r="A398" s="3" t="s">
         <v>688</v>
       </c>
@@ -8464,7 +9060,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" ht="22.05" customHeight="1" spans="1:4">
       <c r="A399" s="2" t="s">
         <v>689</v>
       </c>
@@ -8478,7 +9074,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" ht="22.05" customHeight="1" spans="1:4">
       <c r="A400" s="3" t="s">
         <v>690</v>
       </c>
@@ -8492,7 +9088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" ht="22.05" customHeight="1" spans="1:4">
       <c r="A401" s="2" t="s">
         <v>691</v>
       </c>
@@ -8506,7 +9102,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" ht="22.05" customHeight="1" spans="1:4">
       <c r="A402" s="3" t="s">
         <v>693</v>
       </c>
@@ -8520,7 +9116,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" ht="22.05" customHeight="1" spans="1:4">
       <c r="A403" s="2" t="s">
         <v>695</v>
       </c>
@@ -8534,7 +9130,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" ht="22.05" customHeight="1" spans="1:4">
       <c r="A404" s="3" t="s">
         <v>696</v>
       </c>
@@ -8548,7 +9144,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" ht="22.05" customHeight="1" spans="1:4">
       <c r="A405" s="2" t="s">
         <v>697</v>
       </c>
@@ -8562,7 +9158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" ht="22.05" customHeight="1" spans="1:4">
       <c r="A406" s="3" t="s">
         <v>698</v>
       </c>
@@ -8576,7 +9172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" ht="22.05" customHeight="1" spans="1:4">
       <c r="A407" s="2" t="s">
         <v>699</v>
       </c>
@@ -8590,7 +9186,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" ht="22.05" customHeight="1" spans="1:4">
       <c r="A408" s="3" t="s">
         <v>701</v>
       </c>
@@ -8604,7 +9200,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" ht="22.05" customHeight="1" spans="1:4">
       <c r="A409" s="2" t="s">
         <v>702</v>
       </c>
@@ -8618,7 +9214,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" ht="22.05" customHeight="1" spans="1:4">
       <c r="A410" s="3" t="s">
         <v>703</v>
       </c>
@@ -8632,7 +9228,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" ht="22.05" customHeight="1" spans="1:4">
       <c r="A411" s="2" t="s">
         <v>703</v>
       </c>
@@ -8646,7 +9242,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" ht="22.05" customHeight="1" spans="1:4">
       <c r="A412" s="3" t="s">
         <v>705</v>
       </c>
@@ -8660,7 +9256,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" ht="22.05" customHeight="1" spans="1:4">
       <c r="A413" s="2" t="s">
         <v>706</v>
       </c>
@@ -8674,7 +9270,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" ht="22.05" customHeight="1" spans="1:4">
       <c r="A414" s="3" t="s">
         <v>707</v>
       </c>
@@ -8688,7 +9284,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" ht="22.05" customHeight="1" spans="1:4">
       <c r="A415" s="2" t="s">
         <v>708</v>
       </c>
@@ -8702,7 +9298,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" ht="22.05" customHeight="1" spans="1:4">
       <c r="A416" s="3" t="s">
         <v>709</v>
       </c>
@@ -8716,7 +9312,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" ht="22.05" customHeight="1" spans="1:4">
       <c r="A417" s="2" t="s">
         <v>711</v>
       </c>
@@ -8730,7 +9326,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" ht="22.05" customHeight="1" spans="1:4">
       <c r="A418" s="3" t="s">
         <v>712</v>
       </c>
@@ -8744,7 +9340,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" ht="22.05" customHeight="1" spans="1:4">
       <c r="A419" s="2" t="s">
         <v>713</v>
       </c>
@@ -8758,7 +9354,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" ht="22.05" customHeight="1" spans="1:4">
       <c r="A420" s="3" t="s">
         <v>714</v>
       </c>
@@ -8772,7 +9368,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" ht="22.05" customHeight="1" spans="1:4">
       <c r="A421" s="2" t="s">
         <v>715</v>
       </c>
@@ -8786,7 +9382,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" ht="22.05" customHeight="1" spans="1:4">
       <c r="A422" s="3" t="s">
         <v>716</v>
       </c>
@@ -8800,7 +9396,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" ht="22.05" customHeight="1" spans="1:4">
       <c r="A423" s="2" t="s">
         <v>717</v>
       </c>
@@ -8814,7 +9410,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" ht="22.05" customHeight="1" spans="1:4">
       <c r="A424" s="3" t="s">
         <v>718</v>
       </c>
@@ -8828,7 +9424,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" ht="22.05" customHeight="1" spans="1:4">
       <c r="A425" s="2" t="s">
         <v>720</v>
       </c>
@@ -8842,7 +9438,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" ht="22.05" customHeight="1" spans="1:4">
       <c r="A426" s="3" t="s">
         <v>722</v>
       </c>
@@ -8856,7 +9452,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" ht="22.05" customHeight="1" spans="1:4">
       <c r="A427" s="2" t="s">
         <v>723</v>
       </c>
@@ -8870,7 +9466,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" ht="22.05" customHeight="1" spans="1:4">
       <c r="A428" s="3" t="s">
         <v>724</v>
       </c>
@@ -8884,7 +9480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" ht="22.05" customHeight="1" spans="1:4">
       <c r="A429" s="2" t="s">
         <v>725</v>
       </c>
@@ -8898,7 +9494,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" ht="22.05" customHeight="1" spans="1:4">
       <c r="A430" s="3" t="s">
         <v>727</v>
       </c>
@@ -8912,7 +9508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" ht="22.05" customHeight="1" spans="1:4">
       <c r="A431" s="2" t="s">
         <v>729</v>
       </c>
@@ -8926,7 +9522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" ht="22.05" customHeight="1" spans="1:4">
       <c r="A432" s="3" t="s">
         <v>730</v>
       </c>
@@ -8940,7 +9536,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" ht="22.05" customHeight="1" spans="1:4">
       <c r="A433" s="2" t="s">
         <v>731</v>
       </c>
@@ -8954,7 +9550,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" ht="22.05" customHeight="1" spans="1:4">
       <c r="A434" s="3" t="s">
         <v>733</v>
       </c>
@@ -8968,7 +9564,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" ht="22.05" customHeight="1" spans="1:4">
       <c r="A435" s="2" t="s">
         <v>734</v>
       </c>
@@ -8982,7 +9578,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" ht="22.05" customHeight="1" spans="1:4">
       <c r="A436" s="3" t="s">
         <v>736</v>
       </c>
@@ -8996,7 +9592,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" ht="22.05" customHeight="1" spans="1:4">
       <c r="A437" s="2" t="s">
         <v>738</v>
       </c>
@@ -9010,7 +9606,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" ht="22.05" customHeight="1" spans="1:4">
       <c r="A438" s="3" t="s">
         <v>739</v>
       </c>
@@ -9024,7 +9620,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" ht="22.05" customHeight="1" spans="1:4">
       <c r="A439" s="2" t="s">
         <v>741</v>
       </c>
@@ -9038,7 +9634,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" ht="22.05" customHeight="1" spans="1:4">
       <c r="A440" s="3" t="s">
         <v>742</v>
       </c>
@@ -9052,7 +9648,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" ht="22.05" customHeight="1" spans="1:4">
       <c r="A441" s="2" t="s">
         <v>743</v>
       </c>
@@ -9066,7 +9662,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" ht="22.05" customHeight="1" spans="1:4">
       <c r="A442" s="3" t="s">
         <v>745</v>
       </c>
@@ -9080,7 +9676,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" ht="22.05" customHeight="1" spans="1:4">
       <c r="A443" s="2" t="s">
         <v>746</v>
       </c>
@@ -9094,7 +9690,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" ht="22.05" customHeight="1" spans="1:4">
       <c r="A444" s="3" t="s">
         <v>747</v>
       </c>
@@ -9108,7 +9704,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" ht="22.05" customHeight="1" spans="1:4">
       <c r="A445" s="2" t="s">
         <v>749</v>
       </c>
@@ -9122,7 +9718,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" ht="22.05" customHeight="1" spans="1:4">
       <c r="A446" s="3" t="s">
         <v>751</v>
       </c>
@@ -9136,7 +9732,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" ht="22.05" customHeight="1" spans="1:4">
       <c r="A447" s="2" t="s">
         <v>753</v>
       </c>
@@ -9150,7 +9746,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" ht="22.05" customHeight="1" spans="1:4">
       <c r="A448" s="3" t="s">
         <v>756</v>
       </c>
@@ -9164,7 +9760,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" ht="22.05" customHeight="1" spans="1:4">
       <c r="A449" s="2" t="s">
         <v>757</v>
       </c>
@@ -9178,7 +9774,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" ht="22.05" customHeight="1" spans="1:4">
       <c r="A450" s="3" t="s">
         <v>759</v>
       </c>
@@ -9192,7 +9788,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" ht="22.05" customHeight="1" spans="1:4">
       <c r="A451" s="2" t="s">
         <v>761</v>
       </c>
@@ -9206,7 +9802,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" ht="22.05" customHeight="1" spans="1:4">
       <c r="A452" s="3" t="s">
         <v>764</v>
       </c>
@@ -9220,7 +9816,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" ht="22.05" customHeight="1" spans="1:4">
       <c r="A453" s="2" t="s">
         <v>766</v>
       </c>
@@ -9234,7 +9830,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" ht="22.05" customHeight="1" spans="1:4">
       <c r="A454" s="3" t="s">
         <v>767</v>
       </c>
@@ -9248,7 +9844,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" ht="22.05" customHeight="1" spans="1:4">
       <c r="A455" s="2" t="s">
         <v>768</v>
       </c>
@@ -9262,7 +9858,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" ht="22.05" customHeight="1" spans="1:4">
       <c r="A456" s="3" t="s">
         <v>769</v>
       </c>
@@ -9277,21 +9873,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9305,7 +9902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>271</v>
       </c>
@@ -9319,7 +9916,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>271</v>
       </c>
@@ -9333,7 +9930,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>276</v>
       </c>
@@ -9347,7 +9944,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>276</v>
       </c>
@@ -9361,7 +9958,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>278</v>
       </c>
@@ -9375,7 +9972,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>278</v>
       </c>
@@ -9389,7 +9986,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>281</v>
       </c>
@@ -9403,7 +10000,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>284</v>
       </c>
@@ -9418,22 +10015,23 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9447,7 +10045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>288</v>
       </c>
@@ -9461,7 +10059,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>421</v>
       </c>
@@ -9475,7 +10073,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>424</v>
       </c>
@@ -9489,7 +10087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>553</v>
       </c>
@@ -9503,7 +10101,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>647</v>
       </c>
@@ -9517,7 +10115,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>649</v>
       </c>
@@ -9531,7 +10129,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>652</v>
       </c>
@@ -9545,7 +10143,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>653</v>
       </c>
@@ -9559,7 +10157,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>653</v>
       </c>
@@ -9573,7 +10171,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>653</v>
       </c>
@@ -9587,7 +10185,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>653</v>
       </c>
@@ -9601,7 +10199,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>653</v>
       </c>
@@ -9615,7 +10213,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>653</v>
       </c>
@@ -9629,7 +10227,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>663</v>
       </c>
@@ -9643,7 +10241,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>665</v>
       </c>
@@ -9657,7 +10255,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>668</v>
       </c>
@@ -9671,7 +10269,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>669</v>
       </c>
@@ -9685,7 +10283,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>671</v>
       </c>
@@ -9699,7 +10297,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
         <v>673</v>
       </c>
@@ -9713,7 +10311,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>675</v>
       </c>
@@ -9727,7 +10325,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>684</v>
       </c>
@@ -9741,7 +10339,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>691</v>
       </c>
@@ -9755,7 +10353,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="2" t="s">
         <v>702</v>
       </c>
@@ -9769,7 +10367,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>703</v>
       </c>
@@ -9783,7 +10381,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="2" t="s">
         <v>703</v>
       </c>
@@ -9797,7 +10395,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>715</v>
       </c>
@@ -9811,7 +10409,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>716</v>
       </c>
@@ -9825,7 +10423,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>717</v>
       </c>
@@ -9839,11 +10437,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>805</v>
-      </c>
-      <c r="B30" s="17" t="s">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>807</v>
       </c>
       <c r="C30" s="3">
@@ -9853,12 +10451,12 @@
         <v>470</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>806</v>
-      </c>
-      <c r="B31" s="17" t="s">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A31" s="4" t="s">
         <v>808</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>809</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -9867,40 +10465,41 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9914,7 +10513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>436</v>
       </c>
@@ -9928,7 +10527,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>581</v>
       </c>
@@ -9942,7 +10541,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>588</v>
       </c>
@@ -9956,7 +10555,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>591</v>
       </c>
@@ -9970,7 +10569,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>596</v>
       </c>
@@ -9984,7 +10583,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>597</v>
       </c>
@@ -9998,7 +10597,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>634</v>
       </c>
@@ -10013,21 +10612,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10041,7 +10641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>627</v>
       </c>
@@ -10055,7 +10655,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>628</v>
       </c>
@@ -10069,7 +10669,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>629</v>
       </c>
@@ -10083,7 +10683,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>630</v>
       </c>
@@ -10098,21 +10698,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10126,7 +10727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>734</v>
       </c>
@@ -10140,7 +10741,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>736</v>
       </c>
@@ -10154,7 +10755,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>738</v>
       </c>
@@ -10168,7 +10769,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>739</v>
       </c>
@@ -10182,7 +10783,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>741</v>
       </c>
@@ -10196,7 +10797,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>742</v>
       </c>
@@ -10210,7 +10811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>743</v>
       </c>
@@ -10224,7 +10825,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>745</v>
       </c>
@@ -10238,7 +10839,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>746</v>
       </c>
@@ -10252,7 +10853,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>747</v>
       </c>
@@ -10266,7 +10867,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>749</v>
       </c>
@@ -10280,7 +10881,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>751</v>
       </c>
@@ -10294,7 +10895,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>753</v>
       </c>
@@ -10308,7 +10909,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>756</v>
       </c>
@@ -10322,7 +10923,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>757</v>
       </c>
@@ -10336,7 +10937,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>759</v>
       </c>
@@ -10350,7 +10951,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>761</v>
       </c>
@@ -10364,7 +10965,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>764</v>
       </c>
@@ -10378,7 +10979,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
         <v>766</v>
       </c>
@@ -10392,7 +10993,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>767</v>
       </c>
@@ -10406,7 +11007,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>768</v>
       </c>
@@ -10420,7 +11021,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>769</v>
       </c>
@@ -10435,31 +11036,33 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAC5454-EB5F-4F35-AF09-F6FA6FA4E96C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10473,7 +11076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>770</v>
       </c>
@@ -10487,7 +11090,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>772</v>
       </c>
@@ -10501,7 +11104,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>774</v>
       </c>
@@ -10515,7 +11118,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>775</v>
       </c>
@@ -10529,7 +11132,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>777</v>
       </c>
@@ -10543,7 +11146,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>779</v>
       </c>
@@ -10557,7 +11160,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>781</v>
       </c>
@@ -10571,7 +11174,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>783</v>
       </c>
@@ -10585,7 +11188,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>784</v>
       </c>
@@ -10599,7 +11202,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>787</v>
       </c>
@@ -10613,7 +11216,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>788</v>
       </c>
@@ -10627,7 +11230,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>789</v>
       </c>
@@ -10641,21 +11244,21 @@
         <v>790</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="9">
         <v>1850</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="9">
         <v>1850</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -10669,7 +11272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -10683,7 +11286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -10697,7 +11300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
@@ -10711,7 +11314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -10725,7 +11328,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -10739,7 +11342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -10753,7 +11356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -10767,7 +11370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -10781,7 +11384,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -10795,7 +11398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -10809,7 +11412,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
@@ -10823,7 +11426,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="2" t="s">
         <v>40</v>
       </c>
@@ -10837,7 +11440,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
@@ -10851,7 +11454,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="2" t="s">
         <v>58</v>
       </c>
@@ -10865,7 +11468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>60</v>
       </c>
@@ -10879,7 +11482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -10893,7 +11496,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>69</v>
       </c>
@@ -10907,7 +11510,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="2" t="s">
         <v>71</v>
       </c>
@@ -10921,7 +11524,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>73</v>
       </c>
@@ -10935,7 +11538,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="2" t="s">
         <v>74</v>
       </c>
@@ -10949,7 +11552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="3" t="s">
         <v>78</v>
       </c>
@@ -10963,7 +11566,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
       <c r="A37" s="2" t="s">
         <v>81</v>
       </c>
@@ -10977,7 +11580,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
       <c r="A38" s="3" t="s">
         <v>83</v>
       </c>
@@ -10991,7 +11594,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
       <c r="A39" s="2" t="s">
         <v>85</v>
       </c>
@@ -11005,7 +11608,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>87</v>
       </c>
@@ -11019,7 +11622,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
       <c r="A41" s="2" t="s">
         <v>89</v>
       </c>
@@ -11033,7 +11636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>90</v>
       </c>
@@ -11047,7 +11650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
       <c r="A43" s="2" t="s">
         <v>91</v>
       </c>
@@ -11061,7 +11664,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>93</v>
       </c>
@@ -11075,7 +11678,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
@@ -11089,7 +11692,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>102</v>
       </c>
@@ -11103,7 +11706,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
       <c r="A47" s="2" t="s">
         <v>103</v>
       </c>
@@ -11117,7 +11720,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>105</v>
       </c>
@@ -11131,7 +11734,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
       <c r="A49" s="2" t="s">
         <v>106</v>
       </c>
@@ -11145,7 +11748,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
       <c r="A50" s="3" t="s">
         <v>115</v>
       </c>
@@ -11159,7 +11762,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
       <c r="A51" s="2" t="s">
         <v>117</v>
       </c>
@@ -11173,7 +11776,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
       <c r="A52" s="3" t="s">
         <v>118</v>
       </c>
@@ -11187,7 +11790,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
       <c r="A53" s="2" t="s">
         <v>119</v>
       </c>
@@ -11201,7 +11804,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
       <c r="A54" s="3" t="s">
         <v>120</v>
       </c>
@@ -11215,7 +11818,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
       <c r="A55" s="2" t="s">
         <v>121</v>
       </c>
@@ -11229,7 +11832,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
       <c r="A56" s="3" t="s">
         <v>127</v>
       </c>
@@ -11243,7 +11846,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
       <c r="A57" s="2" t="s">
         <v>127</v>
       </c>
@@ -11257,7 +11860,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
       <c r="A58" s="3" t="s">
         <v>129</v>
       </c>
@@ -11271,7 +11874,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
       <c r="A59" s="2" t="s">
         <v>130</v>
       </c>
@@ -11285,7 +11888,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
       <c r="A60" s="3" t="s">
         <v>133</v>
       </c>
@@ -11299,7 +11902,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
       <c r="A61" s="2" t="s">
         <v>134</v>
       </c>
@@ -11313,7 +11916,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
       <c r="A62" s="3" t="s">
         <v>136</v>
       </c>
@@ -11327,7 +11930,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
       <c r="A63" s="2" t="s">
         <v>138</v>
       </c>
@@ -11341,7 +11944,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
       <c r="A64" s="3" t="s">
         <v>140</v>
       </c>
@@ -11355,7 +11958,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="22.05" customHeight="1" spans="1:4">
       <c r="A65" s="2" t="s">
         <v>142</v>
       </c>
@@ -11369,7 +11972,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="22.05" customHeight="1" spans="1:4">
       <c r="A66" s="3" t="s">
         <v>144</v>
       </c>
@@ -11383,7 +11986,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="22.05" customHeight="1" spans="1:4">
       <c r="A67" s="2" t="s">
         <v>152</v>
       </c>
@@ -11397,7 +12000,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="22.05" customHeight="1" spans="1:4">
       <c r="A68" s="3" t="s">
         <v>154</v>
       </c>
@@ -11411,7 +12014,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="22.05" customHeight="1" spans="1:4">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -11425,7 +12028,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="22.05" customHeight="1" spans="1:4">
       <c r="A70" s="3" t="s">
         <v>161</v>
       </c>
@@ -11439,7 +12042,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="22.05" customHeight="1" spans="1:4">
       <c r="A71" s="2" t="s">
         <v>162</v>
       </c>
@@ -11453,7 +12056,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="22.05" customHeight="1" spans="1:4">
       <c r="A72" s="3" t="s">
         <v>164</v>
       </c>
@@ -11467,7 +12070,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="22.05" customHeight="1" spans="1:4">
       <c r="A73" s="2" t="s">
         <v>165</v>
       </c>
@@ -11481,7 +12084,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="22.05" customHeight="1" spans="1:4">
       <c r="A74" s="3" t="s">
         <v>166</v>
       </c>
@@ -11495,7 +12098,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="22.05" customHeight="1" spans="1:4">
       <c r="A75" s="2" t="s">
         <v>167</v>
       </c>
@@ -11509,7 +12112,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="22.05" customHeight="1" spans="1:4">
       <c r="A76" s="3" t="s">
         <v>170</v>
       </c>
@@ -11523,7 +12126,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="22.05" customHeight="1" spans="1:4">
       <c r="A77" s="2" t="s">
         <v>172</v>
       </c>
@@ -11537,7 +12140,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="22.05" customHeight="1" spans="1:4">
       <c r="A78" s="3" t="s">
         <v>268</v>
       </c>
@@ -11551,7 +12154,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="22.05" customHeight="1" spans="1:4">
       <c r="A79" s="2" t="s">
         <v>296</v>
       </c>
@@ -11565,7 +12168,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="22.05" customHeight="1" spans="1:4">
       <c r="A80" s="3" t="s">
         <v>303</v>
       </c>
@@ -11579,7 +12182,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="22.05" customHeight="1" spans="1:4">
       <c r="A81" s="2" t="s">
         <v>305</v>
       </c>
@@ -11593,7 +12196,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="22.05" customHeight="1" spans="1:4">
       <c r="A82" s="3" t="s">
         <v>306</v>
       </c>
@@ -11607,7 +12210,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="22.05" customHeight="1" spans="1:4">
       <c r="A83" s="2" t="s">
         <v>308</v>
       </c>
@@ -11621,7 +12224,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="22.05" customHeight="1" spans="1:4">
       <c r="A84" s="3" t="s">
         <v>310</v>
       </c>
@@ -11635,7 +12238,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="22.05" customHeight="1" spans="1:4">
       <c r="A85" s="2" t="s">
         <v>313</v>
       </c>
@@ -11649,7 +12252,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="22.05" customHeight="1" spans="1:4">
       <c r="A86" s="3" t="s">
         <v>324</v>
       </c>
@@ -11663,7 +12266,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="22.05" customHeight="1" spans="1:4">
       <c r="A87" s="2" t="s">
         <v>325</v>
       </c>
@@ -11677,7 +12280,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="22.05" customHeight="1" spans="1:4">
       <c r="A88" s="3" t="s">
         <v>344</v>
       </c>
@@ -11691,7 +12294,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="22.05" customHeight="1" spans="1:4">
       <c r="A89" s="2" t="s">
         <v>345</v>
       </c>
@@ -11705,7 +12308,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="22.05" customHeight="1" spans="1:4">
       <c r="A90" s="3" t="s">
         <v>346</v>
       </c>
@@ -11719,7 +12322,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="22.05" customHeight="1" spans="1:4">
       <c r="A91" s="2" t="s">
         <v>355</v>
       </c>
@@ -11733,7 +12336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="22.05" customHeight="1" spans="1:4">
       <c r="A92" s="3" t="s">
         <v>357</v>
       </c>
@@ -11747,7 +12350,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="22.05" customHeight="1" spans="1:4">
       <c r="A93" s="2" t="s">
         <v>360</v>
       </c>
@@ -11761,7 +12364,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="22.05" customHeight="1" spans="1:4">
       <c r="A94" s="3" t="s">
         <v>362</v>
       </c>
@@ -11775,7 +12378,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="22.05" customHeight="1" spans="1:4">
       <c r="A95" s="2" t="s">
         <v>584</v>
       </c>
@@ -11789,7 +12392,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="22.05" customHeight="1" spans="1:4">
       <c r="A96" s="3" t="s">
         <v>601</v>
       </c>
@@ -11803,7 +12406,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="22.05" customHeight="1" spans="1:4">
       <c r="A97" s="2" t="s">
         <v>602</v>
       </c>
@@ -11817,7 +12420,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="22.05" customHeight="1" spans="1:4">
       <c r="A98" s="3" t="s">
         <v>603</v>
       </c>
@@ -11831,7 +12434,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="22.05" customHeight="1" spans="1:4">
       <c r="A99" s="2" t="s">
         <v>632</v>
       </c>
@@ -11845,7 +12448,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="22.05" customHeight="1" spans="1:4">
       <c r="A100" s="3" t="s">
         <v>633</v>
       </c>
@@ -11859,7 +12462,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="22.05" customHeight="1" spans="1:4">
       <c r="A101" s="2" t="s">
         <v>712</v>
       </c>
@@ -11873,100 +12476,101 @@
         <v>315</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:4">
+      <c r="A102" s="10" t="s">
         <v>791</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="11">
         <v>155</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="11">
         <v>155</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" s="10" t="s">
         <v>792</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="11">
         <v>155</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="11">
         <v>155</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" s="10" t="s">
         <v>793</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="11">
         <v>155</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="11">
         <v>155</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="13" t="s">
+        <v>795</v>
+      </c>
+      <c r="C105" s="14">
+        <v>250</v>
+      </c>
+      <c r="D105" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="15" t="s">
         <v>796</v>
       </c>
-      <c r="C105" s="13">
-        <v>250</v>
-      </c>
-      <c r="D105" s="13">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="14" t="s">
+      <c r="B106" s="13" t="s">
+        <v>795</v>
+      </c>
+      <c r="C106" s="14">
+        <v>260</v>
+      </c>
+      <c r="D106" s="14">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="15" t="s">
         <v>797</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>796</v>
-      </c>
-      <c r="C106" s="13">
-        <v>260</v>
-      </c>
-      <c r="D106" s="13">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D108" s="9"/>
+    </row>
+    <row r="108" spans="4:4">
+      <c r="D108" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11980,7 +12584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -11994,7 +12598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>241</v>
       </c>
@@ -12008,7 +12612,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>244</v>
       </c>
@@ -12022,7 +12626,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>247</v>
       </c>
@@ -12036,7 +12640,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>249</v>
       </c>
@@ -12050,7 +12654,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>251</v>
       </c>
@@ -12064,7 +12668,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>254</v>
       </c>
@@ -12078,7 +12682,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>257</v>
       </c>
@@ -12092,7 +12696,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>259</v>
       </c>
@@ -12106,7 +12710,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>262</v>
       </c>
@@ -12120,7 +12724,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>265</v>
       </c>
@@ -12134,7 +12738,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>269</v>
       </c>
@@ -12148,7 +12752,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>319</v>
       </c>
@@ -12162,7 +12766,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>320</v>
       </c>
@@ -12176,7 +12780,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>607</v>
       </c>
@@ -12190,12 +12794,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>799</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>800</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12204,9 +12808,9 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>795</v>
@@ -12218,9 +12822,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>795</v>
@@ -12232,12 +12836,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A20" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>803</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>804</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12246,22 +12850,48 @@
         <v>2300</v>
       </c>
     </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>804</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>1000</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>805</v>
+      </c>
+      <c r="C22">
+        <v>1060</v>
+      </c>
+      <c r="D22">
+        <v>1060</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12275,7 +12905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
@@ -12289,7 +12919,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
@@ -12303,7 +12933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -12317,7 +12947,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
@@ -12331,7 +12961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
@@ -12345,7 +12975,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
@@ -12359,7 +12989,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
@@ -12373,7 +13003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
@@ -12387,7 +13017,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>65</v>
       </c>
@@ -12401,7 +13031,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -12415,7 +13045,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>76</v>
       </c>
@@ -12429,7 +13059,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>94</v>
       </c>
@@ -12443,7 +13073,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -12457,7 +13087,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
@@ -12471,7 +13101,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>107</v>
       </c>
@@ -12485,7 +13115,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>109</v>
       </c>
@@ -12499,7 +13129,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>131</v>
       </c>
@@ -12513,7 +13143,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>146</v>
       </c>
@@ -12527,7 +13157,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
         <v>148</v>
       </c>
@@ -12541,7 +13171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>149</v>
       </c>
@@ -12555,7 +13185,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>155</v>
       </c>
@@ -12569,7 +13199,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>157</v>
       </c>
@@ -12583,7 +13213,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="2" t="s">
         <v>168</v>
       </c>
@@ -12597,7 +13227,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>169</v>
       </c>
@@ -12611,7 +13241,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="2" t="s">
         <v>298</v>
       </c>
@@ -12625,7 +13255,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>347</v>
       </c>
@@ -12639,7 +13269,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>350</v>
       </c>
@@ -12653,7 +13283,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>351</v>
       </c>
@@ -12667,7 +13297,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="2" t="s">
         <v>352</v>
       </c>
@@ -12681,7 +13311,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>353</v>
       </c>
@@ -12695,7 +13325,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="2" t="s">
         <v>370</v>
       </c>
@@ -12709,7 +13339,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>373</v>
       </c>
@@ -12723,7 +13353,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="2" t="s">
         <v>391</v>
       </c>
@@ -12737,7 +13367,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>393</v>
       </c>
@@ -12751,7 +13381,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="2" t="s">
         <v>396</v>
       </c>
@@ -12765,7 +13395,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
       <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
@@ -12779,7 +13409,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
       <c r="A38" s="2" t="s">
         <v>398</v>
       </c>
@@ -12793,7 +13423,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
       <c r="A39" s="3" t="s">
         <v>399</v>
       </c>
@@ -12807,7 +13437,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
       <c r="A40" s="2" t="s">
         <v>401</v>
       </c>
@@ -12821,7 +13451,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
       <c r="A41" s="3" t="s">
         <v>402</v>
       </c>
@@ -12835,7 +13465,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
       <c r="A42" s="2" t="s">
         <v>403</v>
       </c>
@@ -12849,7 +13479,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
       <c r="A43" s="3" t="s">
         <v>405</v>
       </c>
@@ -12863,7 +13493,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
       <c r="A44" s="2" t="s">
         <v>406</v>
       </c>
@@ -12877,7 +13507,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
       <c r="A45" s="3" t="s">
         <v>407</v>
       </c>
@@ -12891,7 +13521,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
       <c r="A46" s="2" t="s">
         <v>408</v>
       </c>
@@ -12905,7 +13535,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
       <c r="A47" s="3" t="s">
         <v>409</v>
       </c>
@@ -12919,7 +13549,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
       <c r="A48" s="2" t="s">
         <v>410</v>
       </c>
@@ -12933,7 +13563,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
       <c r="A49" s="3" t="s">
         <v>411</v>
       </c>
@@ -12947,7 +13577,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
       <c r="A50" s="2" t="s">
         <v>413</v>
       </c>
@@ -12961,7 +13591,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
       <c r="A51" s="3" t="s">
         <v>416</v>
       </c>
@@ -12975,7 +13605,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
       <c r="A52" s="2" t="s">
         <v>417</v>
       </c>
@@ -12989,7 +13619,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
       <c r="A53" s="3" t="s">
         <v>418</v>
       </c>
@@ -13003,7 +13633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
       <c r="A54" s="2" t="s">
         <v>419</v>
       </c>
@@ -13017,7 +13647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
       <c r="A55" s="3" t="s">
         <v>425</v>
       </c>
@@ -13031,7 +13661,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
       <c r="A56" s="2" t="s">
         <v>427</v>
       </c>
@@ -13045,7 +13675,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
       <c r="A57" s="3" t="s">
         <v>428</v>
       </c>
@@ -13059,7 +13689,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
       <c r="A58" s="2" t="s">
         <v>431</v>
       </c>
@@ -13073,7 +13703,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
       <c r="A59" s="3" t="s">
         <v>432</v>
       </c>
@@ -13087,7 +13717,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
       <c r="A60" s="2" t="s">
         <v>434</v>
       </c>
@@ -13101,7 +13731,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
       <c r="A61" s="3" t="s">
         <v>439</v>
       </c>
@@ -13115,7 +13745,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
       <c r="A62" s="2" t="s">
         <v>441</v>
       </c>
@@ -13129,7 +13759,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
       <c r="A63" s="3" t="s">
         <v>444</v>
       </c>
@@ -13143,7 +13773,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
       <c r="A64" s="2" t="s">
         <v>446</v>
       </c>
@@ -13157,7 +13787,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="22.05" customHeight="1" spans="1:4">
       <c r="A65" s="3" t="s">
         <v>447</v>
       </c>
@@ -13171,7 +13801,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="22.05" customHeight="1" spans="1:4">
       <c r="A66" s="2" t="s">
         <v>448</v>
       </c>
@@ -13185,7 +13815,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="22.05" customHeight="1" spans="1:4">
       <c r="A67" s="3" t="s">
         <v>449</v>
       </c>
@@ -13199,7 +13829,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="22.05" customHeight="1" spans="1:4">
       <c r="A68" s="2" t="s">
         <v>450</v>
       </c>
@@ -13213,7 +13843,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="22.05" customHeight="1" spans="1:4">
       <c r="A69" s="3" t="s">
         <v>452</v>
       </c>
@@ -13227,7 +13857,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="22.05" customHeight="1" spans="1:4">
       <c r="A70" s="2" t="s">
         <v>453</v>
       </c>
@@ -13241,7 +13871,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="22.05" customHeight="1" spans="1:4">
       <c r="A71" s="3" t="s">
         <v>455</v>
       </c>
@@ -13255,7 +13885,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="22.05" customHeight="1" spans="1:4">
       <c r="A72" s="2" t="s">
         <v>456</v>
       </c>
@@ -13269,7 +13899,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="22.05" customHeight="1" spans="1:4">
       <c r="A73" s="3" t="s">
         <v>460</v>
       </c>
@@ -13283,7 +13913,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="22.05" customHeight="1" spans="1:4">
       <c r="A74" s="2" t="s">
         <v>462</v>
       </c>
@@ -13297,7 +13927,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="22.05" customHeight="1" spans="1:4">
       <c r="A75" s="3" t="s">
         <v>465</v>
       </c>
@@ -13311,7 +13941,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="22.05" customHeight="1" spans="1:4">
       <c r="A76" s="2" t="s">
         <v>467</v>
       </c>
@@ -13325,7 +13955,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="22.05" customHeight="1" spans="1:4">
       <c r="A77" s="3" t="s">
         <v>470</v>
       </c>
@@ -13339,7 +13969,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="22.05" customHeight="1" spans="1:4">
       <c r="A78" s="2" t="s">
         <v>472</v>
       </c>
@@ -13353,7 +13983,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="22.05" customHeight="1" spans="1:4">
       <c r="A79" s="3" t="s">
         <v>475</v>
       </c>
@@ -13367,7 +13997,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="22.05" customHeight="1" spans="1:4">
       <c r="A80" s="2" t="s">
         <v>477</v>
       </c>
@@ -13381,7 +14011,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="22.05" customHeight="1" spans="1:4">
       <c r="A81" s="3" t="s">
         <v>479</v>
       </c>
@@ -13395,7 +14025,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="22.05" customHeight="1" spans="1:4">
       <c r="A82" s="2" t="s">
         <v>480</v>
       </c>
@@ -13409,7 +14039,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="22.05" customHeight="1" spans="1:4">
       <c r="A83" s="3" t="s">
         <v>481</v>
       </c>
@@ -13423,7 +14053,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="22.05" customHeight="1" spans="1:4">
       <c r="A84" s="2" t="s">
         <v>482</v>
       </c>
@@ -13437,7 +14067,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="22.05" customHeight="1" spans="1:4">
       <c r="A85" s="3" t="s">
         <v>483</v>
       </c>
@@ -13451,7 +14081,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="22.05" customHeight="1" spans="1:4">
       <c r="A86" s="2" t="s">
         <v>484</v>
       </c>
@@ -13465,7 +14095,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="22.05" customHeight="1" spans="1:4">
       <c r="A87" s="3" t="s">
         <v>485</v>
       </c>
@@ -13479,7 +14109,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="22.05" customHeight="1" spans="1:4">
       <c r="A88" s="2" t="s">
         <v>487</v>
       </c>
@@ -13493,7 +14123,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="22.05" customHeight="1" spans="1:4">
       <c r="A89" s="3" t="s">
         <v>488</v>
       </c>
@@ -13507,7 +14137,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="22.05" customHeight="1" spans="1:4">
       <c r="A90" s="2" t="s">
         <v>489</v>
       </c>
@@ -13521,7 +14151,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="22.05" customHeight="1" spans="1:4">
       <c r="A91" s="3" t="s">
         <v>491</v>
       </c>
@@ -13535,7 +14165,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="22.05" customHeight="1" spans="1:4">
       <c r="A92" s="2" t="s">
         <v>494</v>
       </c>
@@ -13549,7 +14179,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="22.05" customHeight="1" spans="1:4">
       <c r="A93" s="3" t="s">
         <v>495</v>
       </c>
@@ -13563,7 +14193,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="22.05" customHeight="1" spans="1:4">
       <c r="A94" s="2" t="s">
         <v>496</v>
       </c>
@@ -13577,7 +14207,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="22.05" customHeight="1" spans="1:4">
       <c r="A95" s="3" t="s">
         <v>502</v>
       </c>
@@ -13591,7 +14221,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="22.05" customHeight="1" spans="1:4">
       <c r="A96" s="2" t="s">
         <v>505</v>
       </c>
@@ -13605,7 +14235,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="22.05" customHeight="1" spans="1:4">
       <c r="A97" s="3" t="s">
         <v>506</v>
       </c>
@@ -13619,7 +14249,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="22.05" customHeight="1" spans="1:4">
       <c r="A98" s="2" t="s">
         <v>507</v>
       </c>
@@ -13633,7 +14263,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="22.05" customHeight="1" spans="1:4">
       <c r="A99" s="3" t="s">
         <v>508</v>
       </c>
@@ -13647,7 +14277,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="22.05" customHeight="1" spans="1:4">
       <c r="A100" s="2" t="s">
         <v>509</v>
       </c>
@@ -13661,7 +14291,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="22.05" customHeight="1" spans="1:4">
       <c r="A101" s="3" t="s">
         <v>512</v>
       </c>
@@ -13675,7 +14305,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="22.05" customHeight="1" spans="1:4">
       <c r="A102" s="2" t="s">
         <v>514</v>
       </c>
@@ -13689,7 +14319,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="3" t="s">
         <v>516</v>
       </c>
@@ -13703,7 +14333,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="22.05" customHeight="1" spans="1:4">
       <c r="A104" s="2" t="s">
         <v>517</v>
       </c>
@@ -13717,7 +14347,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="22.05" customHeight="1" spans="1:4">
       <c r="A105" s="3" t="s">
         <v>518</v>
       </c>
@@ -13731,7 +14361,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="22.05" customHeight="1" spans="1:4">
       <c r="A106" s="2" t="s">
         <v>519</v>
       </c>
@@ -13745,7 +14375,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="22.05" customHeight="1" spans="1:4">
       <c r="A107" s="3" t="s">
         <v>520</v>
       </c>
@@ -13759,7 +14389,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="22.05" customHeight="1" spans="1:4">
       <c r="A108" s="2" t="s">
         <v>522</v>
       </c>
@@ -13773,7 +14403,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="22.05" customHeight="1" spans="1:4">
       <c r="A109" s="3" t="s">
         <v>524</v>
       </c>
@@ -13787,7 +14417,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="22.05" customHeight="1" spans="1:4">
       <c r="A110" s="2" t="s">
         <v>526</v>
       </c>
@@ -13801,7 +14431,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="22.05" customHeight="1" spans="1:4">
       <c r="A111" s="3" t="s">
         <v>529</v>
       </c>
@@ -13815,7 +14445,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="22.05" customHeight="1" spans="1:4">
       <c r="A112" s="2" t="s">
         <v>531</v>
       </c>
@@ -13829,7 +14459,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="22.05" customHeight="1" spans="1:4">
       <c r="A113" s="3" t="s">
         <v>533</v>
       </c>
@@ -13843,7 +14473,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="22.05" customHeight="1" spans="1:4">
       <c r="A114" s="2" t="s">
         <v>534</v>
       </c>
@@ -13857,7 +14487,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="22.05" customHeight="1" spans="1:4">
       <c r="A115" s="3" t="s">
         <v>536</v>
       </c>
@@ -13871,7 +14501,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="22.05" customHeight="1" spans="1:4">
       <c r="A116" s="2" t="s">
         <v>537</v>
       </c>
@@ -13885,7 +14515,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="22.05" customHeight="1" spans="1:4">
       <c r="A117" s="3" t="s">
         <v>539</v>
       </c>
@@ -13899,7 +14529,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="22.05" customHeight="1" spans="1:4">
       <c r="A118" s="2" t="s">
         <v>541</v>
       </c>
@@ -13913,7 +14543,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="22.05" customHeight="1" spans="1:4">
       <c r="A119" s="3" t="s">
         <v>544</v>
       </c>
@@ -13927,7 +14557,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="22.05" customHeight="1" spans="1:4">
       <c r="A120" s="2" t="s">
         <v>547</v>
       </c>
@@ -13941,7 +14571,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="22.05" customHeight="1" spans="1:4">
       <c r="A121" s="3" t="s">
         <v>548</v>
       </c>
@@ -13955,7 +14585,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="22.05" customHeight="1" spans="1:4">
       <c r="A122" s="2" t="s">
         <v>550</v>
       </c>
@@ -13969,7 +14599,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="22.05" customHeight="1" spans="1:4">
       <c r="A123" s="3" t="s">
         <v>552</v>
       </c>
@@ -13983,7 +14613,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="22.05" customHeight="1" spans="1:4">
       <c r="A124" s="2" t="s">
         <v>555</v>
       </c>
@@ -13993,11 +14623,11 @@
       <c r="C124" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="6" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="22.05" customHeight="1" spans="1:4">
       <c r="A125" s="3" t="s">
         <v>558</v>
       </c>
@@ -14011,7 +14641,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="22.05" customHeight="1" spans="1:4">
       <c r="A126" s="2" t="s">
         <v>560</v>
       </c>
@@ -14025,7 +14655,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="22.05" customHeight="1" spans="1:4">
       <c r="A127" s="3" t="s">
         <v>561</v>
       </c>
@@ -14039,7 +14669,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="22.05" customHeight="1" spans="1:4">
       <c r="A128" s="2" t="s">
         <v>562</v>
       </c>
@@ -14053,7 +14683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="22.05" customHeight="1" spans="1:4">
       <c r="A129" s="3" t="s">
         <v>568</v>
       </c>
@@ -14067,7 +14697,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="22.05" customHeight="1" spans="1:4">
       <c r="A130" s="2" t="s">
         <v>571</v>
       </c>
@@ -14081,7 +14711,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="22.05" customHeight="1" spans="1:4">
       <c r="A131" s="3" t="s">
         <v>572</v>
       </c>
@@ -14095,7 +14725,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="22.05" customHeight="1" spans="1:4">
       <c r="A132" s="2" t="s">
         <v>573</v>
       </c>
@@ -14109,7 +14739,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="22.05" customHeight="1" spans="1:4">
       <c r="A133" s="3" t="s">
         <v>574</v>
       </c>
@@ -14123,7 +14753,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="22.05" customHeight="1" spans="1:4">
       <c r="A134" s="2" t="s">
         <v>575</v>
       </c>
@@ -14137,7 +14767,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="22.05" customHeight="1" spans="1:4">
       <c r="A135" s="3" t="s">
         <v>577</v>
       </c>
@@ -14151,7 +14781,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="22.05" customHeight="1" spans="1:4">
       <c r="A136" s="2" t="s">
         <v>578</v>
       </c>
@@ -14165,7 +14795,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="22.05" customHeight="1" spans="1:4">
       <c r="A137" s="3" t="s">
         <v>580</v>
       </c>
@@ -14179,7 +14809,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="22.05" customHeight="1" spans="1:4">
       <c r="A138" s="2" t="s">
         <v>583</v>
       </c>
@@ -14193,7 +14823,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="22.05" customHeight="1" spans="1:4">
       <c r="A139" s="3" t="s">
         <v>586</v>
       </c>
@@ -14207,7 +14837,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="22.05" customHeight="1" spans="1:4">
       <c r="A140" s="2" t="s">
         <v>608</v>
       </c>
@@ -14221,7 +14851,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="22.05" customHeight="1" spans="1:4">
       <c r="A141" s="3" t="s">
         <v>610</v>
       </c>
@@ -14235,7 +14865,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="22.05" customHeight="1" spans="1:4">
       <c r="A142" s="2" t="s">
         <v>611</v>
       </c>
@@ -14249,7 +14879,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="22.05" customHeight="1" spans="1:4">
       <c r="A143" s="3" t="s">
         <v>613</v>
       </c>
@@ -14263,7 +14893,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="22.05" customHeight="1" spans="1:4">
       <c r="A144" s="2" t="s">
         <v>614</v>
       </c>
@@ -14277,7 +14907,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="22.05" customHeight="1" spans="1:4">
       <c r="A145" s="3" t="s">
         <v>616</v>
       </c>
@@ -14291,7 +14921,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="22.05" customHeight="1" spans="1:4">
       <c r="A146" s="2" t="s">
         <v>617</v>
       </c>
@@ -14305,7 +14935,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="22.05" customHeight="1" spans="1:4">
       <c r="A147" s="3" t="s">
         <v>642</v>
       </c>
@@ -14319,7 +14949,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="22.05" customHeight="1" spans="1:4">
       <c r="A148" s="2" t="s">
         <v>662</v>
       </c>
@@ -14333,7 +14963,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="22.05" customHeight="1" spans="1:4">
       <c r="A149" s="3" t="s">
         <v>666</v>
       </c>
@@ -14347,7 +14977,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="22.05" customHeight="1" spans="1:4">
       <c r="A150" s="2" t="s">
         <v>686</v>
       </c>
@@ -14361,7 +14991,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="22.05" customHeight="1" spans="1:4">
       <c r="A151" s="3" t="s">
         <v>688</v>
       </c>
@@ -14375,7 +15005,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="22.05" customHeight="1" spans="1:4">
       <c r="A152" s="2" t="s">
         <v>695</v>
       </c>
@@ -14389,7 +15019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="22.05" customHeight="1" spans="1:4">
       <c r="A153" s="3" t="s">
         <v>696</v>
       </c>
@@ -14403,7 +15033,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="22.05" customHeight="1" spans="1:4">
       <c r="A154" s="2" t="s">
         <v>697</v>
       </c>
@@ -14417,7 +15047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="22.05" customHeight="1" spans="1:4">
       <c r="A155" s="3" t="s">
         <v>698</v>
       </c>
@@ -14431,7 +15061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="22.05" customHeight="1" spans="1:4">
       <c r="A156" s="2" t="s">
         <v>699</v>
       </c>
@@ -14445,7 +15075,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="22.05" customHeight="1" spans="1:4">
       <c r="A157" s="3" t="s">
         <v>701</v>
       </c>
@@ -14459,7 +15089,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="22.05" customHeight="1" spans="1:4">
       <c r="A158" s="2" t="s">
         <v>705</v>
       </c>
@@ -14473,7 +15103,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="22.05" customHeight="1" spans="1:4">
       <c r="A159" s="3" t="s">
         <v>706</v>
       </c>
@@ -14487,7 +15117,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="22.05" customHeight="1" spans="1:4">
       <c r="A160" s="2" t="s">
         <v>707</v>
       </c>
@@ -14501,7 +15131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="22.05" customHeight="1" spans="1:4">
       <c r="A161" s="3" t="s">
         <v>708</v>
       </c>
@@ -14515,7 +15145,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="22.05" customHeight="1" spans="1:4">
       <c r="A162" s="2" t="s">
         <v>709</v>
       </c>
@@ -14529,7 +15159,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="22.05" customHeight="1" spans="1:4">
       <c r="A163" s="3" t="s">
         <v>711</v>
       </c>
@@ -14543,7 +15173,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="22.05" customHeight="1" spans="1:4">
       <c r="A164" s="2" t="s">
         <v>713</v>
       </c>
@@ -14557,7 +15187,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="22.05" customHeight="1" spans="1:4">
       <c r="A165" s="3" t="s">
         <v>724</v>
       </c>
@@ -14571,7 +15201,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="22.05" customHeight="1" spans="1:4">
       <c r="A166" s="2" t="s">
         <v>725</v>
       </c>
@@ -14585,7 +15215,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="22.05" customHeight="1" spans="1:4">
       <c r="A167" s="3" t="s">
         <v>731</v>
       </c>
@@ -14600,21 +15230,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14628,7 +15259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
@@ -14643,21 +15274,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14671,7 +15303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>111</v>
       </c>
@@ -14685,7 +15317,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>111</v>
       </c>
@@ -14699,7 +15331,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>213</v>
       </c>
@@ -14713,7 +15345,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>216</v>
       </c>
@@ -14727,7 +15359,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>218</v>
       </c>
@@ -14741,7 +15373,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>220</v>
       </c>
@@ -14755,7 +15387,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>223</v>
       </c>
@@ -14769,7 +15401,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>226</v>
       </c>
@@ -14783,7 +15415,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>229</v>
       </c>
@@ -14797,7 +15429,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>232</v>
       </c>
@@ -14811,7 +15443,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>233</v>
       </c>
@@ -14825,7 +15457,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>233</v>
       </c>
@@ -14839,7 +15471,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>233</v>
       </c>
@@ -14853,7 +15485,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>239</v>
       </c>
@@ -14867,7 +15499,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>291</v>
       </c>
@@ -14881,7 +15513,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>294</v>
       </c>
@@ -14895,7 +15527,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>323</v>
       </c>
@@ -14909,7 +15541,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>327</v>
       </c>
@@ -14923,7 +15555,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
         <v>378</v>
       </c>
@@ -14937,7 +15569,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>380</v>
       </c>
@@ -14951,7 +15583,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>383</v>
       </c>
@@ -14965,7 +15597,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>386</v>
       </c>
@@ -14979,7 +15611,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="2" t="s">
         <v>387</v>
       </c>
@@ -14993,7 +15625,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>389</v>
       </c>
@@ -15007,7 +15639,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="2" t="s">
         <v>499</v>
       </c>
@@ -15021,7 +15653,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>576</v>
       </c>
@@ -15035,7 +15667,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>592</v>
       </c>
@@ -15049,7 +15681,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>594</v>
       </c>
@@ -15063,7 +15695,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="2" t="s">
         <v>620</v>
       </c>
@@ -15077,7 +15709,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>620</v>
       </c>
@@ -15091,7 +15723,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="2" t="s">
         <v>624</v>
       </c>
@@ -15105,7 +15737,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>625</v>
       </c>
@@ -15119,7 +15751,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="2" t="s">
         <v>636</v>
       </c>
@@ -15133,7 +15765,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>638</v>
       </c>
@@ -15147,7 +15779,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="2" t="s">
         <v>639</v>
       </c>
@@ -15162,21 +15794,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15190,7 +15823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -15204,7 +15837,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>125</v>
       </c>
@@ -15218,7 +15851,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>174</v>
       </c>
@@ -15232,7 +15865,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>177</v>
       </c>
@@ -15246,7 +15879,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>179</v>
       </c>
@@ -15260,7 +15893,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>182</v>
       </c>
@@ -15274,7 +15907,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>185</v>
       </c>
@@ -15288,7 +15921,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>187</v>
       </c>
@@ -15302,7 +15935,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.05" customHeight="1" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>189</v>
       </c>
@@ -15312,11 +15945,11 @@
       <c r="C10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="22.05" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>192</v>
       </c>
@@ -15330,7 +15963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>193</v>
       </c>
@@ -15344,7 +15977,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>196</v>
       </c>
@@ -15358,7 +15991,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>199</v>
       </c>
@@ -15372,7 +16005,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>301</v>
       </c>
@@ -15386,7 +16019,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>307</v>
       </c>
@@ -15400,7 +16033,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>316</v>
       </c>
@@ -15414,7 +16047,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>317</v>
       </c>
@@ -15428,7 +16061,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>321</v>
       </c>
@@ -15442,7 +16075,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
         <v>330</v>
       </c>
@@ -15456,7 +16089,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>332</v>
       </c>
@@ -15470,7 +16103,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>334</v>
       </c>
@@ -15484,7 +16117,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>337</v>
       </c>
@@ -15498,7 +16131,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="2" t="s">
         <v>337</v>
       </c>
@@ -15512,7 +16145,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>340</v>
       </c>
@@ -15526,7 +16159,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="2" t="s">
         <v>341</v>
       </c>
@@ -15540,7 +16173,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>363</v>
       </c>
@@ -15554,7 +16187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>364</v>
       </c>
@@ -15568,7 +16201,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>366</v>
       </c>
@@ -15582,7 +16215,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="2" t="s">
         <v>368</v>
       </c>
@@ -15596,7 +16229,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>375</v>
       </c>
@@ -15610,7 +16243,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="2" t="s">
         <v>394</v>
       </c>
@@ -15624,7 +16257,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>458</v>
       </c>
@@ -15638,7 +16271,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="2" t="s">
         <v>492</v>
       </c>
@@ -15652,7 +16285,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>564</v>
       </c>
@@ -15666,7 +16299,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="2" t="s">
         <v>565</v>
       </c>
@@ -15680,7 +16313,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
       <c r="A37" s="3" t="s">
         <v>567</v>
       </c>
@@ -15694,7 +16327,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
       <c r="A38" s="2" t="s">
         <v>599</v>
       </c>
@@ -15708,7 +16341,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
       <c r="A39" s="3" t="s">
         <v>604</v>
       </c>
@@ -15722,7 +16355,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
       <c r="A40" s="2" t="s">
         <v>606</v>
       </c>
@@ -15736,7 +16369,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
       <c r="A41" s="3" t="s">
         <v>618</v>
       </c>
@@ -15750,7 +16383,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
       <c r="A42" s="2" t="s">
         <v>619</v>
       </c>
@@ -15764,7 +16397,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
       <c r="A43" s="3" t="s">
         <v>643</v>
       </c>
@@ -15778,7 +16411,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
       <c r="A44" s="2" t="s">
         <v>645</v>
       </c>
@@ -15792,7 +16425,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
       <c r="A45" s="3" t="s">
         <v>677</v>
       </c>
@@ -15806,7 +16439,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
       <c r="A46" s="2" t="s">
         <v>678</v>
       </c>
@@ -15820,7 +16453,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
       <c r="A47" s="3" t="s">
         <v>680</v>
       </c>
@@ -15834,7 +16467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
       <c r="A48" s="2" t="s">
         <v>681</v>
       </c>
@@ -15848,7 +16481,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
       <c r="A49" s="3" t="s">
         <v>682</v>
       </c>
@@ -15862,7 +16495,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
       <c r="A50" s="2" t="s">
         <v>683</v>
       </c>
@@ -15876,7 +16509,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
       <c r="A51" s="3" t="s">
         <v>689</v>
       </c>
@@ -15890,7 +16523,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
       <c r="A52" s="2" t="s">
         <v>690</v>
       </c>
@@ -15904,7 +16537,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
       <c r="A53" s="3" t="s">
         <v>693</v>
       </c>
@@ -15918,7 +16551,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
       <c r="A54" s="2" t="s">
         <v>714</v>
       </c>
@@ -15932,7 +16565,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
       <c r="A55" s="3" t="s">
         <v>718</v>
       </c>
@@ -15946,7 +16579,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
       <c r="A56" s="2" t="s">
         <v>720</v>
       </c>
@@ -15960,7 +16593,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
       <c r="A57" s="3" t="s">
         <v>722</v>
       </c>
@@ -15974,7 +16607,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
       <c r="A58" s="2" t="s">
         <v>723</v>
       </c>
@@ -15988,7 +16621,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
       <c r="A59" s="3" t="s">
         <v>727</v>
       </c>
@@ -16002,7 +16635,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
       <c r="A60" s="2" t="s">
         <v>729</v>
       </c>
@@ -16016,7 +16649,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
       <c r="A61" s="3" t="s">
         <v>730</v>
       </c>
@@ -16031,21 +16664,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16059,7 +16693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -16073,7 +16707,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>285</v>
       </c>
@@ -16088,21 +16722,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16116,7 +16751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>205</v>
       </c>
@@ -16130,7 +16765,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>207</v>
       </c>
@@ -16144,7 +16779,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>209</v>
       </c>
@@ -16158,7 +16793,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>211</v>
       </c>
@@ -16172,7 +16807,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>600</v>
       </c>
@@ -16186,7 +16821,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>631</v>
       </c>
@@ -16200,7 +16835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>733</v>
       </c>
@@ -16215,7 +16850,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="811">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2458,7 +2458,10 @@
     <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
   </si>
   <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版含麻深蓝）</t>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
+  </si>
+  <si>
+    <t>1.5ml/支/盒 含麻</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -10439,10 +10442,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10453,10 +10456,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -12567,7 +12570,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
@@ -12864,9 +12868,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" ht="28.8" spans="1:4">
       <c r="A22" t="s">
         <v>805</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>806</v>
       </c>
       <c r="C22">
         <v>1060</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="2"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="810">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2432,9 +2432,6 @@
   </si>
   <si>
     <t>姣兰 / Lips 唇部玻尿酸</t>
-  </si>
-  <si>
-    <t>乔雅登天使针</t>
   </si>
   <si>
     <t>冰月岚 / 面部童颜针</t>
@@ -2487,7 +2484,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2499,13 +2496,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2539,12 +2529,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9.5"/>
@@ -3053,137 +3037,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3194,44 +3178,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3680,10 +3655,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>1850</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>1850</v>
       </c>
     </row>
@@ -5083,7 +5058,7 @@
       <c r="C114" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="14" t="s">
         <v>191</v>
       </c>
     </row>
@@ -7813,7 +7788,7 @@
       <c r="C309" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D309" s="6" t="s">
+      <c r="D309" s="5" t="s">
         <v>557</v>
       </c>
     </row>
@@ -10441,11 +10416,11 @@
       </c>
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>808</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10455,11 +10430,11 @@
       </c>
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>809</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>810</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -11254,10 +11229,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>1850</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>1850</v>
       </c>
     </row>
@@ -12480,82 +12455,80 @@
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="8" t="s">
         <v>791</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="11">
-        <v>155</v>
-      </c>
-      <c r="D102" s="11">
-        <v>155</v>
+      <c r="C102" s="9">
+        <v>165</v>
+      </c>
+      <c r="D102" s="9">
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="8" t="s">
         <v>792</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="11">
-        <v>155</v>
-      </c>
-      <c r="D103" s="11">
-        <v>155</v>
+      <c r="C103" s="9">
+        <v>165</v>
+      </c>
+      <c r="D103" s="9">
+        <v>165</v>
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="8" t="s">
         <v>793</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C104" s="11">
-        <v>155</v>
-      </c>
-      <c r="D104" s="11">
-        <v>155</v>
+      <c r="C104" s="9">
+        <v>165</v>
+      </c>
+      <c r="D104" s="9">
+        <v>165</v>
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="C105" s="14">
+      <c r="C105" s="11">
         <v>250</v>
       </c>
-      <c r="D105" s="14">
+      <c r="D105" s="11">
         <v>250</v>
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="12" t="s">
         <v>796</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="C106" s="14">
+      <c r="C106" s="11">
         <v>260</v>
       </c>
-      <c r="D106" s="14">
+      <c r="D106" s="11">
         <v>260</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="15" t="s">
-        <v>797</v>
-      </c>
+      <c r="A107" s="12"/>
     </row>
     <row r="108" spans="4:4">
-      <c r="D108" s="16"/>
+      <c r="D108" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12800,10 +12773,10 @@
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>799</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12814,7 +12787,7 @@
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>795</v>
@@ -12828,7 +12801,7 @@
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>795</v>
@@ -12841,11 +12814,11 @@
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>803</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12856,7 +12829,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>33</v>
@@ -12868,12 +12841,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:4">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
+        <v>804</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="C22">
         <v>1060</v>
@@ -14630,7 +14603,7 @@
       <c r="C124" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="5" t="s">
         <v>557</v>
       </c>
     </row>
@@ -15952,7 +15925,7 @@
       <c r="C10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>191</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="814">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2410,12 +2410,24 @@
     <t>乔雅登（法国本土版）/4号</t>
   </si>
   <si>
-    <t>乔雅登（法国本土版）/5号</t>
+    <t>乔雅登（法国本土版）/5号 丰颜</t>
   </si>
   <si>
     <t>¥1,600</t>
   </si>
   <si>
+    <t>乔雅登（法国本土版）/6号 朔颜</t>
+  </si>
+  <si>
+    <t>乔雅登（韩版）/5号 丰颜</t>
+  </si>
+  <si>
+    <t>乔雅登（韩版）/6号 朔颜</t>
+  </si>
+  <si>
+    <t>乔雅登（韩版）/8号 质颜</t>
+  </si>
+  <si>
     <t>艾莉薇大分子玻尿酸/韩版</t>
   </si>
   <si>
@@ -2434,6 +2446,9 @@
     <t>姣兰 / Lips 唇部玻尿酸</t>
   </si>
   <si>
+    <t>乔雅登天使针</t>
+  </si>
+  <si>
     <t>冰月岚 / 面部童颜针</t>
   </si>
   <si>
@@ -2455,10 +2470,7 @@
     <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
   </si>
   <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
-  </si>
-  <si>
-    <t>1.5ml/支/盒 含麻</t>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版含麻深蓝）</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -10417,10 +10429,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10431,10 +10443,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -11033,10 +11045,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11224,7 +11236,7 @@
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>791</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
@@ -11237,1298 +11249,1342 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
+      <c r="A15" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1550</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1550</v>
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
-        <v>12</v>
+      <c r="A16" s="2" t="s">
+        <v>793</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1800</v>
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1240</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="3" t="s">
+    <row r="21" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="2" t="s">
+    <row r="22" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="3" t="s">
+    <row r="23" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="2" t="s">
+    <row r="24" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="3" t="s">
+    <row r="25" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="2" t="s">
+    <row r="26" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="3" t="s">
+    <row r="27" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="2" t="s">
+    <row r="28" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="3" t="s">
+    <row r="29" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="2" t="s">
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="3" t="s">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="2" t="s">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A32" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="3" t="s">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="2" t="s">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="3" t="s">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="2" t="s">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="3" t="s">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="2" t="s">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="3" t="s">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A37" s="2" t="s">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A40" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A38" s="3" t="s">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A41" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A39" s="2" t="s">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A42" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A40" s="3" t="s">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A43" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="41" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A41" s="2" t="s">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A44" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A42" s="3" t="s">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A45" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A43" s="2" t="s">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="44" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A44" s="3" t="s">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A47" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A45" s="2" t="s">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A48" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A46" s="3" t="s">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="B49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A47" s="2" t="s">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A50" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A48" s="3" t="s">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A51" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="49" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A49" s="2" t="s">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A52" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A50" s="3" t="s">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A53" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="51" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A51" s="2" t="s">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A54" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="52" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A52" s="3" t="s">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A55" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="B55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A53" s="2" t="s">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A56" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="B56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="54" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A54" s="3" t="s">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A57" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="55" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A55" s="2" t="s">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A58" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="56" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A56" s="3" t="s">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A59" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B59" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A57" s="2" t="s">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A60" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A58" s="3" t="s">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A61" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="B61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="59" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A59" s="2" t="s">
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="60" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A60" s="3" t="s">
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="B63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="61" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A61" s="2" t="s">
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="B64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="62" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A62" s="3" t="s">
+    <row r="65" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="B65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="63" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A63" s="2" t="s">
+    <row r="66" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="64" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
+    <row r="67" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A67" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="B67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="65" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A65" s="2" t="s">
+    <row r="68" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="B68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="66" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A66" s="3" t="s">
+    <row r="69" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A69" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="B69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="67" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A67" s="2" t="s">
+    <row r="70" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A70" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="B70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="68" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A68" s="3" t="s">
+    <row r="71" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A71" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="B71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A69" s="2" t="s">
+    <row r="72" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A72" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="B72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="70" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A70" s="3" t="s">
+    <row r="73" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A73" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="3" t="s">
+      <c r="B73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A71" s="2" t="s">
+    <row r="74" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A74" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="B74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="72" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A72" s="3" t="s">
+    <row r="75" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A75" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="B75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="73" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A73" s="2" t="s">
+    <row r="76" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A76" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="B76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="74" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A74" s="3" t="s">
+    <row r="77" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A77" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="B77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="75" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A75" s="2" t="s">
+    <row r="78" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A78" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="B78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="76" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A76" s="3" t="s">
+    <row r="79" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A79" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="B79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="77" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A77" s="2" t="s">
+    <row r="80" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A80" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="78" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A78" s="3" t="s">
+    <row r="81" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A81" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="B81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="79" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A79" s="2" t="s">
+    <row r="82" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A82" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="80" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A80" s="3" t="s">
+    <row r="83" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A83" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="B83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="81" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A81" s="2" t="s">
+    <row r="84" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A84" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="82" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A82" s="3" t="s">
+    <row r="85" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A85" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B85" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="83" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A83" s="2" t="s">
+    <row r="86" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A86" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="84" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A84" s="3" t="s">
+    <row r="87" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A87" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B87" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="85" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A85" s="2" t="s">
+    <row r="88" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A88" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="86" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A86" s="3" t="s">
+    <row r="89" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A89" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="3" t="s">
+      <c r="B89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="87" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A87" s="2" t="s">
+    <row r="90" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A90" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="88" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A88" s="3" t="s">
+    <row r="91" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A91" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="B91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D91" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="89" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A89" s="2" t="s">
+    <row r="92" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A92" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="90" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A90" s="3" t="s">
+    <row r="93" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A93" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="3" t="s">
+      <c r="B93" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D93" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="91" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A91" s="2" t="s">
+    <row r="94" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A94" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="92" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A92" s="3" t="s">
+    <row r="95" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A95" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B95" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="93" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A93" s="2" t="s">
+    <row r="96" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A96" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="94" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A94" s="3" t="s">
+    <row r="97" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A97" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="3" t="s">
+      <c r="B97" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="95" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A95" s="2" t="s">
+    <row r="98" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A98" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="2" t="s">
+      <c r="B98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="96" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A96" s="3" t="s">
+    <row r="99" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A99" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="3" t="s">
+      <c r="B99" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="97" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A97" s="2" t="s">
+    <row r="100" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A100" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="B100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="98" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A98" s="3" t="s">
+    <row r="101" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A101" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="3" t="s">
+      <c r="B101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D101" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="99" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A99" s="2" t="s">
+    <row r="102" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A102" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="100" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A100" s="3" t="s">
+    <row r="103" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A103" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="3" t="s">
+      <c r="B103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="101" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A101" s="2" t="s">
+    <row r="104" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A104" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>315</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="9">
-        <v>165</v>
-      </c>
-      <c r="D102" s="9">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="9">
-        <v>165</v>
-      </c>
-      <c r="D103" s="9">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="8" t="s">
-        <v>793</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="9">
-        <v>165</v>
-      </c>
-      <c r="D104" s="9">
-        <v>165</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="B105" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="C105" s="11">
+      <c r="B105" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="9">
+        <v>155</v>
+      </c>
+      <c r="D105" s="9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="9">
+        <v>155</v>
+      </c>
+      <c r="D106" s="9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="9">
+        <v>155</v>
+      </c>
+      <c r="D107" s="9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="C108" s="11">
         <v>250</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D108" s="11">
         <v>250</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="12" t="s">
-        <v>796</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>795</v>
-      </c>
-      <c r="C106" s="11">
+    <row r="109" spans="1:4">
+      <c r="A109" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="C109" s="11">
         <v>260</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D109" s="11">
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="12"/>
-    </row>
-    <row r="108" spans="4:4">
-      <c r="D108" s="13"/>
+    <row r="110" spans="1:1">
+      <c r="A110" s="12" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4">
+      <c r="D111" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12543,8 +12599,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
@@ -12773,10 +12828,10 @@
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12787,10 +12842,10 @@
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="C18" s="2">
         <v>390</v>
@@ -12801,10 +12856,10 @@
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C19" s="2">
         <v>390</v>
@@ -12815,10 +12870,10 @@
     </row>
     <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="6" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12829,7 +12884,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>33</v>
@@ -12843,10 +12898,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>804</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C22">
         <v>1060</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="814">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -12900,6 +12900,9 @@
       <c r="A22" t="s">
         <v>809</v>
       </c>
+      <c r="B22" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C22">
         <v>1060</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="815">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2470,7 +2470,10 @@
     <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
   </si>
   <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版含麻深蓝）</t>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
+  </si>
+  <si>
+    <t>1.5ml/支/盒 含麻</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -10429,10 +10432,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10443,10 +10446,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -12599,7 +12602,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
@@ -12896,12 +12900,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" ht="28.8" spans="1:4">
       <c r="A22" t="s">
         <v>809</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>33</v>
+        <v>810</v>
       </c>
       <c r="C22">
         <v>1060</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2473,7 +2473,7 @@
     <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
   </si>
   <si>
-    <t>1.5ml/支/盒（含麻）</t>
+    <t>（含麻）1.5ml/支/盒</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -2499,7 +2499,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2534,13 +2534,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF4757"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3052,13 +3045,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3067,122 +3063,119 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3199,11 +3192,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3215,7 +3207,7 @@
     <xf numFmtId="6" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3670,10 +3662,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>1850</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>1850</v>
       </c>
     </row>
@@ -5073,7 +5065,7 @@
       <c r="C114" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D114" s="14" t="s">
+      <c r="D114" s="13" t="s">
         <v>191</v>
       </c>
     </row>
@@ -11244,10 +11236,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>1850</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>1850</v>
       </c>
     </row>
@@ -11258,10 +11250,10 @@
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>1550</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>1550</v>
       </c>
     </row>
@@ -11272,10 +11264,10 @@
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>1800</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>1800</v>
       </c>
     </row>
@@ -11286,10 +11278,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>1240</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>1240</v>
       </c>
     </row>
@@ -12512,82 +12504,82 @@
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="7" t="s">
         <v>795</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="8">
         <v>155</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="7" t="s">
         <v>796</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <v>155</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="7" t="s">
         <v>797</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107" s="8">
         <v>155</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B108" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>250</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <v>250</v>
       </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B109" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>260</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="11" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="111" spans="4:4">
-      <c r="D111" s="13"/>
+      <c r="D111" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12598,7 +12590,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
@@ -12816,7 +12808,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
+    <row r="16" ht="21" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>607</v>
       </c>
@@ -12830,7 +12822,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
+    <row r="17" ht="21" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
         <v>802</v>
       </c>
@@ -12844,7 +12836,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
+    <row r="18" ht="21" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>804</v>
       </c>
@@ -12858,7 +12850,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
+    <row r="19" ht="21" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>805</v>
       </c>
@@ -12872,8 +12864,8 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="6" t="s">
+    <row r="20" ht="21" customHeight="1" spans="1:4">
+      <c r="A20" s="2" t="s">
         <v>806</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -12886,33 +12878,39 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+    <row r="21" ht="21" customHeight="1" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>1000</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+    <row r="22" ht="21" customHeight="1" spans="1:4">
+      <c r="A22" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>1060</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>1060</v>
       </c>
+    </row>
+    <row r="23" ht="21" customHeight="1" spans="1:4">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="2"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="814">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2410,13 +2410,10 @@
     <t>乔雅登（法国本土版）/4号</t>
   </si>
   <si>
-    <t>乔雅登（法国本土版）/5号 丰颜</t>
+    <t>乔雅登（法国本土版）/5号</t>
   </si>
   <si>
     <t>¥1,600</t>
-  </si>
-  <si>
-    <t>乔雅登（法国本土版）/6号 朔颜</t>
   </si>
   <si>
     <t>乔雅登（韩版）/5号 丰颜</t>
@@ -10424,10 +10421,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>811</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>812</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10438,10 +10435,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>813</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -11231,7 +11228,7 @@
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>791</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
@@ -11245,7 +11242,7 @@
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -11259,7 +11256,7 @@
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>5</v>
@@ -11273,7 +11270,7 @@
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
@@ -12505,7 +12502,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="7" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>10</v>
@@ -12519,7 +12516,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>10</v>
@@ -12533,7 +12530,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>10</v>
@@ -12547,10 +12544,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="B108" s="9" t="s">
         <v>798</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>799</v>
       </c>
       <c r="C108" s="10">
         <v>250</v>
@@ -12561,10 +12558,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="11" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C109" s="10">
         <v>260</v>
@@ -12575,7 +12572,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="111" spans="4:4">
@@ -12824,10 +12821,10 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12838,10 +12835,10 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C18" s="2">
         <v>390</v>
@@ -12852,10 +12849,10 @@
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C19" s="2">
         <v>390</v>
@@ -12866,10 +12863,10 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12880,7 +12877,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
@@ -12894,10 +12891,10 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>810</v>
       </c>
       <c r="C22" s="2">
         <v>1060</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="818">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2437,24 +2437,33 @@
     <t>姣兰 / 经典玻尿酸</t>
   </si>
   <si>
+    <t>姣兰 / Lips 唇部玻尿酸</t>
+  </si>
+  <si>
+    <t>德彩 1 号 小分子</t>
+  </si>
+  <si>
+    <t>德彩 2 号 中分子</t>
+  </si>
+  <si>
+    <t>德彩 3 号 大分子</t>
+  </si>
+  <si>
+    <t>德彩 4 号 加大分子</t>
+  </si>
+  <si>
+    <t>冰月岚 / 面部童颜针</t>
+  </si>
+  <si>
+    <t>350mg+10ml / 盒（粉末 + 液体双剂）</t>
+  </si>
+  <si>
+    <t>冰月岚 / 黑金少女针</t>
+  </si>
+  <si>
     <t>1ml / 支 / 盒</t>
   </si>
   <si>
-    <t>姣兰 / Lips 唇部玻尿酸</t>
-  </si>
-  <si>
-    <t>乔雅登天使针</t>
-  </si>
-  <si>
-    <t>冰月岚 / 面部童颜针</t>
-  </si>
-  <si>
-    <t>350mg+10ml / 盒（粉末 + 液体双剂）</t>
-  </si>
-  <si>
-    <t>冰月岚 / 黑金少女针</t>
-  </si>
-  <si>
     <t>冰月岚 / 粉金少女针</t>
   </si>
   <si>
@@ -2471,6 +2480,9 @@
   </si>
   <si>
     <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>伊妍仕/少女针(欧版)</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -2496,7 +2508,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2534,12 +2546,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2892,7 +2898,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2913,17 +2919,6 @@
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -3042,13 +3037,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3057,122 +3055,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3183,6 +3178,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3191,24 +3189,6 @@
     </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3659,10 +3639,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>1850</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>1850</v>
       </c>
     </row>
@@ -5062,7 +5042,7 @@
       <c r="C114" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="8" t="s">
         <v>191</v>
       </c>
     </row>
@@ -7792,7 +7772,7 @@
       <c r="C309" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D309" s="5" t="s">
+      <c r="D309" s="6" t="s">
         <v>557</v>
       </c>
     </row>
@@ -10421,10 +10401,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10435,10 +10415,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -11037,11 +11017,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
@@ -11233,10 +11214,10 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>1850</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>1850</v>
       </c>
     </row>
@@ -11247,10 +11228,10 @@
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>1550</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>1550</v>
       </c>
     </row>
@@ -11261,10 +11242,10 @@
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>1800</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>1800</v>
       </c>
     </row>
@@ -11275,10 +11256,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>1240</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="7">
         <v>1240</v>
       </c>
     </row>
@@ -12459,124 +12440,172 @@
       </c>
     </row>
     <row r="102" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="B102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="3" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="3" t="s">
+      <c r="B103" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="104" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="B104" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="3" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="7" t="s">
+    <row r="105" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A105" s="2" t="s">
         <v>794</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="2">
         <v>155</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="2">
         <v>155</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="7" t="s">
+    <row r="106" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A106" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106" s="8">
+      <c r="B106" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="3">
         <v>155</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="3">
         <v>155</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="7" t="s">
+    <row r="107" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A107" s="2" t="s">
         <v>796</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="2">
         <v>155</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="2">
         <v>155</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="7" t="s">
+    <row r="108" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A108" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="3">
+        <v>250</v>
+      </c>
+      <c r="D108" s="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="109" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A109" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="C108" s="10">
-        <v>250</v>
-      </c>
-      <c r="D108" s="10">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="11" t="s">
+      <c r="B109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="2">
+        <v>260</v>
+      </c>
+      <c r="D109" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A110" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="B109" s="9" t="s">
-        <v>798</v>
-      </c>
-      <c r="C109" s="10">
-        <v>260</v>
-      </c>
-      <c r="D109" s="10">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="11" t="s">
+      <c r="B110" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="3">
+        <v>90</v>
+      </c>
+      <c r="D110" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="111" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A111" s="2" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="111" spans="4:4">
-      <c r="D111" s="12"/>
+      <c r="B111" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="2">
+        <v>90</v>
+      </c>
+      <c r="D111" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A112" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="3">
+        <v>90</v>
+      </c>
+      <c r="D112" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="113" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A113" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="2">
+        <v>90</v>
+      </c>
+      <c r="D113" s="2">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12821,10 +12850,10 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12835,10 +12864,10 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="C18" s="2">
         <v>390</v>
@@ -12849,10 +12878,10 @@
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="C19" s="2">
         <v>390</v>
@@ -12863,10 +12892,10 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12877,7 +12906,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
@@ -12891,10 +12920,10 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C22" s="2">
         <v>1060</v>
@@ -14657,7 +14686,7 @@
       <c r="C124" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="6" t="s">
         <v>557</v>
       </c>
     </row>
@@ -15979,7 +16008,7 @@
       <c r="C10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>191</v>
       </c>
     </row>
@@ -16764,8 +16793,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16883,6 +16912,20 @@
         <v>273</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="8"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3678" uniqueCount="814">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2438,18 +2438,6 @@
   </si>
   <si>
     <t>姣兰 / Lips 唇部玻尿酸</t>
-  </si>
-  <si>
-    <t>德彩 1 号 小分子</t>
-  </si>
-  <si>
-    <t>德彩 2 号 中分子</t>
-  </si>
-  <si>
-    <t>德彩 3 号 大分子</t>
-  </si>
-  <si>
-    <t>德彩 4 号 加大分子</t>
   </si>
   <si>
     <t>冰月岚 / 面部童颜针</t>
@@ -10401,10 +10389,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10415,10 +10403,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -12552,60 +12540,28 @@
       </c>
     </row>
     <row r="110" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A110" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C110" s="3">
-        <v>90</v>
-      </c>
-      <c r="D110" s="3">
-        <v>90</v>
-      </c>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A111" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C111" s="2">
-        <v>90</v>
-      </c>
-      <c r="D111" s="2">
-        <v>90</v>
-      </c>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
     </row>
     <row r="112" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="3">
-        <v>90</v>
-      </c>
-      <c r="D112" s="3">
-        <v>90</v>
-      </c>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A113" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C113" s="2">
-        <v>90</v>
-      </c>
-      <c r="D113" s="2">
-        <v>90</v>
-      </c>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12850,10 +12806,10 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12864,10 +12820,10 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C18" s="2">
         <v>390</v>
@@ -12878,10 +12834,10 @@
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C19" s="2">
         <v>390</v>
@@ -12892,10 +12848,10 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12906,7 +12862,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
@@ -12920,10 +12876,10 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C22" s="2">
         <v>1060</v>
@@ -16914,7 +16870,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3678" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="818">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2468,6 +2468,18 @@
   </si>
   <si>
     <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>弗缦 Pro/0.5版</t>
+  </si>
+  <si>
+    <t>0.5ml/支</t>
+  </si>
+  <si>
+    <t>弗缦 Pro/1.0版</t>
+  </si>
+  <si>
+    <t>1ml/支</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
@@ -10389,10 +10401,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10403,10 +10415,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -15821,7 +15833,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -16680,6 +16692,34 @@
       </c>
       <c r="D61" s="3" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1450</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
@@ -16870,7 +16910,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="6"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -11229,10 +11229,10 @@
         <v>5</v>
       </c>
       <c r="C15" s="7">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D15" s="7">
-        <v>1550</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
@@ -11243,10 +11243,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="7">
-        <v>1800</v>
+        <v>1730</v>
       </c>
       <c r="D16" s="7">
-        <v>1800</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
@@ -12489,10 +12489,10 @@
         <v>10</v>
       </c>
       <c r="C105" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D105" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106" ht="22.05" customHeight="1" spans="1:4">
@@ -12502,11 +12502,11 @@
       <c r="B106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="3">
-        <v>155</v>
-      </c>
-      <c r="D106" s="3">
-        <v>155</v>
+      <c r="C106" s="2">
+        <v>160</v>
+      </c>
+      <c r="D106" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="107" ht="22.05" customHeight="1" spans="1:4">
@@ -12517,10 +12517,10 @@
         <v>10</v>
       </c>
       <c r="C107" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D107" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" ht="22.05" customHeight="1" spans="1:4">
@@ -16916,10 +16916,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="4">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D9" s="2">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="1"/>
+    <workbookView windowWidth="20135" windowHeight="11711" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="819">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2495,6 +2495,9 @@
   </si>
   <si>
     <t>50ml+10ml / 盒</t>
+  </si>
+  <si>
+    <t>韩国原版Babyface皮贴骨</t>
   </si>
 </sst>
 </file>
@@ -10428,10 +10431,18 @@
       </c>
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="A32" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="C32" s="3">
+        <v>840</v>
+      </c>
+      <c r="D32" s="3">
+        <v>840</v>
+      </c>
     </row>
     <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2497,7 +2497,7 @@
     <t>50ml+10ml / 盒</t>
   </si>
   <si>
-    <t>韩国原版Babyface皮贴骨</t>
+    <t>韩版Babyface皮贴骨</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20135" windowHeight="11711" activeTab="10"/>
+    <workbookView windowWidth="20568" windowHeight="12840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="820">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2480,6 +2480,9 @@
   </si>
   <si>
     <t>1ml/支</t>
+  </si>
+  <si>
+    <t>韩版肤丽美</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
@@ -3542,7 +3545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D444"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3564,3412 +3567,3508 @@
       </c>
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1850</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1850</v>
+      </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
+      <c r="A14" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1850</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1850</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" ht="22.05" customHeight="1" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="22.05" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" ht="22.05" customHeight="1" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" ht="22.05" customHeight="1" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" ht="22.05" customHeight="1" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" ht="22.05" customHeight="1" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" ht="22.05" customHeight="1" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" ht="22.05" customHeight="1" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" ht="22.05" customHeight="1" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" ht="22.05" customHeight="1" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" ht="22.05" customHeight="1" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" ht="22.05" customHeight="1" spans="1:4">
       <c r="A42" s="3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" ht="22.05" customHeight="1" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" ht="22.05" customHeight="1" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" ht="22.05" customHeight="1" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" ht="22.05" customHeight="1" spans="1:4">
       <c r="A46" s="3" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="22.05" customHeight="1" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" ht="22.05" customHeight="1" spans="1:4">
       <c r="A48" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" ht="22.05" customHeight="1" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" ht="22.05" customHeight="1" spans="1:4">
       <c r="A50" s="3" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" ht="22.05" customHeight="1" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" ht="22.05" customHeight="1" spans="1:4">
       <c r="A52" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" ht="22.05" customHeight="1" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" ht="22.05" customHeight="1" spans="1:4">
       <c r="A54" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" ht="22.05" customHeight="1" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" ht="22.05" customHeight="1" spans="1:4">
       <c r="A56" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" ht="22.05" customHeight="1" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.05" customHeight="1" spans="1:4">
       <c r="A58" s="3" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" ht="22.05" customHeight="1" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" ht="22.05" customHeight="1" spans="1:4">
       <c r="A60" s="3" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" ht="22.05" customHeight="1" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" ht="22.05" customHeight="1" spans="1:4">
       <c r="A62" s="3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" ht="22.05" customHeight="1" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" ht="22.05" customHeight="1" spans="1:4">
       <c r="A64" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" ht="22.05" customHeight="1" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" ht="22.05" customHeight="1" spans="1:4">
       <c r="A66" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" ht="22.05" customHeight="1" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" ht="22.05" customHeight="1" spans="1:4">
       <c r="A68" s="3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" ht="22.05" customHeight="1" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" ht="22.05" customHeight="1" spans="1:4">
       <c r="A70" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" ht="22.05" customHeight="1" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" ht="22.05" customHeight="1" spans="1:4">
       <c r="A72" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" ht="22.05" customHeight="1" spans="1:4">
       <c r="A73" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" ht="22.05" customHeight="1" spans="1:4">
       <c r="A74" s="3" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" ht="22.05" customHeight="1" spans="1:4">
       <c r="A75" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" ht="22.05" customHeight="1" spans="1:4">
       <c r="A76" s="3" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" ht="22.05" customHeight="1" spans="1:4">
       <c r="A77" s="2" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" ht="22.05" customHeight="1" spans="1:4">
       <c r="A78" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" ht="22.05" customHeight="1" spans="1:4">
       <c r="A79" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" ht="22.05" customHeight="1" spans="1:4">
       <c r="A80" s="3" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" ht="22.05" customHeight="1" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" ht="22.05" customHeight="1" spans="1:4">
       <c r="A82" s="3" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" ht="22.05" customHeight="1" spans="1:4">
       <c r="A83" s="2" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" ht="22.05" customHeight="1" spans="1:4">
       <c r="A84" s="3" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" ht="22.05" customHeight="1" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" ht="22.05" customHeight="1" spans="1:4">
       <c r="A86" s="3" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" ht="22.05" customHeight="1" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" ht="22.05" customHeight="1" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" ht="22.05" customHeight="1" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" ht="22.05" customHeight="1" spans="1:4">
       <c r="A90" s="3" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" ht="22.05" customHeight="1" spans="1:4">
       <c r="A91" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" ht="22.05" customHeight="1" spans="1:4">
       <c r="A92" s="3" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" ht="22.05" customHeight="1" spans="1:4">
       <c r="A93" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94" ht="22.05" customHeight="1" spans="1:4">
       <c r="A94" s="3" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" ht="22.05" customHeight="1" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" ht="22.05" customHeight="1" spans="1:4">
       <c r="A96" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" ht="22.05" customHeight="1" spans="1:4">
       <c r="A97" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
     </row>
     <row r="98" ht="22.05" customHeight="1" spans="1:4">
       <c r="A98" s="3" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" ht="22.05" customHeight="1" spans="1:4">
       <c r="A99" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="100" ht="22.05" customHeight="1" spans="1:4">
       <c r="A100" s="3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" ht="22.05" customHeight="1" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
     </row>
     <row r="102" ht="22.05" customHeight="1" spans="1:4">
       <c r="A102" s="3" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>116</v>
+        <v>190</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" ht="22.05" customHeight="1" spans="1:4">
       <c r="A104" s="3" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" ht="22.05" customHeight="1" spans="1:4">
       <c r="A105" s="2" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" ht="22.05" customHeight="1" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" ht="22.05" customHeight="1" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" ht="22.05" customHeight="1" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" ht="22.05" customHeight="1" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" ht="22.05" customHeight="1" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="111" ht="22.05" customHeight="1" spans="1:4">
       <c r="A111" s="2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" ht="22.05" customHeight="1" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" ht="22.05" customHeight="1" spans="1:4">
       <c r="A113" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" ht="22.05" customHeight="1" spans="1:4">
       <c r="A114" s="3" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>191</v>
+        <v>219</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="115" ht="22.05" customHeight="1" spans="1:4">
       <c r="A115" s="2" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>57</v>
+        <v>222</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>57</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" ht="22.05" customHeight="1" spans="1:4">
       <c r="A116" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" ht="22.05" customHeight="1" spans="1:4">
       <c r="A117" s="2" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
     </row>
     <row r="118" ht="22.05" customHeight="1" spans="1:4">
       <c r="A118" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
     </row>
     <row r="119" ht="22.05" customHeight="1" spans="1:4">
       <c r="A119" s="2" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="120" ht="22.05" customHeight="1" spans="1:4">
       <c r="A120" s="3" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" ht="22.05" customHeight="1" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>5</v>
+        <v>236</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" ht="22.05" customHeight="1" spans="1:4">
       <c r="A122" s="3" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123" ht="22.05" customHeight="1" spans="1:4">
       <c r="A123" s="2" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
     </row>
     <row r="124" ht="22.05" customHeight="1" spans="1:4">
       <c r="A124" s="3" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
     </row>
     <row r="125" ht="22.05" customHeight="1" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>5</v>
+        <v>245</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" ht="22.05" customHeight="1" spans="1:4">
       <c r="A126" s="3" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>47</v>
+        <v>242</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
     </row>
     <row r="127" ht="22.05" customHeight="1" spans="1:4">
       <c r="A127" s="2" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
     </row>
     <row r="128" ht="22.05" customHeight="1" spans="1:4">
       <c r="A128" s="3" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
     </row>
     <row r="129" ht="22.05" customHeight="1" spans="1:4">
       <c r="A129" s="2" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" ht="22.05" customHeight="1" spans="1:4">
       <c r="A130" s="3" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>230</v>
+        <v>63</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" ht="22.05" customHeight="1" spans="1:4">
       <c r="A131" s="2" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" ht="22.05" customHeight="1" spans="1:4">
       <c r="A132" s="3" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" ht="22.05" customHeight="1" spans="1:4">
       <c r="A133" s="2" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
     </row>
     <row r="134" ht="22.05" customHeight="1" spans="1:4">
       <c r="A134" s="3" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135" ht="22.05" customHeight="1" spans="1:4">
       <c r="A135" s="2" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" ht="22.05" customHeight="1" spans="1:4">
       <c r="A136" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" ht="22.05" customHeight="1" spans="1:4">
       <c r="A137" s="2" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
     </row>
     <row r="138" ht="22.05" customHeight="1" spans="1:4">
       <c r="A138" s="3" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" ht="22.05" customHeight="1" spans="1:4">
       <c r="A139" s="2" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" ht="22.05" customHeight="1" spans="1:4">
       <c r="A140" s="3" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
     </row>
     <row r="141" ht="22.05" customHeight="1" spans="1:4">
       <c r="A141" s="2" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142" ht="22.05" customHeight="1" spans="1:4">
       <c r="A142" s="3" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>63</v>
+        <v>282</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="143" ht="22.05" customHeight="1" spans="1:4">
       <c r="A143" s="2" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>261</v>
+        <v>96</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>261</v>
+        <v>96</v>
       </c>
     </row>
     <row r="144" ht="22.05" customHeight="1" spans="1:4">
       <c r="A144" s="3" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
     </row>
     <row r="145" ht="22.05" customHeight="1" spans="1:4">
       <c r="A145" s="2" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="146" ht="22.05" customHeight="1" spans="1:4">
       <c r="A146" s="3" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>10</v>
+        <v>292</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
     </row>
     <row r="147" ht="22.05" customHeight="1" spans="1:4">
       <c r="A147" s="2" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" ht="22.05" customHeight="1" spans="1:4">
       <c r="A148" s="3" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
     </row>
     <row r="149" ht="22.05" customHeight="1" spans="1:4">
       <c r="A149" s="2" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="150" ht="22.05" customHeight="1" spans="1:4">
       <c r="A150" s="3" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>277</v>
+        <v>99</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>277</v>
+        <v>99</v>
       </c>
     </row>
     <row r="151" ht="22.05" customHeight="1" spans="1:4">
       <c r="A151" s="2" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>188</v>
+        <v>304</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>188</v>
+        <v>304</v>
       </c>
     </row>
     <row r="152" ht="22.05" customHeight="1" spans="1:4">
       <c r="A152" s="3" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="153" ht="22.05" customHeight="1" spans="1:4">
       <c r="A153" s="2" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>274</v>
+        <v>56</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>280</v>
+        <v>159</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>280</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" ht="22.05" customHeight="1" spans="1:4">
       <c r="A154" s="3" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>282</v>
+        <v>10</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>283</v>
+        <v>80</v>
       </c>
     </row>
     <row r="155" ht="22.05" customHeight="1" spans="1:4">
       <c r="A155" s="2" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" ht="22.05" customHeight="1" spans="1:4">
       <c r="A156" s="3" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="157" ht="22.05" customHeight="1" spans="1:4">
       <c r="A157" s="2" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" ht="22.05" customHeight="1" spans="1:4">
       <c r="A158" s="3" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>292</v>
+        <v>10</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>293</v>
+        <v>99</v>
       </c>
     </row>
     <row r="159" ht="22.05" customHeight="1" spans="1:4">
       <c r="A159" s="2" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>295</v>
+        <v>10</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>225</v>
+        <v>318</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>225</v>
+        <v>318</v>
       </c>
     </row>
     <row r="160" ht="22.05" customHeight="1" spans="1:4">
       <c r="A160" s="3" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
     </row>
     <row r="161" ht="22.05" customHeight="1" spans="1:4">
       <c r="A161" s="2" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>299</v>
+        <v>10</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>300</v>
+        <v>57</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>300</v>
+        <v>57</v>
       </c>
     </row>
     <row r="162" ht="22.05" customHeight="1" spans="1:4">
       <c r="A162" s="3" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163" ht="22.05" customHeight="1" spans="1:4">
       <c r="A163" s="2" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>304</v>
+        <v>190</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>304</v>
+        <v>190</v>
       </c>
     </row>
     <row r="164" ht="22.05" customHeight="1" spans="1:4">
       <c r="A164" s="3" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" ht="22.05" customHeight="1" spans="1:4">
       <c r="A165" s="2" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>159</v>
+        <v>326</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>159</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" ht="22.05" customHeight="1" spans="1:4">
       <c r="A166" s="3" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>10</v>
+        <v>328</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>80</v>
+        <v>329</v>
       </c>
     </row>
     <row r="167" ht="22.05" customHeight="1" spans="1:4">
       <c r="A167" s="2" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="168" ht="22.05" customHeight="1" spans="1:4">
       <c r="A168" s="3" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
     </row>
     <row r="169" ht="22.05" customHeight="1" spans="1:4">
       <c r="A169" s="2" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170" ht="22.05" customHeight="1" spans="1:4">
       <c r="A170" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>10</v>
+        <v>338</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
     </row>
     <row r="171" ht="22.05" customHeight="1" spans="1:4">
       <c r="A171" s="2" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>10</v>
+        <v>339</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
     </row>
     <row r="172" ht="22.05" customHeight="1" spans="1:4">
       <c r="A172" s="3" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>318</v>
+        <v>137</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>318</v>
+        <v>137</v>
       </c>
     </row>
     <row r="173" ht="22.05" customHeight="1" spans="1:4">
       <c r="A173" s="2" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>10</v>
+        <v>342</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>57</v>
+        <v>343</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>57</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" ht="22.05" customHeight="1" spans="1:4">
       <c r="A174" s="3" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>322</v>
+        <v>10</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" ht="22.05" customHeight="1" spans="1:4">
       <c r="A175" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
     </row>
     <row r="176" ht="22.05" customHeight="1" spans="1:4">
       <c r="A176" s="3" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="177" ht="22.05" customHeight="1" spans="1:4">
       <c r="A177" s="2" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>5</v>
+        <v>348</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
     </row>
     <row r="178" ht="22.05" customHeight="1" spans="1:4">
       <c r="A178" s="3" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" ht="22.05" customHeight="1" spans="1:4">
       <c r="A179" s="2" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>80</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" ht="22.05" customHeight="1" spans="1:4">
       <c r="A180" s="3" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" ht="22.05" customHeight="1" spans="1:4">
       <c r="A181" s="2" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>336</v>
+        <v>99</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>336</v>
+        <v>99</v>
       </c>
     </row>
     <row r="182" ht="22.05" customHeight="1" spans="1:4">
       <c r="A182" s="3" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" ht="22.05" customHeight="1" spans="1:4">
       <c r="A183" s="2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>264</v>
+        <v>359</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>264</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" ht="22.05" customHeight="1" spans="1:4">
       <c r="A184" s="3" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>10</v>
+        <v>361</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="185" ht="22.05" customHeight="1" spans="1:4">
       <c r="A185" s="2" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>342</v>
+        <v>10</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>343</v>
+        <v>116</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>343</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186" ht="22.05" customHeight="1" spans="1:4">
       <c r="A186" s="3" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="187" ht="22.05" customHeight="1" spans="1:4">
       <c r="A187" s="2" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>72</v>
+        <v>365</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>72</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" ht="22.05" customHeight="1" spans="1:4">
       <c r="A188" s="3" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>10</v>
+        <v>367</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="189" ht="22.05" customHeight="1" spans="1:4">
       <c r="A189" s="2" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>349</v>
+        <v>135</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>349</v>
+        <v>135</v>
       </c>
     </row>
     <row r="190" ht="22.05" customHeight="1" spans="1:4">
       <c r="A190" s="3" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
     </row>
     <row r="191" ht="22.05" customHeight="1" spans="1:4">
       <c r="A191" s="2" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>349</v>
+        <v>190</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>349</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" ht="22.05" customHeight="1" spans="1:4">
       <c r="A192" s="3" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" ht="22.05" customHeight="1" spans="1:4">
       <c r="A193" s="2" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="194" ht="22.05" customHeight="1" spans="1:4">
       <c r="A194" s="3" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
     </row>
     <row r="195" ht="22.05" customHeight="1" spans="1:4">
       <c r="A195" s="2" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="196" ht="22.05" customHeight="1" spans="1:4">
       <c r="A196" s="3" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>201</v>
+        <v>385</v>
       </c>
     </row>
     <row r="197" ht="22.05" customHeight="1" spans="1:4">
       <c r="A197" s="2" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>10</v>
+        <v>379</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>116</v>
+        <v>388</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>116</v>
+        <v>388</v>
       </c>
     </row>
     <row r="198" ht="22.05" customHeight="1" spans="1:4">
       <c r="A198" s="3" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>95</v>
+        <v>356</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>61</v>
+        <v>390</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>61</v>
+        <v>390</v>
       </c>
     </row>
     <row r="199" ht="22.05" customHeight="1" spans="1:4">
       <c r="A199" s="2" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>95</v>
+        <v>392</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
     </row>
     <row r="200" ht="22.05" customHeight="1" spans="1:4">
       <c r="A200" s="3" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
     </row>
     <row r="201" ht="22.05" customHeight="1" spans="1:4">
       <c r="A201" s="2" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="202" ht="22.05" customHeight="1" spans="1:4">
       <c r="A202" s="3" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>372</v>
+        <v>277</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>372</v>
+        <v>277</v>
       </c>
     </row>
     <row r="203" ht="22.05" customHeight="1" spans="1:4">
       <c r="A203" s="2" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>374</v>
+        <v>150</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
     </row>
     <row r="204" ht="22.05" customHeight="1" spans="1:4">
       <c r="A204" s="3" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>376</v>
+        <v>150</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>377</v>
+        <v>72</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>377</v>
+        <v>72</v>
       </c>
     </row>
     <row r="205" ht="22.05" customHeight="1" spans="1:4">
       <c r="A205" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>92</v>
+        <v>400</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>92</v>
+        <v>400</v>
       </c>
     </row>
     <row r="206" ht="22.05" customHeight="1" spans="1:4">
       <c r="A206" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207" ht="22.05" customHeight="1" spans="1:4">
       <c r="A207" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>385</v>
+        <v>225</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>385</v>
+        <v>225</v>
       </c>
     </row>
     <row r="208" ht="22.05" customHeight="1" spans="1:4">
       <c r="A208" s="3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>385</v>
+        <v>171</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>385</v>
+        <v>171</v>
       </c>
     </row>
     <row r="209" ht="22.05" customHeight="1" spans="1:4">
       <c r="A209" s="2" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>388</v>
+        <v>300</v>
       </c>
     </row>
     <row r="210" ht="22.05" customHeight="1" spans="1:4">
       <c r="A210" s="3" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>356</v>
+        <v>404</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="211" ht="22.05" customHeight="1" spans="1:4">
       <c r="A211" s="2" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>293</v>
+        <v>385</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>293</v>
+        <v>385</v>
       </c>
     </row>
     <row r="212" ht="22.05" customHeight="1" spans="1:4">
       <c r="A212" s="3" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>264</v>
+        <v>385</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>264</v>
+        <v>385</v>
       </c>
     </row>
     <row r="213" ht="22.05" customHeight="1" spans="1:4">
       <c r="A213" s="2" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>145</v>
+        <v>385</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>145</v>
+        <v>385</v>
       </c>
     </row>
     <row r="214" ht="22.05" customHeight="1" spans="1:4">
       <c r="A214" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>277</v>
+        <v>385</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>277</v>
+        <v>385</v>
       </c>
     </row>
     <row r="215" ht="22.05" customHeight="1" spans="1:4">
       <c r="A215" s="2" t="s">
-        <v>168</v>
+        <v>411</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216" ht="22.05" customHeight="1" spans="1:4">
       <c r="A216" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>150</v>
+        <v>414</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>72</v>
+        <v>415</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>72</v>
+        <v>415</v>
       </c>
     </row>
     <row r="217" ht="22.05" customHeight="1" spans="1:4">
       <c r="A217" s="2" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>374</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>400</v>
+        <v>139</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>400</v>
+        <v>139</v>
       </c>
     </row>
     <row r="218" ht="22.05" customHeight="1" spans="1:4">
       <c r="A218" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>400</v>
+        <v>293</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>400</v>
+        <v>293</v>
       </c>
     </row>
     <row r="219" ht="22.05" customHeight="1" spans="1:4">
       <c r="A219" s="2" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>225</v>
+        <v>41</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>225</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" ht="22.05" customHeight="1" spans="1:4">
       <c r="A220" s="3" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
     </row>
     <row r="221" ht="22.05" customHeight="1" spans="1:4">
       <c r="A221" s="2" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>300</v>
+        <v>423</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>300</v>
+        <v>423</v>
       </c>
     </row>
     <row r="222" ht="22.05" customHeight="1" spans="1:4">
       <c r="A222" s="3" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
     </row>
     <row r="223" ht="22.05" customHeight="1" spans="1:4">
       <c r="A223" s="2" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>404</v>
+        <v>158</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
     </row>
     <row r="224" ht="22.05" customHeight="1" spans="1:4">
       <c r="A224" s="3" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>404</v>
+        <v>95</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
     </row>
     <row r="225" ht="22.05" customHeight="1" spans="1:4">
       <c r="A225" s="2" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
     </row>
     <row r="226" ht="22.05" customHeight="1" spans="1:4">
       <c r="A226" s="3" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>404</v>
+        <v>95</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>385</v>
+        <v>275</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>385</v>
+        <v>275</v>
       </c>
     </row>
     <row r="227" ht="22.05" customHeight="1" spans="1:4">
       <c r="A227" s="2" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>412</v>
+        <v>95</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>84</v>
+        <v>433</v>
       </c>
     </row>
     <row r="228" ht="22.05" customHeight="1" spans="1:4">
       <c r="A228" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>415</v>
+        <v>139</v>
       </c>
     </row>
     <row r="229" ht="22.05" customHeight="1" spans="1:4">
       <c r="A229" s="2" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>139</v>
+        <v>438</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>139</v>
+        <v>438</v>
       </c>
     </row>
     <row r="230" ht="22.05" customHeight="1" spans="1:4">
       <c r="A230" s="3" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>293</v>
+        <v>440</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>293</v>
+        <v>440</v>
       </c>
     </row>
     <row r="231" ht="22.05" customHeight="1" spans="1:4">
       <c r="A231" s="2" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>348</v>
+        <v>442</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>41</v>
+        <v>443</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>41</v>
+        <v>443</v>
       </c>
     </row>
     <row r="232" ht="22.05" customHeight="1" spans="1:4">
       <c r="A232" s="3" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>37</v>
+        <v>445</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>37</v>
+        <v>445</v>
       </c>
     </row>
     <row r="233" ht="22.05" customHeight="1" spans="1:4">
       <c r="A233" s="2" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>422</v>
+        <v>374</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="234" ht="22.05" customHeight="1" spans="1:4">
       <c r="A234" s="3" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>29</v>
+        <v>443</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>29</v>
+        <v>443</v>
       </c>
     </row>
     <row r="235" ht="22.05" customHeight="1" spans="1:4">
       <c r="A235" s="2" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>158</v>
+        <v>442</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
     </row>
     <row r="236" ht="22.05" customHeight="1" spans="1:4">
       <c r="A236" s="3" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>95</v>
+        <v>374</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>29</v>
+        <v>440</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>29</v>
+        <v>440</v>
       </c>
     </row>
     <row r="237" ht="22.05" customHeight="1" spans="1:4">
       <c r="A237" s="2" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
     </row>
     <row r="238" ht="22.05" customHeight="1" spans="1:4">
       <c r="A238" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
     </row>
     <row r="239" ht="22.05" customHeight="1" spans="1:4">
       <c r="A239" s="2" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
     </row>
     <row r="240" ht="22.05" customHeight="1" spans="1:4">
       <c r="A240" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>435</v>
+        <v>158</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" ht="22.05" customHeight="1" spans="1:4">
       <c r="A241" s="2" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>437</v>
+        <v>158</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
     </row>
     <row r="242" ht="22.05" customHeight="1" spans="1:4">
       <c r="A242" s="3" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>374</v>
+        <v>459</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>440</v>
+        <v>61</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>440</v>
+        <v>61</v>
       </c>
     </row>
     <row r="243" ht="22.05" customHeight="1" spans="1:4">
       <c r="A243" s="2" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>443</v>
+        <v>212</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>443</v>
+        <v>212</v>
       </c>
     </row>
     <row r="244" ht="22.05" customHeight="1" spans="1:4">
       <c r="A244" s="3" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="245" ht="22.05" customHeight="1" spans="1:4">
       <c r="A245" s="2" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
     </row>
     <row r="246" ht="22.05" customHeight="1" spans="1:4">
       <c r="A246" s="3" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
     </row>
     <row r="247" ht="22.05" customHeight="1" spans="1:4">
       <c r="A247" s="2" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>445</v>
+        <v>54</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>445</v>
+        <v>54</v>
       </c>
     </row>
     <row r="248" ht="22.05" customHeight="1" spans="1:4">
       <c r="A248" s="3" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>374</v>
+        <v>473</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
     </row>
     <row r="249" ht="22.05" customHeight="1" spans="1:4">
       <c r="A249" s="2" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="250" ht="22.05" customHeight="1" spans="1:4">
       <c r="A250" s="3" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
     </row>
     <row r="251" ht="22.05" customHeight="1" spans="1:4">
       <c r="A251" s="2" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>158</v>
+        <v>374</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>454</v>
+        <v>141</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>454</v>
+        <v>141</v>
       </c>
     </row>
     <row r="252" ht="22.05" customHeight="1" spans="1:4">
       <c r="A252" s="3" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>158</v>
@@ -6983,2857 +7082,2689 @@
     </row>
     <row r="253" ht="22.05" customHeight="1" spans="1:4">
       <c r="A253" s="2" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>457</v>
+        <v>267</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>457</v>
+        <v>267</v>
       </c>
     </row>
     <row r="254" ht="22.05" customHeight="1" spans="1:4">
       <c r="A254" s="3" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>459</v>
+        <v>158</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>61</v>
+        <v>267</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>61</v>
+        <v>267</v>
       </c>
     </row>
     <row r="255" ht="22.05" customHeight="1" spans="1:4">
       <c r="A255" s="2" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>461</v>
+        <v>158</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
     </row>
     <row r="256" ht="22.05" customHeight="1" spans="1:4">
       <c r="A256" s="3" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>463</v>
+        <v>158</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
     </row>
     <row r="257" ht="22.05" customHeight="1" spans="1:4">
       <c r="A257" s="2" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
     </row>
     <row r="258" ht="22.05" customHeight="1" spans="1:4">
       <c r="A258" s="3" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>468</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>469</v>
+        <v>293</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>469</v>
+        <v>293</v>
       </c>
     </row>
     <row r="259" ht="22.05" customHeight="1" spans="1:4">
       <c r="A259" s="2" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>471</v>
+        <v>371</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>54</v>
+        <v>464</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>54</v>
+        <v>464</v>
       </c>
     </row>
     <row r="260" ht="22.05" customHeight="1" spans="1:4">
       <c r="A260" s="3" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
     </row>
     <row r="261" ht="22.05" customHeight="1" spans="1:4">
       <c r="A261" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>468</v>
+        <v>371</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
     </row>
     <row r="262" ht="22.05" customHeight="1" spans="1:4">
       <c r="A262" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>478</v>
+        <v>371</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>198</v>
+        <v>493</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>198</v>
+        <v>493</v>
       </c>
     </row>
     <row r="263" ht="22.05" customHeight="1" spans="1:4">
       <c r="A263" s="2" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>141</v>
+        <v>464</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>141</v>
+        <v>464</v>
       </c>
     </row>
     <row r="264" ht="22.05" customHeight="1" spans="1:4">
       <c r="A264" s="3" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>158</v>
+        <v>371</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>267</v>
+        <v>493</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>267</v>
+        <v>493</v>
       </c>
     </row>
     <row r="265" ht="22.05" customHeight="1" spans="1:4">
       <c r="A265" s="2" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>158</v>
+        <v>497</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>267</v>
+        <v>498</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>267</v>
+        <v>498</v>
       </c>
     </row>
     <row r="266" ht="22.05" customHeight="1" spans="1:4">
       <c r="A266" s="3" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>158</v>
+        <v>500</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>267</v>
+        <v>501</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>267</v>
+        <v>501</v>
       </c>
     </row>
     <row r="267" ht="22.05" customHeight="1" spans="1:4">
       <c r="A267" s="2" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>158</v>
+        <v>503</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>267</v>
+        <v>504</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>267</v>
+        <v>504</v>
       </c>
     </row>
     <row r="268" ht="22.05" customHeight="1" spans="1:4">
       <c r="A268" s="3" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>158</v>
+        <v>503</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
     </row>
     <row r="269" ht="22.05" customHeight="1" spans="1:4">
       <c r="A269" s="2" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
     </row>
     <row r="270" ht="22.05" customHeight="1" spans="1:4">
       <c r="A270" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>293</v>
+        <v>504</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>293</v>
+        <v>504</v>
       </c>
     </row>
     <row r="271" ht="22.05" customHeight="1" spans="1:4">
       <c r="A271" s="2" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>371</v>
+        <v>503</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>464</v>
+        <v>504</v>
       </c>
     </row>
     <row r="272" ht="22.05" customHeight="1" spans="1:4">
       <c r="A272" s="3" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
     </row>
     <row r="273" ht="22.05" customHeight="1" spans="1:4">
       <c r="A273" s="2" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>371</v>
+        <v>513</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>464</v>
+        <v>151</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>464</v>
+        <v>151</v>
       </c>
     </row>
     <row r="274" ht="22.05" customHeight="1" spans="1:4">
       <c r="A274" s="3" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
     </row>
     <row r="275" ht="22.05" customHeight="1" spans="1:4">
       <c r="A275" s="2" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
     </row>
     <row r="276" ht="22.05" customHeight="1" spans="1:4">
       <c r="A276" s="3" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
     </row>
     <row r="277" ht="22.05" customHeight="1" spans="1:4">
       <c r="A277" s="2" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>498</v>
+        <v>246</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>498</v>
+        <v>246</v>
       </c>
     </row>
     <row r="278" ht="22.05" customHeight="1" spans="1:4">
       <c r="A278" s="3" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>500</v>
+        <v>374</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>501</v>
+        <v>246</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>501</v>
+        <v>246</v>
       </c>
     </row>
     <row r="279" ht="22.05" customHeight="1" spans="1:4">
       <c r="A279" s="2" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
     </row>
     <row r="280" ht="22.05" customHeight="1" spans="1:4">
       <c r="A280" s="3" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>504</v>
+        <v>186</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>504</v>
+        <v>186</v>
       </c>
     </row>
     <row r="281" ht="22.05" customHeight="1" spans="1:4">
       <c r="A281" s="2" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>503</v>
+        <v>158</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
     </row>
     <row r="282" ht="22.05" customHeight="1" spans="1:4">
       <c r="A282" s="3" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
     </row>
     <row r="283" ht="22.05" customHeight="1" spans="1:4">
       <c r="A283" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>503</v>
+        <v>463</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
     </row>
     <row r="284" ht="22.05" customHeight="1" spans="1:4">
       <c r="A284" s="3" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
     </row>
     <row r="285" ht="22.05" customHeight="1" spans="1:4">
       <c r="A285" s="2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
     </row>
     <row r="286" ht="22.05" customHeight="1" spans="1:4">
       <c r="A286" s="3" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>374</v>
+        <v>468</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
     <row r="287" ht="22.05" customHeight="1" spans="1:4">
       <c r="A287" s="2" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>374</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>515</v>
+        <v>466</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>515</v>
+        <v>466</v>
       </c>
     </row>
     <row r="288" ht="22.05" customHeight="1" spans="1:4">
       <c r="A288" s="3" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
     </row>
     <row r="289" ht="22.05" customHeight="1" spans="1:4">
       <c r="A289" s="2" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>374</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>246</v>
+        <v>540</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>246</v>
+        <v>540</v>
       </c>
     </row>
     <row r="290" ht="22.05" customHeight="1" spans="1:4">
       <c r="A290" s="3" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>374</v>
+        <v>542</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>246</v>
+        <v>543</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>246</v>
+        <v>543</v>
       </c>
     </row>
     <row r="291" ht="22.05" customHeight="1" spans="1:4">
       <c r="A291" s="2" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
     </row>
     <row r="292" ht="22.05" customHeight="1" spans="1:4">
       <c r="A292" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>186</v>
+        <v>546</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>186</v>
+        <v>546</v>
       </c>
     </row>
     <row r="293" ht="22.05" customHeight="1" spans="1:4">
       <c r="A293" s="2" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>158</v>
+        <v>549</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>525</v>
+        <v>318</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>525</v>
+        <v>318</v>
       </c>
     </row>
     <row r="294" ht="22.05" customHeight="1" spans="1:4">
       <c r="A294" s="3" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>527</v>
+        <v>150</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
     </row>
     <row r="295" ht="22.05" customHeight="1" spans="1:4">
       <c r="A295" s="2" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>463</v>
+        <v>158</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>530</v>
+        <v>246</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>530</v>
+        <v>246</v>
       </c>
     </row>
     <row r="296" ht="22.05" customHeight="1" spans="1:4">
       <c r="A296" s="3" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>530</v>
+        <v>92</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>530</v>
+        <v>92</v>
       </c>
     </row>
     <row r="297" ht="22.05" customHeight="1" spans="1:4">
       <c r="A297" s="2" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>267</v>
+        <v>349</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="298" ht="22.05" customHeight="1" spans="1:4">
       <c r="A298" s="3" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>468</v>
+        <v>559</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>535</v>
+        <v>349</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>535</v>
+        <v>349</v>
       </c>
     </row>
     <row r="299" ht="22.05" customHeight="1" spans="1:4">
       <c r="A299" s="2" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>466</v>
+        <v>88</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>466</v>
+        <v>88</v>
       </c>
     </row>
     <row r="300" ht="22.05" customHeight="1" spans="1:4">
       <c r="A300" s="3" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>538</v>
+        <v>88</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>538</v>
+        <v>88</v>
       </c>
     </row>
     <row r="301" ht="22.05" customHeight="1" spans="1:4">
       <c r="A301" s="2" t="s">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>374</v>
+        <v>563</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>540</v>
+        <v>92</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>540</v>
+        <v>92</v>
       </c>
     </row>
     <row r="302" ht="22.05" customHeight="1" spans="1:4">
       <c r="A302" s="3" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>542</v>
+        <v>56</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>543</v>
+        <v>50</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>543</v>
+        <v>50</v>
       </c>
     </row>
     <row r="303" ht="22.05" customHeight="1" spans="1:4">
       <c r="A303" s="2" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>545</v>
+        <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
     </row>
     <row r="304" ht="22.05" customHeight="1" spans="1:4">
       <c r="A304" s="3" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>545</v>
+        <v>56</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>546</v>
+        <v>54</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>546</v>
+        <v>54</v>
       </c>
     </row>
     <row r="305" ht="22.05" customHeight="1" spans="1:4">
       <c r="A305" s="2" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>318</v>
+        <v>570</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>318</v>
+        <v>570</v>
       </c>
     </row>
     <row r="306" ht="22.05" customHeight="1" spans="1:4">
       <c r="A306" s="3" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>150</v>
+        <v>459</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>551</v>
+        <v>37</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>551</v>
+        <v>37</v>
       </c>
     </row>
     <row r="307" ht="22.05" customHeight="1" spans="1:4">
       <c r="A307" s="2" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
     </row>
     <row r="308" ht="22.05" customHeight="1" spans="1:4">
       <c r="A308" s="3" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>554</v>
+        <v>158</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="309" ht="22.05" customHeight="1" spans="1:4">
       <c r="A309" s="2" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>556</v>
+        <v>158</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D309" s="6" t="s">
-        <v>557</v>
+        <v>99</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="310" ht="22.05" customHeight="1" spans="1:4">
       <c r="A310" s="3" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>559</v>
+        <v>158</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
     </row>
     <row r="311" ht="22.05" customHeight="1" spans="1:4">
       <c r="A311" s="2" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>429</v>
+        <v>379</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="312" ht="22.05" customHeight="1" spans="1:4">
       <c r="A312" s="3" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>429</v>
+        <v>158</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>88</v>
+        <v>566</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>88</v>
+        <v>566</v>
       </c>
     </row>
     <row r="313" ht="22.05" customHeight="1" spans="1:4">
       <c r="A313" s="2" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>563</v>
+        <v>158</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>92</v>
+        <v>579</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>92</v>
+        <v>579</v>
       </c>
     </row>
     <row r="314" ht="22.05" customHeight="1" spans="1:4">
       <c r="A314" s="3" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>50</v>
+        <v>579</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>50</v>
+        <v>579</v>
       </c>
     </row>
     <row r="315" ht="22.05" customHeight="1" spans="1:4">
       <c r="A315" s="2" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>10</v>
+        <v>582</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>566</v>
+        <v>68</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>566</v>
+        <v>68</v>
       </c>
     </row>
     <row r="316" ht="22.05" customHeight="1" spans="1:4">
       <c r="A316" s="3" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
     </row>
     <row r="317" ht="22.05" customHeight="1" spans="1:4">
       <c r="A317" s="2" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>569</v>
+        <v>10</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
     </row>
     <row r="318" ht="22.05" customHeight="1" spans="1:4">
       <c r="A318" s="3" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>459</v>
+        <v>587</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>37</v>
+        <v>275</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>37</v>
+        <v>275</v>
       </c>
     </row>
     <row r="319" ht="22.05" customHeight="1" spans="1:4">
       <c r="A319" s="2" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>158</v>
+        <v>589</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>163</v>
+        <v>590</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>163</v>
+        <v>590</v>
       </c>
     </row>
     <row r="320" ht="22.05" customHeight="1" spans="1:4">
       <c r="A320" s="3" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>158</v>
+        <v>589</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>99</v>
+        <v>590</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>99</v>
+        <v>590</v>
       </c>
     </row>
     <row r="321" ht="22.05" customHeight="1" spans="1:4">
       <c r="A321" s="2" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>158</v>
+        <v>593</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
     </row>
     <row r="322" ht="22.05" customHeight="1" spans="1:4">
       <c r="A322" s="3" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>158</v>
+        <v>595</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>267</v>
+        <v>349</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>267</v>
+        <v>349</v>
       </c>
     </row>
     <row r="323" ht="22.05" customHeight="1" spans="1:4">
       <c r="A323" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>379</v>
+        <v>589</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
     </row>
     <row r="324" ht="22.05" customHeight="1" spans="1:4">
       <c r="A324" s="3" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>158</v>
+        <v>598</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>566</v>
+        <v>88</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>566</v>
+        <v>88</v>
       </c>
     </row>
     <row r="325" ht="22.05" customHeight="1" spans="1:4">
       <c r="A325" s="2" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>579</v>
+        <v>349</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>579</v>
+        <v>349</v>
       </c>
     </row>
     <row r="326" ht="22.05" customHeight="1" spans="1:4">
       <c r="A326" s="3" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>579</v>
+        <v>382</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>579</v>
+        <v>382</v>
       </c>
     </row>
     <row r="327" ht="22.05" customHeight="1" spans="1:4">
       <c r="A327" s="2" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>582</v>
+        <v>10</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>68</v>
+        <v>304</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>68</v>
+        <v>304</v>
       </c>
     </row>
     <row r="328" ht="22.05" customHeight="1" spans="1:4">
       <c r="A328" s="3" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
     </row>
     <row r="329" ht="22.05" customHeight="1" spans="1:4">
       <c r="A329" s="2" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>585</v>
+        <v>173</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>585</v>
+        <v>173</v>
       </c>
     </row>
     <row r="330" ht="22.05" customHeight="1" spans="1:4">
       <c r="A330" s="3" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>587</v>
+        <v>10</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>275</v>
+        <v>605</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>275</v>
+        <v>605</v>
       </c>
     </row>
     <row r="331" ht="22.05" customHeight="1" spans="1:4">
       <c r="A331" s="2" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>589</v>
+        <v>10</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>590</v>
+        <v>68</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>590</v>
+        <v>68</v>
       </c>
     </row>
     <row r="332" ht="22.05" customHeight="1" spans="1:4">
       <c r="A332" s="3" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>589</v>
+        <v>10</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>590</v>
+        <v>45</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>590</v>
+        <v>45</v>
       </c>
     </row>
     <row r="333" ht="22.05" customHeight="1" spans="1:4">
       <c r="A333" s="2" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>593</v>
+        <v>33</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>300</v>
+        <v>609</v>
       </c>
     </row>
     <row r="334" ht="22.05" customHeight="1" spans="1:4">
       <c r="A334" s="3" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="335" ht="22.05" customHeight="1" spans="1:4">
       <c r="A335" s="2" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="336" ht="22.05" customHeight="1" spans="1:4">
       <c r="A336" s="3" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>598</v>
+        <v>95</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
     </row>
     <row r="337" ht="22.05" customHeight="1" spans="1:4">
       <c r="A337" s="2" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>10</v>
+        <v>615</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
     </row>
     <row r="338" ht="22.05" customHeight="1" spans="1:4">
       <c r="A338" s="3" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>67</v>
+        <v>615</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>382</v>
+        <v>159</v>
       </c>
     </row>
     <row r="339" ht="22.05" customHeight="1" spans="1:4">
       <c r="A339" s="2" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>10</v>
+        <v>615</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
     </row>
     <row r="340" ht="22.05" customHeight="1" spans="1:4">
       <c r="A340" s="3" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>10</v>
+        <v>384</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
     <row r="341" ht="22.05" customHeight="1" spans="1:4">
       <c r="A341" s="2" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="342" ht="22.05" customHeight="1" spans="1:4">
       <c r="A342" s="3" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>10</v>
+        <v>621</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
     </row>
     <row r="343" ht="22.05" customHeight="1" spans="1:4">
       <c r="A343" s="2" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>10</v>
+        <v>623</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>68</v>
+        <v>336</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>68</v>
+        <v>336</v>
       </c>
     </row>
     <row r="344" ht="22.05" customHeight="1" spans="1:4">
       <c r="A344" s="3" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>10</v>
+        <v>342</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
     </row>
     <row r="345" ht="22.05" customHeight="1" spans="1:4">
       <c r="A345" s="2" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>33</v>
+        <v>626</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>609</v>
+        <v>137</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>609</v>
+        <v>137</v>
       </c>
     </row>
     <row r="346" ht="22.05" customHeight="1" spans="1:4">
       <c r="A346" s="3" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>429</v>
+        <v>10</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>343</v>
+        <v>622</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>343</v>
+        <v>622</v>
       </c>
     </row>
     <row r="347" ht="22.05" customHeight="1" spans="1:4">
       <c r="A347" s="2" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>612</v>
+        <v>10</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>159</v>
+        <v>336</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>159</v>
+        <v>336</v>
       </c>
     </row>
     <row r="348" ht="22.05" customHeight="1" spans="1:4">
       <c r="A348" s="3" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
     </row>
     <row r="349" ht="22.05" customHeight="1" spans="1:4">
       <c r="A349" s="2" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>615</v>
+        <v>10</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>159</v>
+        <v>318</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>159</v>
+        <v>318</v>
       </c>
     </row>
     <row r="350" ht="22.05" customHeight="1" spans="1:4">
       <c r="A350" s="3" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>615</v>
+        <v>354</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
     </row>
     <row r="351" ht="22.05" customHeight="1" spans="1:4">
       <c r="A351" s="2" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>615</v>
+        <v>10</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="352" ht="22.05" customHeight="1" spans="1:4">
       <c r="A352" s="3" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>384</v>
+        <v>10</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
     </row>
     <row r="353" ht="22.05" customHeight="1" spans="1:4">
       <c r="A353" s="2" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>67</v>
+        <v>635</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>159</v>
+        <v>622</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>159</v>
+        <v>622</v>
       </c>
     </row>
     <row r="354" ht="22.05" customHeight="1" spans="1:4">
       <c r="A354" s="3" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>622</v>
+        <v>312</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>622</v>
+        <v>312</v>
       </c>
     </row>
     <row r="355" ht="22.05" customHeight="1" spans="1:4">
       <c r="A355" s="2" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>623</v>
+        <v>379</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>336</v>
+        <v>57</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>336</v>
+        <v>57</v>
       </c>
     </row>
     <row r="356" ht="22.05" customHeight="1" spans="1:4">
       <c r="A356" s="3" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>342</v>
+        <v>640</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>264</v>
+        <v>641</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>264</v>
+        <v>641</v>
       </c>
     </row>
     <row r="357" ht="22.05" customHeight="1" spans="1:4">
       <c r="A357" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>626</v>
+        <v>36</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="358" ht="22.05" customHeight="1" spans="1:4">
       <c r="A358" s="3" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>10</v>
+        <v>644</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>622</v>
+        <v>493</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>622</v>
+        <v>493</v>
       </c>
     </row>
     <row r="359" ht="22.05" customHeight="1" spans="1:4">
       <c r="A359" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>10</v>
+        <v>646</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>336</v>
+        <v>70</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>336</v>
+        <v>70</v>
       </c>
     </row>
     <row r="360" ht="22.05" customHeight="1" spans="1:4">
       <c r="A360" s="3" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>10</v>
+        <v>648</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>57</v>
+        <v>385</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>57</v>
+        <v>385</v>
       </c>
     </row>
     <row r="361" ht="22.05" customHeight="1" spans="1:4">
       <c r="A361" s="2" t="s">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>10</v>
+        <v>650</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>318</v>
+        <v>651</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>318</v>
+        <v>651</v>
       </c>
     </row>
     <row r="362" ht="22.05" customHeight="1" spans="1:4">
       <c r="A362" s="3" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>354</v>
+        <v>648</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>25</v>
+        <v>273</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>25</v>
+        <v>273</v>
       </c>
     </row>
     <row r="363" ht="22.05" customHeight="1" spans="1:4">
       <c r="A363" s="2" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>10</v>
+        <v>654</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>141</v>
+        <v>570</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>141</v>
+        <v>570</v>
       </c>
     </row>
     <row r="364" ht="22.05" customHeight="1" spans="1:4">
       <c r="A364" s="3" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>10</v>
+        <v>655</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>336</v>
+        <v>656</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>336</v>
+        <v>656</v>
       </c>
     </row>
     <row r="365" ht="22.05" customHeight="1" spans="1:4">
       <c r="A365" s="2" t="s">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>622</v>
+        <v>511</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>622</v>
+        <v>511</v>
       </c>
     </row>
     <row r="366" ht="22.05" customHeight="1" spans="1:4">
       <c r="A366" s="3" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
     </row>
     <row r="367" ht="22.05" customHeight="1" spans="1:4">
       <c r="A367" s="2" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>379</v>
+        <v>659</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
     </row>
     <row r="368" ht="22.05" customHeight="1" spans="1:4">
       <c r="A368" s="3" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
     </row>
     <row r="369" ht="22.05" customHeight="1" spans="1:4">
       <c r="A369" s="2" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="370" ht="22.05" customHeight="1" spans="1:4">
       <c r="A370" s="3" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
     </row>
     <row r="371" ht="22.05" customHeight="1" spans="1:4">
       <c r="A371" s="2" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>70</v>
+        <v>454</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>70</v>
+        <v>454</v>
       </c>
     </row>
     <row r="372" ht="22.05" customHeight="1" spans="1:4">
       <c r="A372" s="3" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>648</v>
+        <v>404</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>385</v>
+        <v>667</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>385</v>
+        <v>667</v>
       </c>
     </row>
     <row r="373" ht="22.05" customHeight="1" spans="1:4">
       <c r="A373" s="2" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>650</v>
+        <v>374</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>651</v>
+        <v>312</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>651</v>
+        <v>312</v>
       </c>
     </row>
     <row r="374" ht="22.05" customHeight="1" spans="1:4">
       <c r="A374" s="3" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>273</v>
+        <v>605</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>273</v>
+        <v>605</v>
       </c>
     </row>
     <row r="375" ht="22.05" customHeight="1" spans="1:4">
       <c r="A375" s="2" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>570</v>
+        <v>171</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>570</v>
+        <v>171</v>
       </c>
     </row>
     <row r="376" ht="22.05" customHeight="1" spans="1:4">
       <c r="A376" s="3" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>656</v>
+        <v>45</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>656</v>
+        <v>45</v>
       </c>
     </row>
     <row r="377" ht="22.05" customHeight="1" spans="1:4">
       <c r="A377" s="2" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>511</v>
+        <v>124</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>511</v>
+        <v>124</v>
       </c>
     </row>
     <row r="378" ht="22.05" customHeight="1" spans="1:4">
       <c r="A378" s="3" t="s">
-        <v>653</v>
+        <v>677</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>658</v>
+        <v>429</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>181</v>
+        <v>501</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>181</v>
+        <v>501</v>
       </c>
     </row>
     <row r="379" ht="22.05" customHeight="1" spans="1:4">
       <c r="A379" s="2" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
     </row>
     <row r="380" ht="22.05" customHeight="1" spans="1:4">
       <c r="A380" s="3" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>660</v>
+        <v>369</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>661</v>
+        <v>116</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>661</v>
+        <v>116</v>
       </c>
     </row>
     <row r="381" ht="22.05" customHeight="1" spans="1:4">
       <c r="A381" s="2" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
     </row>
     <row r="382" ht="22.05" customHeight="1" spans="1:4">
       <c r="A382" s="3" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>664</v>
+        <v>369</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>454</v>
+        <v>80</v>
       </c>
     </row>
     <row r="383" ht="22.05" customHeight="1" spans="1:4">
       <c r="A383" s="2" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>664</v>
+        <v>471</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>454</v>
+        <v>116</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>454</v>
+        <v>116</v>
       </c>
     </row>
     <row r="384" ht="22.05" customHeight="1" spans="1:4">
       <c r="A384" s="3" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>404</v>
+        <v>685</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>667</v>
+        <v>57</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>667</v>
+        <v>57</v>
       </c>
     </row>
     <row r="385" ht="22.05" customHeight="1" spans="1:4">
       <c r="A385" s="2" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>374</v>
+        <v>687</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>312</v>
+        <v>451</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>312</v>
+        <v>451</v>
       </c>
     </row>
     <row r="386" ht="22.05" customHeight="1" spans="1:4">
       <c r="A386" s="3" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>670</v>
+        <v>158</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>605</v>
+        <v>80</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>605</v>
+        <v>80</v>
       </c>
     </row>
     <row r="387" ht="22.05" customHeight="1" spans="1:4">
       <c r="A387" s="2" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>672</v>
+        <v>10</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
     </row>
     <row r="388" ht="22.05" customHeight="1" spans="1:4">
       <c r="A388" s="3" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>674</v>
+        <v>10</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="389" ht="22.05" customHeight="1" spans="1:4">
       <c r="A389" s="2" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>124</v>
+        <v>343</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>124</v>
+        <v>343</v>
       </c>
     </row>
     <row r="390" ht="22.05" customHeight="1" spans="1:4">
       <c r="A390" s="3" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>429</v>
+        <v>694</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>501</v>
+        <v>116</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>501</v>
+        <v>116</v>
       </c>
     </row>
     <row r="391" ht="22.05" customHeight="1" spans="1:4">
       <c r="A391" s="2" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>679</v>
+        <v>429</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>273</v>
+        <v>25</v>
       </c>
     </row>
     <row r="392" ht="22.05" customHeight="1" spans="1:4">
       <c r="A392" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>116</v>
+        <v>501</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>116</v>
+        <v>501</v>
       </c>
     </row>
     <row r="393" ht="22.05" customHeight="1" spans="1:4">
       <c r="A393" s="2" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
     </row>
     <row r="394" ht="22.05" customHeight="1" spans="1:4">
       <c r="A394" s="3" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="395" ht="22.05" customHeight="1" spans="1:4">
       <c r="A395" s="2" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>471</v>
+        <v>700</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
     </row>
     <row r="396" ht="22.05" customHeight="1" spans="1:4">
       <c r="A396" s="3" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>685</v>
+        <v>404</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="397" ht="22.05" customHeight="1" spans="1:4">
       <c r="A397" s="2" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>451</v>
+        <v>80</v>
       </c>
     </row>
     <row r="398" ht="22.05" customHeight="1" spans="1:4">
       <c r="A398" s="3" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>158</v>
+        <v>704</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>80</v>
+        <v>570</v>
       </c>
     </row>
     <row r="399" ht="22.05" customHeight="1" spans="1:4">
       <c r="A399" s="2" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>10</v>
+        <v>348</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
     </row>
     <row r="400" ht="22.05" customHeight="1" spans="1:4">
       <c r="A400" s="3" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>10</v>
+        <v>429</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="401" ht="22.05" customHeight="1" spans="1:4">
       <c r="A401" s="2" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>692</v>
+        <v>429</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>343</v>
+        <v>80</v>
       </c>
     </row>
     <row r="402" ht="22.05" customHeight="1" spans="1:4">
       <c r="A402" s="3" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>694</v>
+        <v>429</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row r="403" ht="22.05" customHeight="1" spans="1:4">
       <c r="A403" s="2" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>429</v>
+        <v>513</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="404" ht="22.05" customHeight="1" spans="1:4">
       <c r="A404" s="3" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>429</v>
+        <v>710</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>501</v>
+        <v>145</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>501</v>
+        <v>145</v>
       </c>
     </row>
     <row r="405" ht="22.05" customHeight="1" spans="1:4">
       <c r="A405" s="2" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>429</v>
+        <v>710</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="406" ht="22.05" customHeight="1" spans="1:4">
       <c r="A406" s="3" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>429</v>
+        <v>10</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>25</v>
+        <v>315</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>25</v>
+        <v>315</v>
       </c>
     </row>
     <row r="407" ht="22.05" customHeight="1" spans="1:4">
       <c r="A407" s="2" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="408" ht="22.05" customHeight="1" spans="1:4">
       <c r="A408" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>404</v>
+        <v>10</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="409" ht="22.05" customHeight="1" spans="1:4">
       <c r="A409" s="2" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
     </row>
     <row r="410" ht="22.05" customHeight="1" spans="1:4">
       <c r="A410" s="3" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>704</v>
+        <v>648</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>570</v>
+        <v>343</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>570</v>
+        <v>343</v>
       </c>
     </row>
     <row r="411" ht="22.05" customHeight="1" spans="1:4">
       <c r="A411" s="2" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>348</v>
+        <v>676</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="412" ht="22.05" customHeight="1" spans="1:4">
       <c r="A412" s="3" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>80</v>
+        <v>719</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>80</v>
+        <v>719</v>
       </c>
     </row>
     <row r="413" ht="22.05" customHeight="1" spans="1:4">
       <c r="A413" s="2" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>429</v>
+        <v>721</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
     </row>
     <row r="414" ht="22.05" customHeight="1" spans="1:4">
       <c r="A414" s="3" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>429</v>
+        <v>322</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>80</v>
+        <v>349</v>
       </c>
     </row>
     <row r="415" ht="22.05" customHeight="1" spans="1:4">
       <c r="A415" s="2" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>513</v>
+        <v>10</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>143</v>
+        <v>349</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>143</v>
+        <v>349</v>
       </c>
     </row>
     <row r="416" ht="22.05" customHeight="1" spans="1:4">
       <c r="A416" s="3" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>710</v>
+        <v>322</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
     </row>
     <row r="417" ht="22.05" customHeight="1" spans="1:4">
       <c r="A417" s="2" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="418" ht="22.05" customHeight="1" spans="1:4">
       <c r="A418" s="3" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>10</v>
+        <v>728</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>315</v>
+        <v>61</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>315</v>
+        <v>61</v>
       </c>
     </row>
     <row r="419" ht="22.05" customHeight="1" spans="1:4">
       <c r="A419" s="2" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>315</v>
+        <v>61</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>315</v>
+        <v>61</v>
       </c>
     </row>
     <row r="420" ht="22.05" customHeight="1" spans="1:4">
       <c r="A420" s="3" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>336</v>
+        <v>68</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>336</v>
+        <v>68</v>
       </c>
     </row>
     <row r="421" ht="22.05" customHeight="1" spans="1:4">
       <c r="A421" s="2" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>143</v>
+        <v>415</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>143</v>
+        <v>415</v>
       </c>
     </row>
     <row r="422" ht="22.05" customHeight="1" spans="1:4">
       <c r="A422" s="3" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>648</v>
+        <v>10</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>343</v>
+        <v>273</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>343</v>
+        <v>273</v>
       </c>
     </row>
     <row r="423" ht="22.05" customHeight="1" spans="1:4">
       <c r="A423" s="2" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>676</v>
+        <v>735</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="424" ht="22.05" customHeight="1" spans="1:4">
       <c r="A424" s="3" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>384</v>
+        <v>737</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>719</v>
+        <v>609</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>719</v>
+        <v>609</v>
       </c>
     </row>
     <row r="425" ht="22.05" customHeight="1" spans="1:4">
       <c r="A425" s="2" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>300</v>
+        <v>153</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>300</v>
+        <v>153</v>
       </c>
     </row>
     <row r="426" ht="22.05" customHeight="1" spans="1:4">
       <c r="A426" s="3" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>322</v>
+        <v>740</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>349</v>
+        <v>609</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>349</v>
+        <v>609</v>
       </c>
     </row>
     <row r="427" ht="22.05" customHeight="1" spans="1:4">
       <c r="A427" s="2" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>10</v>
+        <v>740</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
     </row>
     <row r="428" ht="22.05" customHeight="1" spans="1:4">
       <c r="A428" s="3" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>322</v>
+        <v>740</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="429" ht="22.05" customHeight="1" spans="1:4">
       <c r="A429" s="2" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
     </row>
     <row r="430" ht="22.05" customHeight="1" spans="1:4">
       <c r="A430" s="3" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
     </row>
     <row r="431" ht="22.05" customHeight="1" spans="1:4">
       <c r="A431" s="2" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>369</v>
+        <v>740</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>61</v>
+        <v>719</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>61</v>
+        <v>719</v>
       </c>
     </row>
     <row r="432" ht="22.05" customHeight="1" spans="1:4">
       <c r="A432" s="3" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>369</v>
+        <v>748</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
     </row>
     <row r="433" ht="22.05" customHeight="1" spans="1:4">
       <c r="A433" s="2" t="s">
-        <v>731</v>
+        <v>749</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>415</v>
+        <v>147</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>415</v>
+        <v>147</v>
       </c>
     </row>
     <row r="434" ht="22.05" customHeight="1" spans="1:4">
       <c r="A434" s="3" t="s">
-        <v>733</v>
+        <v>751</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>10</v>
+        <v>752</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
     </row>
     <row r="435" ht="22.05" customHeight="1" spans="1:4">
       <c r="A435" s="2" t="s">
-        <v>734</v>
+        <v>753</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>116</v>
+        <v>755</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>116</v>
+        <v>755</v>
       </c>
     </row>
     <row r="436" ht="22.05" customHeight="1" spans="1:4">
       <c r="A436" s="3" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>609</v>
+        <v>75</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>609</v>
+        <v>75</v>
       </c>
     </row>
     <row r="437" ht="22.05" customHeight="1" spans="1:4">
       <c r="A437" s="2" t="s">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>153</v>
+        <v>297</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>153</v>
+        <v>297</v>
       </c>
     </row>
     <row r="438" ht="22.05" customHeight="1" spans="1:4">
       <c r="A438" s="3" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>609</v>
+        <v>415</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>609</v>
+        <v>415</v>
       </c>
     </row>
     <row r="439" ht="22.05" customHeight="1" spans="1:4">
       <c r="A439" s="2" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>304</v>
+        <v>763</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>304</v>
+        <v>763</v>
       </c>
     </row>
     <row r="440" ht="22.05" customHeight="1" spans="1:4">
       <c r="A440" s="3" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>84</v>
+        <v>755</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>84</v>
+        <v>755</v>
       </c>
     </row>
     <row r="441" ht="22.05" customHeight="1" spans="1:4">
       <c r="A441" s="2" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
     </row>
     <row r="442" ht="22.05" customHeight="1" spans="1:4">
       <c r="A442" s="3" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>116</v>
+        <v>755</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>116</v>
+        <v>755</v>
       </c>
     </row>
     <row r="443" ht="22.05" customHeight="1" spans="1:4">
       <c r="A443" s="2" t="s">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>719</v>
+        <v>755</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>719</v>
+        <v>755</v>
       </c>
     </row>
     <row r="444" ht="22.05" customHeight="1" spans="1:4">
       <c r="A444" s="3" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>147</v>
+        <v>755</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="445" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A445" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="B445" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C445" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="446" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A446" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B446" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D446" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="447" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A447" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C447" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D447" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="448" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A448" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B448" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D448" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="449" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A449" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="C449" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="450" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A450" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="B450" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C450" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D450" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="451" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A451" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="452" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A452" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="B452" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D452" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="453" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A453" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D453" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="454" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A454" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="B454" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D454" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="455" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A455" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="C455" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D455" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="456" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A456" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="B456" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C456" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D456" s="3" t="s">
         <v>755</v>
       </c>
     </row>
@@ -10404,10 +10335,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10418,10 +10349,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -10432,10 +10363,10 @@
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C32" s="3">
         <v>840</v>
@@ -15844,7 +15775,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -16731,6 +16662,20 @@
       </c>
       <c r="D63" s="3">
         <v>1450</v>
+      </c>
+    </row>
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="3">
+        <v>350</v>
+      </c>
+      <c r="D64" s="3">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -16921,7 +16866,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20568" windowHeight="12840" activeTab="1"/>
+    <workbookView windowWidth="23505" windowHeight="12030"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="821">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2423,6 +2423,9 @@
   </si>
   <si>
     <t>乔雅登（韩版）/8号 质颜</t>
+  </si>
+  <si>
+    <t>瑞蓝（瑞典本土版）/6号</t>
   </si>
   <si>
     <t>艾莉薇大分子玻尿酸/韩版</t>
@@ -3546,7 +3549,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9778,7 +9781,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9920,10 +9923,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.5583333333333" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10335,10 +10338,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10349,10 +10352,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -10363,10 +10366,10 @@
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C32" s="3">
         <v>840</v>
@@ -10397,7 +10400,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10525,7 +10528,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10611,7 +10614,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10949,7 +10952,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -10959,11 +10962,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D113"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="29.775" customWidth="1"/>
+    <col min="2" max="2" width="15.225" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11185,10 +11188,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="7">
-        <v>1730</v>
+        <v>1700</v>
       </c>
       <c r="D16" s="7">
-        <v>1730</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
@@ -11360,1088 +11363,1088 @@
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
+    <row r="31" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
+    <row r="32" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
+    <row r="33" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
+    <row r="34" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
+    <row r="35" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
+    <row r="36" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
+    <row r="37" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A37" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
+    <row r="38" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A38" s="2" t="s">
+    <row r="39" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
+    <row r="40" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A40" s="2" t="s">
+    <row r="41" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="41" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
+    <row r="42" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="42" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A42" s="2" t="s">
+    <row r="43" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="43" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
+    <row r="44" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A44" s="2" t="s">
+    <row r="45" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
+    <row r="46" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="46" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A46" s="2" t="s">
+    <row r="47" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A47" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A47" s="3" t="s">
+    <row r="48" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A48" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="48" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A48" s="2" t="s">
+    <row r="49" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A49" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
+    <row r="50" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A50" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="50" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A50" s="2" t="s">
+    <row r="51" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A51" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
+    <row r="52" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A52" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="B52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="52" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A52" s="2" t="s">
+    <row r="53" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
+    <row r="54" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A54" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="B54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="54" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A54" s="2" t="s">
+    <row r="55" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A55" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="B55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="55" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
+    <row r="56" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A56" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="B56" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="56" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A56" s="2" t="s">
+    <row r="57" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A57" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="57" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
+    <row r="58" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A58" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A58" s="2" t="s">
+    <row r="59" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A59" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="59" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
+    <row r="60" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="60" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A60" s="2" t="s">
+    <row r="61" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A61" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
+    <row r="62" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A62" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="3" t="s">
+      <c r="B62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A62" s="2" t="s">
+    <row r="63" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A63" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="63" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
+    <row r="64" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A64" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="3" t="s">
+      <c r="B64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="64" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A64" s="2" t="s">
+    <row r="65" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A65" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="65" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A65" s="3" t="s">
+    <row r="66" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A66" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="B66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="66" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A66" s="2" t="s">
+    <row r="67" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A67" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="B67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="67" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A67" s="3" t="s">
+    <row r="68" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A68" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="B68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="68" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A68" s="2" t="s">
+    <row r="69" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A69" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="B69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="69" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A69" s="3" t="s">
+    <row r="70" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A70" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="B70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="70" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A70" s="2" t="s">
+    <row r="71" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A71" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="B71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="71" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A71" s="3" t="s">
+    <row r="72" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A72" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="B72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="72" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A72" s="2" t="s">
+    <row r="73" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A73" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="B73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A73" s="3" t="s">
+    <row r="74" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A74" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="B74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A74" s="2" t="s">
+    <row r="75" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A75" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="B75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="75" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A75" s="3" t="s">
+    <row r="76" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A76" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="B76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="76" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A76" s="2" t="s">
+    <row r="77" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A77" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="B77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="77" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A77" s="3" t="s">
+    <row r="78" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A78" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="B78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="78" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A78" s="2" t="s">
+    <row r="79" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A79" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="B79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="79" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A79" s="3" t="s">
+    <row r="80" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A80" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="B80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="80" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A80" s="2" t="s">
+    <row r="81" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A81" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="81" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A81" s="3" t="s">
+    <row r="82" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A82" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="B82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="82" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A82" s="2" t="s">
+    <row r="83" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A83" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="B83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="83" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A83" s="3" t="s">
+    <row r="84" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A84" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="B84" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="84" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A84" s="2" t="s">
+    <row r="85" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A85" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="B85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="85" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A85" s="3" t="s">
+    <row r="86" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A86" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="86" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A86" s="2" t="s">
+    <row r="87" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A87" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="87" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A87" s="3" t="s">
+    <row r="88" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A88" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="88" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A88" s="2" t="s">
+    <row r="89" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A89" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="89" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A89" s="3" t="s">
+    <row r="90" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A90" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="3" t="s">
+      <c r="B90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A90" s="2" t="s">
+    <row r="91" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A91" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="91" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A91" s="3" t="s">
+    <row r="92" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A92" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="3" t="s">
+      <c r="B92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="92" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A92" s="2" t="s">
+    <row r="93" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A93" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="93" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A93" s="3" t="s">
+    <row r="94" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A94" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="3" t="s">
+      <c r="B94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="94" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A94" s="2" t="s">
+    <row r="95" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A95" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D95" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="95" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A95" s="3" t="s">
+    <row r="96" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A96" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D96" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="96" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A96" s="2" t="s">
+    <row r="97" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A97" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D97" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="97" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A97" s="3" t="s">
+    <row r="98" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A98" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="3" t="s">
+      <c r="B98" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="98" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A98" s="2" t="s">
+    <row r="99" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A99" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="99" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A99" s="3" t="s">
+    <row r="100" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A100" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="B100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="100" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A100" s="2" t="s">
+    <row r="101" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A101" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="B101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="101" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A101" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="102" ht="22.05" customHeight="1" spans="1:4">
       <c r="A102" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="103" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A103" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="3" t="s">
+      <c r="B103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="103" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A103" s="2" t="s">
+    <row r="104" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A104" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="104" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A104" s="3" t="s">
+    <row r="105" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A105" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="3" t="s">
+      <c r="B105" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="105" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A105" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="2">
-        <v>160</v>
-      </c>
-      <c r="D105" s="2">
-        <v>160</v>
-      </c>
-    </row>
     <row r="106" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="2">
@@ -12452,10 +12455,10 @@
       </c>
     </row>
     <row r="107" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="2">
@@ -12466,56 +12469,70 @@
       </c>
     </row>
     <row r="108" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C108" s="3">
+      <c r="B108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="2">
+        <v>160</v>
+      </c>
+      <c r="D108" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="109" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A109" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="3">
         <v>250</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D109" s="3">
         <v>250</v>
       </c>
     </row>
-    <row r="109" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A109" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="2">
+    <row r="110" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A110" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="2">
         <v>260</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D110" s="2">
         <v>260</v>
       </c>
     </row>
-    <row r="110" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-    </row>
     <row r="111" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
     </row>
     <row r="113" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+    </row>
+    <row r="114" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12527,10 +12544,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="44.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="34.775" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12760,10 +12777,10 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C17" s="2">
         <v>340</v>
@@ -12774,10 +12791,10 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C18" s="2">
         <v>390</v>
@@ -12788,10 +12805,10 @@
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="C19" s="2">
         <v>390</v>
@@ -12802,10 +12819,10 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C20" s="2">
         <v>2300</v>
@@ -12816,7 +12833,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
@@ -12830,10 +12847,10 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C22" s="2">
         <v>1060</v>
@@ -12858,7 +12875,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15212,7 +15229,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15256,7 +15273,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15776,7 +15793,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16638,10 +16655,10 @@
     </row>
     <row r="62" ht="22.05" customHeight="1" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C62" s="2">
         <v>1100</v>
@@ -16652,10 +16669,10 @@
     </row>
     <row r="63" ht="22.05" customHeight="1" spans="1:4">
       <c r="A63" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C63" s="3">
         <v>1450</v>
@@ -16666,7 +16683,7 @@
     </row>
     <row r="64" ht="22.05" customHeight="1" spans="1:4">
       <c r="A64" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>10</v>
@@ -16688,7 +16705,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16746,7 +16763,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16866,7 +16883,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23505" windowHeight="12030"/>
+    <workbookView windowWidth="23505" windowHeight="12030" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -16889,10 +16889,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="4">
-        <v>1500</v>
+        <v>3660</v>
       </c>
       <c r="D9" s="2">
-        <v>1500</v>
+        <v>3660</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3692" uniqueCount="821">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -16762,7 +16762,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -16895,6 +16895,20 @@
         <v>3660</v>
       </c>
     </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1790</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3692" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3692" uniqueCount="822">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2489,6 +2489,9 @@
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
+  </si>
+  <si>
+    <t>伊妍仕/少女针单支(欧版)</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -10338,10 +10341,10 @@
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C30" s="3">
         <v>470</v>
@@ -10352,10 +10355,10 @@
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C31" s="3">
         <v>180</v>
@@ -10366,10 +10369,10 @@
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C32" s="3">
         <v>840</v>
@@ -16897,7 +16900,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>314</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2491,7 +2491,7 @@
     <t>伊妍仕/少女针(欧版)</t>
   </si>
   <si>
-    <t>伊妍仕/少女针单支(欧版)</t>
+    <t xml:space="preserve"> 单支 伊妍仕/少女针(欧版)</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2488,10 +2488,10 @@
     <t>韩版肤丽美</t>
   </si>
   <si>
+    <t xml:space="preserve"> 单支 伊妍仕/少女针(欧版)</t>
+  </si>
+  <si>
     <t>伊妍仕/少女针(欧版)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 单支 伊妍仕/少女针(欧版)</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -16765,7 +16765,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -16829,73 +16829,73 @@
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1790</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A9" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4">
-        <v>3660</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3660</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -16903,15 +16903,16 @@
         <v>816</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4">
-        <v>1790</v>
+        <v>3660</v>
       </c>
       <c r="D10" s="2">
-        <v>1790</v>
-      </c>
-    </row>
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2488,7 +2488,7 @@
     <t>韩版肤丽美</t>
   </si>
   <si>
-    <t xml:space="preserve"> 单支 伊妍仕/少女针(欧版)</t>
+    <t xml:space="preserve"> 伊妍仕单支/少女针(欧版)</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23505" windowHeight="12030" activeTab="8"/>
+    <workbookView windowWidth="20568" windowHeight="12840" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3692" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="800">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2353,69 +2353,6 @@
     <t>铂鱼（铂金三文鱼）/海葡萄</t>
   </si>
   <si>
-    <t>乔雅登/雅致</t>
-  </si>
-  <si>
-    <t>¥3,230</t>
-  </si>
-  <si>
-    <t>乔雅登/极致</t>
-  </si>
-  <si>
-    <t>¥5,500</t>
-  </si>
-  <si>
-    <t>乔雅登/盈致</t>
-  </si>
-  <si>
-    <t>乔雅登/丰颜</t>
-  </si>
-  <si>
-    <t>¥5,600</t>
-  </si>
-  <si>
-    <t>乔雅登/缇颜</t>
-  </si>
-  <si>
-    <t>¥5,200</t>
-  </si>
-  <si>
-    <t>乔雅登/质颜</t>
-  </si>
-  <si>
-    <t>¥5,100</t>
-  </si>
-  <si>
-    <t>乔雅登/朔颜</t>
-  </si>
-  <si>
-    <t>¥5,800</t>
-  </si>
-  <si>
-    <t>乔雅登/越致</t>
-  </si>
-  <si>
-    <t>乔雅登（法国本土版）/2号</t>
-  </si>
-  <si>
-    <t>0.55ml*2支/盒</t>
-  </si>
-  <si>
-    <t>¥860</t>
-  </si>
-  <si>
-    <t>乔雅登（法国本土版）/3号</t>
-  </si>
-  <si>
-    <t>乔雅登（法国本土版）/4号</t>
-  </si>
-  <si>
-    <t>乔雅登（法国本土版）/5号</t>
-  </si>
-  <si>
-    <t>¥1,600</t>
-  </si>
-  <si>
     <t>乔雅登（韩版）/5号 丰颜</t>
   </si>
   <si>
@@ -2486,9 +2423,6 @@
   </si>
   <si>
     <t>韩版肤丽美</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 伊妍仕单支/少女针(欧版)</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
@@ -2546,7 +2480,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF27AE60"/>
+      <color rgb="FFFF4757"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2554,7 +2488,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF4757"/>
+      <color rgb="FF27AE60"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3179,7 +3113,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3196,13 +3130,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3552,7 +3483,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -3579,10 +3510,10 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>1850</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1850</v>
       </c>
     </row>
@@ -4982,7 +4913,7 @@
       <c r="C102" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="7" t="s">
         <v>191</v>
       </c>
     </row>
@@ -7712,7 +7643,7 @@
       <c r="C297" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D297" s="6" t="s">
+      <c r="D297" s="5" t="s">
         <v>557</v>
       </c>
     </row>
@@ -9784,7 +9715,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9925,11 +9856,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9948,450 +9879,58 @@
       </c>
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>290</v>
+      <c r="A2" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C2" s="3">
+        <v>470</v>
+      </c>
+      <c r="D2" s="3">
+        <v>470</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>797</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>423</v>
+        <v>798</v>
+      </c>
+      <c r="C3" s="3">
+        <v>180</v>
+      </c>
+      <c r="D3" s="3">
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
+      <c r="A4" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C4" s="3">
+        <v>840</v>
+      </c>
+      <c r="D4" s="3">
+        <v>840</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="C30" s="3">
-        <v>470</v>
-      </c>
-      <c r="D30" s="3">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="C31" s="3">
-        <v>180</v>
-      </c>
-      <c r="D31" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="C32" s="3">
-        <v>840</v>
-      </c>
-      <c r="D32" s="3">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10403,7 +9942,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10531,7 +10070,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10617,7 +10156,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10955,7 +10494,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -10965,11 +10504,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D114"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.775" customWidth="1"/>
-    <col min="2" max="2" width="15.225" customWidth="1"/>
+    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10988,1554 +10527,224 @@
       </c>
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1500</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>772</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>773</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1700</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>329</v>
+      <c r="C4" s="6">
+        <v>1240</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1240</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>775</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>776</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>776</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>777</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>778</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>778</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>779</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>780</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>780</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>781</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>782</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>782</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>780</v>
+      <c r="A9" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>786</v>
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>201</v>
+      <c r="A11" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>160</v>
+      </c>
+      <c r="D11" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>201</v>
+      <c r="A12" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>160</v>
+      </c>
+      <c r="D12" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>790</v>
+      <c r="A13" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>160</v>
+      </c>
+      <c r="D13" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
+      <c r="A14" s="3" t="s">
+        <v>777</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1850</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1850</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>250</v>
+      </c>
+      <c r="D14" s="3">
+        <v>250</v>
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1500</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1500</v>
+      <c r="A15" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2">
+        <v>260</v>
+      </c>
+      <c r="D15" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1700</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1700</v>
-      </c>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1240</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1240</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A37" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A38" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A46" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A47" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A49" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A51" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A55" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="57" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="60" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A66" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="67" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="68" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="69" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A70" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="71" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A71" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="72" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A72" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A73" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A74" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A75" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="76" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A76" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="77" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A77" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="78" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A78" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="79" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A79" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="80" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A80" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="81" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="82" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A82" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="83" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A83" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="84" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A84" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="85" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A85" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="86" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A86" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="87" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A87" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A88" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="89" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A89" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="90" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A91" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="92" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A92" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="93" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A93" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="94" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="95" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A95" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="96" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A96" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="97" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A97" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="98" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A98" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="99" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A99" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="100" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A100" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="101" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A101" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="102" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A102" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="103" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A103" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="104" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A104" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="105" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A105" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="106" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A106" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106" s="2">
-        <v>160</v>
-      </c>
-      <c r="D106" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="107" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A107" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="2">
-        <v>160</v>
-      </c>
-      <c r="D107" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="108" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A108" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C108" s="2">
-        <v>160</v>
-      </c>
-      <c r="D108" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="109" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A109" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="3">
-        <v>250</v>
-      </c>
-      <c r="D109" s="3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="110" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A110" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="2">
-        <v>260</v>
-      </c>
-      <c r="D110" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="111" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-    </row>
-    <row r="112" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-    </row>
-    <row r="113" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-    </row>
-    <row r="114" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12546,11 +10755,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="34.775" customWidth="1"/>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12568,305 +10777,95 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
+    <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>779</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
+        <v>780</v>
+      </c>
+      <c r="C2" s="2">
+        <v>340</v>
+      </c>
+      <c r="D2" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C3" s="2">
+        <v>390</v>
+      </c>
+      <c r="D3" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>244</v>
+        <v>783</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+        <v>782</v>
+      </c>
+      <c r="C4" s="2">
+        <v>390</v>
+      </c>
+      <c r="D4" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>249</v>
+        <v>786</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="C17" s="2">
-        <v>340</v>
-      </c>
-      <c r="D17" s="2">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C18" s="2">
-        <v>390</v>
-      </c>
-      <c r="D18" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C19" s="2">
-        <v>390</v>
-      </c>
-      <c r="D19" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2300</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="C6" s="2">
         <v>1000</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D6" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" ht="21" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="C22" s="2">
+    <row r="7" ht="21" customHeight="1" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" s="2">
         <v>1060</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D7" s="2">
         <v>1060</v>
       </c>
     </row>
-    <row r="23" ht="21" customHeight="1" spans="1:4">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+    <row r="8" ht="21" customHeight="1" spans="1:4">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12878,7 +10877,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -14616,7 +12615,7 @@
       <c r="C124" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="5" t="s">
         <v>557</v>
       </c>
     </row>
@@ -15232,7 +13231,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15276,7 +13275,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15795,8 +13794,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -15818,883 +13817,43 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>789</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>790</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1100</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>791</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>124</v>
+        <v>792</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1450</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1450</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="37" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A38" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="39" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="40" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A40" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A42" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="43" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="44" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A44" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="46" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A46" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="47" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A48" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="49" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A50" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="52" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A52" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="54" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A54" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="55" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="56" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A56" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="58" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="59" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1100</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="63" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="C63" s="3">
-        <v>1450</v>
-      </c>
-      <c r="D63" s="3">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="64" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="3">
+      <c r="C4" s="3">
         <v>350</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D4" s="3">
         <v>350</v>
       </c>
     </row>
@@ -16708,7 +13867,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16765,8 +13924,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -16786,133 +13945,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>794</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1790</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4">
-        <v>3660</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3660</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
+      <c r="C2" s="4">
+        <v>1850</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20568" windowHeight="12840" activeTab="10"/>
+    <workbookView windowWidth="20568" windowHeight="12840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -10562,10 +10562,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>1240</v>
+        <v>1700</v>
       </c>
       <c r="D4" s="6">
-        <v>1240</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20568" windowHeight="12840" activeTab="1"/>
+    <workbookView windowWidth="19764" windowHeight="11304" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -10562,10 +10562,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>1700</v>
+        <v>1520</v>
       </c>
       <c r="D4" s="6">
-        <v>1700</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19764" windowHeight="11304" activeTab="1"/>
+    <workbookView windowWidth="19775" windowHeight="11304" firstSheet="5" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="复合酸" sheetId="12" r:id="rId12"/>
     <sheet name="琼脂糖" sheetId="13" r:id="rId13"/>
     <sheet name="医用敷贴" sheetId="14" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="15" r:id="rId15"/>
+    <sheet name="删除" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="801">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2441,6 +2441,9 @@
   </si>
   <si>
     <t>韩版Babyface皮贴骨</t>
+  </si>
+  <si>
+    <t>瑞德喜(德国）/微晶瓷</t>
   </si>
 </sst>
 </file>
@@ -10493,9 +10496,23 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.8" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19775" windowHeight="11304" firstSheet="5" activeTab="14"/>
+    <workbookView windowWidth="19775" windowHeight="11304" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="800">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2365,15 +2365,6 @@
     <t>瑞蓝（瑞典本土版）/6号</t>
   </si>
   <si>
-    <t>艾莉薇大分子玻尿酸/韩版</t>
-  </si>
-  <si>
-    <t>艾莉薇中分子玻尿酸/韩版</t>
-  </si>
-  <si>
-    <t>艾莉薇小分子玻尿酸/韩版</t>
-  </si>
-  <si>
     <t>姣兰 / 经典玻尿酸</t>
   </si>
   <si>
@@ -2444,6 +2435,12 @@
   </si>
   <si>
     <t>瑞德喜(德国）/微晶瓷</t>
+  </si>
+  <si>
+    <t>伊妍仕(荷兰）/ELLANSE--S</t>
+  </si>
+  <si>
+    <t>伊妍仕(荷兰）/ELLANSE--M</t>
   </si>
 </sst>
 </file>
@@ -9883,10 +9880,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C2" s="3">
         <v>470</v>
@@ -9897,10 +9894,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C3" s="3">
         <v>180</v>
@@ -9911,10 +9908,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C4" s="3">
         <v>840</v>
@@ -10158,7 +10155,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -10179,314 +10176,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10496,20 +10185,30 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>800</v>
+        <v>797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>799</v>
       </c>
     </row>
   </sheetData>
@@ -10521,7 +10220,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
@@ -10551,10 +10250,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="6">
-        <v>1500</v>
+        <v>15500</v>
       </c>
       <c r="D2" s="6">
-        <v>1500</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
@@ -10579,10 +10278,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>1520</v>
+        <v>1350</v>
       </c>
       <c r="D4" s="6">
-        <v>1520</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
@@ -10670,98 +10369,56 @@
       </c>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="2">
-        <v>160</v>
-      </c>
-      <c r="D11" s="2">
-        <v>160</v>
+      <c r="C11" s="3">
+        <v>250</v>
+      </c>
+      <c r="D11" s="3">
+        <v>250</v>
       </c>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="2">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="D12" s="2">
-        <v>160</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2">
-        <v>160</v>
-      </c>
-      <c r="D13" s="2">
-        <v>160</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3">
-        <v>250</v>
-      </c>
-      <c r="D14" s="3">
-        <v>250</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2">
-        <v>260</v>
-      </c>
-      <c r="D15" s="2">
-        <v>260</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10796,10 +10453,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C2" s="2">
         <v>340</v>
@@ -10810,10 +10467,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C3" s="2">
         <v>390</v>
@@ -10824,10 +10481,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C4" s="2">
         <v>390</v>
@@ -10838,10 +10495,10 @@
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C5" s="2">
         <v>2300</v>
@@ -10852,7 +10509,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>33</v>
@@ -10866,10 +10523,10 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C7" s="2">
         <v>1060</v>
@@ -13834,10 +13491,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C2" s="2">
         <v>1100</v>
@@ -13848,10 +13505,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C3" s="3">
         <v>1450</v>
@@ -13862,7 +13519,7 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -13964,7 +13621,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19775" windowHeight="11304" activeTab="1"/>
+    <workbookView windowWidth="19895" windowHeight="11100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -10250,7 +10250,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="6">
-        <v>15500</v>
+        <v>1550</v>
       </c>
       <c r="D2" s="6">
         <v>1550</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10264,10 +10264,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="6">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="D3" s="6">
-        <v>1700</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19895" windowHeight="11100" activeTab="1"/>
+    <workbookView windowWidth="20663" windowHeight="10740" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="800">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -10558,2342 +10558,1006 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>108</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>147</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>151</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>300</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>349</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>349</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>372</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>190</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>264</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>277</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A38" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>400</v>
-      </c>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A40" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>400</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A42" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>300</v>
-      </c>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A44" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>385</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>385</v>
-      </c>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A46" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>385</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="47" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>385</v>
-      </c>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A48" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>385</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
     </row>
     <row r="49" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A50" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>415</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
     </row>
     <row r="51" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>139</v>
-      </c>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A52" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
     </row>
     <row r="53" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A54" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
     </row>
     <row r="55" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>426</v>
-      </c>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A56" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
     </row>
     <row r="57" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>430</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>275</v>
-      </c>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
     </row>
     <row r="59" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>433</v>
-      </c>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>440</v>
-      </c>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>443</v>
-      </c>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
     </row>
     <row r="63" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>445</v>
-      </c>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>440</v>
-      </c>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
     </row>
     <row r="65" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A65" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>443</v>
-      </c>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>445</v>
-      </c>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
     </row>
     <row r="67" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>440</v>
-      </c>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>451</v>
-      </c>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
     </row>
     <row r="69" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>246</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A70" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A71" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A72" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>457</v>
-      </c>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
     </row>
     <row r="73" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
     </row>
     <row r="74" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A74" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>464</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
     </row>
     <row r="75" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A75" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>466</v>
-      </c>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A76" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>469</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
     </row>
     <row r="77" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A77" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
     </row>
     <row r="78" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A78" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>474</v>
-      </c>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
     </row>
     <row r="79" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A79" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>476</v>
-      </c>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
     </row>
     <row r="80" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A80" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>198</v>
-      </c>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
     </row>
     <row r="81" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
     </row>
     <row r="82" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A82" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
     </row>
     <row r="83" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A83" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
     </row>
     <row r="84" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A84" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
     </row>
     <row r="85" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A85" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A86" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>457</v>
-      </c>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
     </row>
     <row r="87" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A87" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>486</v>
-      </c>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
     </row>
     <row r="88" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A88" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
     </row>
     <row r="89" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A89" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>464</v>
-      </c>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
     </row>
     <row r="90" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A90" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>490</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
     </row>
     <row r="91" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>464</v>
-      </c>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
     </row>
     <row r="92" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A92" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>464</v>
-      </c>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
     </row>
     <row r="93" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A93" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>493</v>
-      </c>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
     </row>
     <row r="94" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A94" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>498</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
     </row>
     <row r="95" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A95" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>504</v>
-      </c>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A96" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>504</v>
-      </c>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
     </row>
     <row r="97" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A97" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>504</v>
-      </c>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A98" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>504</v>
-      </c>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
     </row>
     <row r="99" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A99" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>504</v>
-      </c>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A100" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>511</v>
-      </c>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
     </row>
     <row r="101" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A101" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>151</v>
-      </c>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A102" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>515</v>
-      </c>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
     </row>
     <row r="103" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A103" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>515</v>
-      </c>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A104" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>515</v>
-      </c>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
     </row>
     <row r="105" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A105" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>246</v>
-      </c>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A106" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>246</v>
-      </c>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
     </row>
     <row r="107" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A107" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>521</v>
-      </c>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A108" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
     </row>
     <row r="109" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A109" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>525</v>
-      </c>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A110" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>528</v>
-      </c>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
     </row>
     <row r="111" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A111" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>530</v>
-      </c>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A112" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>530</v>
-      </c>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
     </row>
     <row r="113" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
     </row>
     <row r="114" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A114" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>535</v>
-      </c>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
     </row>
     <row r="115" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A115" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>466</v>
-      </c>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A116" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>538</v>
-      </c>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
     </row>
     <row r="117" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A117" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>540</v>
-      </c>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
     </row>
     <row r="118" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A118" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>543</v>
-      </c>
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
     </row>
     <row r="119" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A119" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>546</v>
-      </c>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
     </row>
     <row r="120" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A120" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>546</v>
-      </c>
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
     </row>
     <row r="121" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A121" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>318</v>
-      </c>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
     </row>
     <row r="122" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A122" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>551</v>
-      </c>
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
     </row>
     <row r="123" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A123" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>246</v>
-      </c>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
     </row>
     <row r="124" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A124" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>557</v>
-      </c>
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="5"/>
     </row>
     <row r="125" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A125" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>349</v>
-      </c>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
     </row>
     <row r="126" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A126" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
     </row>
     <row r="127" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A127" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>88</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
     </row>
     <row r="128" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A128" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
     </row>
     <row r="129" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A129" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
     </row>
     <row r="130" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A130" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
     </row>
     <row r="131" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A131" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
     </row>
     <row r="132" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A132" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
     </row>
     <row r="133" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A133" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
     </row>
     <row r="134" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A134" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
     </row>
     <row r="135" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A135" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>566</v>
-      </c>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
     </row>
     <row r="136" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A136" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>579</v>
-      </c>
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A137" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>579</v>
-      </c>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
     </row>
     <row r="138" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A138" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
     </row>
     <row r="139" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A139" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>275</v>
-      </c>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
     </row>
     <row r="140" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A140" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>609</v>
-      </c>
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
     </row>
     <row r="141" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A141" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>343</v>
-      </c>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
     </row>
     <row r="142" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A142" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
     </row>
     <row r="143" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A143" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
     </row>
     <row r="144" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A144" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
     </row>
     <row r="145" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A145" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
     </row>
     <row r="146" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A146" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A147" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>147</v>
-      </c>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
     </row>
     <row r="148" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A148" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
     </row>
     <row r="149" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A149" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>667</v>
-      </c>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
     </row>
     <row r="150" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A150" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>451</v>
-      </c>
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
     </row>
     <row r="151" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A151" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
     </row>
     <row r="152" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A152" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
     </row>
     <row r="153" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A153" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>501</v>
-      </c>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
     </row>
     <row r="154" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A154" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A155" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
     </row>
     <row r="156" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A156" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A157" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
     </row>
     <row r="158" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A158" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
     </row>
     <row r="159" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A159" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
     </row>
     <row r="160" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A160" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
     </row>
     <row r="161" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A161" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
     </row>
     <row r="162" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A162" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
     </row>
     <row r="163" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A163" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A164" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>315</v>
-      </c>
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
     </row>
     <row r="165" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A165" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
     </row>
     <row r="166" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A166" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A167" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>415</v>
-      </c>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12904,8 +11568,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -12923,20 +11587,6 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -12948,7 +11598,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -12967,496 +11617,6 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -13627,10 +11787,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>1850</v>
+        <v>2250</v>
       </c>
       <c r="D2" s="4">
-        <v>1850</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="801">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2417,6 +2417,9 @@
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
+  </si>
+  <si>
+    <t>1ml*1支</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -9880,10 +9883,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C2" s="3">
         <v>470</v>
@@ -9894,10 +9897,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C3" s="3">
         <v>180</v>
@@ -9908,10 +9911,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C4" s="3">
         <v>840</v>
@@ -10198,17 +10201,17 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -11787,13 +11790,26 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>2250</v>
+        <v>2550</v>
       </c>
       <c r="D2" s="4">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11790,10 +11790,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>2550</v>
+        <v>2750</v>
       </c>
       <c r="D2" s="4">
-        <v>2550</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11790,10 +11790,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>2750</v>
+        <v>3350</v>
       </c>
       <c r="D2" s="4">
-        <v>2750</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20663" windowHeight="10740" firstSheet="5" activeTab="8"/>
+    <workbookView windowWidth="20663" windowHeight="10740" firstSheet="5" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="801">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -11631,8 +11631,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11681,18 +11681,66 @@
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>350</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>350</v>
       </c>
+    </row>
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3750</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1120</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="801">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -11737,10 +11737,18 @@
       </c>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1730</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1730</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -23,25 +23,12 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId14"/>
     <sheet name="删除" sheetId="15" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2401,6 +2388,9 @@
     <t>（含麻）1.5ml/支/盒</t>
   </si>
   <si>
+    <t>韩版肤丽美</t>
+  </si>
+  <si>
     <t>弗缦 Pro/0.5版</t>
   </si>
   <si>
@@ -2411,9 +2401,6 @@
   </si>
   <si>
     <t>1ml/支</t>
-  </si>
-  <si>
-    <t>韩版肤丽美</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
@@ -2449,13 +2436,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -2497,9 +2484,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2513,34 +2514,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2553,7 +2531,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2561,7 +2539,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2575,7 +2553,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -2591,8 +2568,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2613,10 +2591,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2627,15 +2606,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2662,7 +2649,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2674,169 +2823,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2871,6 +2858,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2895,30 +2891,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2930,6 +2902,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2951,15 +2932,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -2968,151 +2940,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3142,61 +3129,188 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -3479,14 +3593,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9715,10 +9830,10 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9857,13 +9972,13 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9942,10 +10057,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10070,10 +10185,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10156,10 +10271,10 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10186,15 +10301,15 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="15.4" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10215,19 +10330,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="29.7767857142857" customWidth="1"/>
+    <col min="2" max="2" width="15.2232142857143" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10430,13 +10545,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10551,10 +10666,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11569,10 +11684,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11599,10 +11714,10 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11629,10 +11744,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11657,97 +11772,97 @@
         <v>786</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>787</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="D2" s="2">
-        <v>1100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>788</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>789</v>
+        <v>175</v>
       </c>
       <c r="C3" s="3">
-        <v>1450</v>
+        <v>3750</v>
       </c>
       <c r="D3" s="3">
-        <v>1450</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>790</v>
+        <v>729</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
       <c r="C4" s="2">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="D4" s="2">
-        <v>350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>730</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3">
-        <v>3750</v>
+        <v>1120</v>
       </c>
       <c r="D5" s="3">
-        <v>3750</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1120</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1730</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="7" ht="15.4" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="8" ht="15.4" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>789</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>790</v>
       </c>
       <c r="C8" s="3">
-        <v>1730</v>
+        <v>1450</v>
       </c>
       <c r="D8" s="3">
-        <v>1730</v>
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
@@ -11757,10 +11872,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11815,10 +11930,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11838,7 +11953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="15.4" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>791</v>
       </c>
@@ -11852,7 +11967,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="15.4" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>791</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20663" windowHeight="10740" firstSheet="5" activeTab="6"/>
+    <workbookView windowWidth="27660" windowHeight="13044" firstSheet="5" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,25 @@
     <sheet name="医用敷贴" sheetId="14" r:id="rId14"/>
     <sheet name="删除" sheetId="15" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="802">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2373,36 +2386,36 @@
     <t>冰月岚 / 粉金少女针</t>
   </si>
   <si>
-    <t>塑颜萃 Sculptra（欧版）</t>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
+  </si>
+  <si>
+    <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>塑然雅/塑颜萃 Sculptra（欧版）</t>
   </si>
   <si>
     <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
   </si>
   <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
-  </si>
-  <si>
-    <t>芮得怡（瑞德喜）/面部填充剂（欧版深蓝）</t>
-  </si>
-  <si>
-    <t>（含麻）1.5ml/支/盒</t>
+    <t>弗缦 Pro/0.5版</t>
+  </si>
+  <si>
+    <t>0.5ml/支</t>
+  </si>
+  <si>
+    <t>弗缦 Pro/1.0版</t>
+  </si>
+  <si>
+    <t>1ml/支</t>
   </si>
   <si>
     <t>韩版肤丽美</t>
   </si>
   <si>
-    <t>弗缦 Pro/0.5版</t>
-  </si>
-  <si>
-    <t>0.5ml/支</t>
-  </si>
-  <si>
-    <t>弗缦 Pro/1.0版</t>
-  </si>
-  <si>
-    <t>1ml/支</t>
-  </si>
-  <si>
     <t>伊妍仕/少女针(欧版)</t>
   </si>
   <si>
@@ -2431,18 +2444,21 @@
   </si>
   <si>
     <t>伊妍仕(荷兰）/ELLANSE--M</t>
+  </si>
+  <si>
+    <t>塑然雅（法国）/童颜</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
+    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -2484,23 +2500,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2514,11 +2516,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2531,7 +2556,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2539,7 +2564,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2553,6 +2578,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -2568,9 +2594,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2591,11 +2616,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2606,23 +2630,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2649,13 +2665,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2667,7 +2797,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2679,19 +2809,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2703,49 +2821,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2757,73 +2839,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2858,15 +2874,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2891,6 +2898,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2902,15 +2933,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2932,6 +2954,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -2940,166 +2971,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3129,188 +3145,61 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="267968C86FFD4C36ACC19EA1FD1885CA">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3593,15 +3482,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9830,10 +9718,10 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -9972,13 +9860,13 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5535714285714" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10057,10 +9945,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10185,10 +10073,10 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10271,10 +10159,10 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -10301,15 +10189,15 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="3"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="20.1071428571429" customWidth="1"/>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.4" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10329,20 +10217,25 @@
         <v>800</v>
       </c>
     </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>801</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.7767857142857" customWidth="1"/>
-    <col min="2" max="2" width="15.2232142857143" customWidth="1"/>
+    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10545,13 +10438,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5535714285714" customWidth="1"/>
-    <col min="2" max="2" width="34.7767857142857" customWidth="1"/>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10616,48 +10509,34 @@
         <v>781</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>782</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="2">
-        <v>2300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C6" s="2">
-        <v>1000</v>
+        <v>1060</v>
       </c>
       <c r="D6" s="2">
-        <v>1000</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1060</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="8" ht="21" customHeight="1" spans="1:4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10666,10 +10545,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11684,10 +11563,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11714,10 +11593,55 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelCol="3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="30.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2300</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11737,17 +11661,115 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="3" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1450</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="4" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>350</v>
+      </c>
+      <c r="D4" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3750</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1120</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1730</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1730</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11769,100 +11791,30 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>786</v>
+        <v>202</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2">
-        <v>350</v>
-      </c>
-      <c r="D2" s="2">
-        <v>350</v>
+        <v>203</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3750</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1120</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1730</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="7" ht="15.4" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1100</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="8" ht="15.4" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1450</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1450</v>
+        <v>286</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -11871,11 +11823,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11895,65 +11847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="13.1" outlineLevelRow="2" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="15.4" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>791</v>
       </c>
@@ -11967,7 +11861,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" ht="15.4" spans="1:4">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>791</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13044" firstSheet="5" activeTab="14"/>
+    <workbookView windowWidth="27660" windowHeight="13044" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -16,12 +16,11 @@
     <sheet name="胶原蛋白" sheetId="7" r:id="rId7"/>
     <sheet name="PMMA" sheetId="8" r:id="rId8"/>
     <sheet name="PCL" sheetId="9" r:id="rId9"/>
-    <sheet name="肉毒" sheetId="10" r:id="rId10"/>
-    <sheet name="溶脂提升" sheetId="11" r:id="rId11"/>
-    <sheet name="复合酸" sheetId="12" r:id="rId12"/>
-    <sheet name="琼脂糖" sheetId="13" r:id="rId13"/>
-    <sheet name="医用敷贴" sheetId="14" r:id="rId14"/>
-    <sheet name="删除" sheetId="15" r:id="rId15"/>
+    <sheet name="溶脂提升" sheetId="11" r:id="rId10"/>
+    <sheet name="复合酸" sheetId="12" r:id="rId11"/>
+    <sheet name="琼脂糖" sheetId="13" r:id="rId12"/>
+    <sheet name="医用敷贴" sheetId="14" r:id="rId13"/>
+    <sheet name="删除" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="804">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2435,6 +2434,12 @@
   </si>
   <si>
     <t>韩版Babyface皮贴骨</t>
+  </si>
+  <si>
+    <t>大熊溶脂 V-OLET</t>
+  </si>
+  <si>
+    <t>2ml×5支 /盒</t>
   </si>
   <si>
     <t>瑞德喜(德国）/微晶瓷</t>
@@ -9720,148 +9725,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
@@ -9927,10 +9790,18 @@
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3000</v>
+      </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="3"/>
@@ -9944,7 +9815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D8"/>
@@ -10072,7 +9943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
@@ -10158,7 +10029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
@@ -10188,7 +10059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A5"/>
@@ -10204,22 +10075,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13044" firstSheet="5" activeTab="9"/>
+    <workbookView windowWidth="20364" windowHeight="10931" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -10383,10 +10383,10 @@
         <v>33</v>
       </c>
       <c r="C5" s="2">
-        <v>1000</v>
+        <v>1350</v>
       </c>
       <c r="D5" s="2">
-        <v>1000</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
@@ -10397,10 +10397,10 @@
         <v>783</v>
       </c>
       <c r="C6" s="2">
-        <v>1060</v>
+        <v>1400</v>
       </c>
       <c r="D6" s="2">
-        <v>1060</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20364" windowHeight="10931" activeTab="2"/>
+    <workbookView windowWidth="20700" windowHeight="11435" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="805">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2413,6 +2413,9 @@
   </si>
   <si>
     <t>韩版肤丽美</t>
+  </si>
+  <si>
+    <t>台版双美/肤莱美 肤力原</t>
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
@@ -9749,10 +9752,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C2" s="3">
         <v>470</v>
@@ -9763,10 +9766,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C3" s="3">
         <v>180</v>
@@ -9777,10 +9780,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C4" s="3">
         <v>840</v>
@@ -9791,10 +9794,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C5" s="3">
         <v>3000</v>
@@ -10075,22 +10078,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -11511,8 +11514,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11628,6 +11631,20 @@
       </c>
       <c r="D8" s="3">
         <v>1730</v>
+      </c>
+    </row>
+    <row r="9" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
@@ -11720,7 +11737,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -11734,10 +11751,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C3" s="4">
         <v>1750</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21276" windowHeight="11735" firstSheet="3" activeTab="13"/>
+    <workbookView windowWidth="21276" windowHeight="11735" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21276" windowHeight="11735" activeTab="8"/>
+    <workbookView windowWidth="21276" windowHeight="11735" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="814">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2473,6 +2473,15 @@
   </si>
   <si>
     <t>瑞蓝（瑞典）/refyne</t>
+  </si>
+  <si>
+    <t>Mounjaro日替/替西泊肽</t>
+  </si>
+  <si>
+    <t>Tizaro孟替/替西泊肽</t>
+  </si>
+  <si>
+    <t>BCN（西班牙）/ADIPO溶脂</t>
   </si>
 </sst>
 </file>
@@ -9929,7 +9938,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -9983,6 +9992,21 @@
     <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>810</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="813">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -2419,9 +2419,6 @@
   </si>
   <si>
     <t>伊妍仕/少女针(欧版)</t>
-  </si>
-  <si>
-    <t>1ml*1支</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -9779,10 +9776,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -9793,10 +9790,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -9807,10 +9804,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -9821,10 +9818,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -9951,62 +9948,62 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -11599,8 +11596,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -11634,20 +11631,6 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1750</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1750</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22931" windowHeight="11735" firstSheet="1" activeTab="12"/>
+    <workbookView windowWidth="20268" windowHeight="10475" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>BCN（西班牙）/ADIPO溶脂</t>
+  </si>
+  <si>
+    <t>姣兰/Lips 唇部玻尿酸</t>
   </si>
 </sst>
 </file>
@@ -4153,7 +4156,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -4222,6 +4225,11 @@
     <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4514,10 +4522,10 @@
         <v>26</v>
       </c>
       <c r="C5" s="3">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="D5" s="3">
-        <v>1300</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
@@ -4528,10 +4536,10 @@
         <v>28</v>
       </c>
       <c r="C6" s="3">
-        <v>1360</v>
+        <v>1300</v>
       </c>
       <c r="D6" s="3">
-        <v>1360</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20268" windowHeight="10475" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="20190" windowHeight="12405" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="69">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>3ml/支/盒</t>
   </si>
   <si>
     <t>塑然雅/塑颜萃 Sculptra（欧版）</t>
@@ -1286,7 +1289,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -3966,10 +3969,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="21.5583333333333" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3989,10 +3992,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4003,10 +4006,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4017,10 +4020,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4031,10 +4034,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4045,10 +4048,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4067,7 +4070,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4097,7 +4100,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4127,7 +4130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4157,9 +4160,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="20.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4169,67 +4172,67 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4242,10 +4245,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="29.775" customWidth="1"/>
+    <col min="2" max="2" width="15.225" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4451,10 +4454,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="44.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="34.775" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4543,10 +4546,18 @@
       </c>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2050</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2050</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4558,7 +4569,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5576,7 +5587,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5606,10 +5617,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="30.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="30.775" customWidth="1"/>
+    <col min="2" max="2" width="25.775" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5629,10 +5640,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5651,7 +5662,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5673,10 +5684,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3">
         <v>1100</v>
@@ -5687,10 +5698,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2">
         <v>1450</v>
@@ -5701,7 +5712,7 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -5715,10 +5726,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2">
         <v>3750</v>
@@ -5729,10 +5740,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <v>1000</v>
@@ -5743,10 +5754,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C7" s="2">
         <v>1120</v>
@@ -5757,10 +5768,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2">
         <v>1730</v>
@@ -5771,7 +5782,7 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -5793,7 +5804,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5823,7 +5834,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5845,7 +5856,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20190" windowHeight="12405" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="20190" windowHeight="12405" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="70">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>姣兰/Lips 唇部玻尿酸</t>
+  </si>
+  <si>
+    <t>瑞德喜（欧版）/微晶瓷</t>
   </si>
 </sst>
 </file>
@@ -4159,7 +4162,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.1083333333333" customWidth="1"/>
@@ -4233,6 +4236,11 @@
     <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20190" windowHeight="12405" firstSheet="4" activeTab="13"/>
+    <workbookView windowWidth="18900" windowHeight="10295" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -100,6 +100,18 @@
   </si>
   <si>
     <t>姣兰 / Lips 唇部玻尿酸</t>
+  </si>
+  <si>
+    <t>艾莉薇（韩版）/紫色</t>
+  </si>
+  <si>
+    <t>艾莉薇（韩版）/蓝色</t>
+  </si>
+  <si>
+    <t>艾莉薇（韩版）/粉色</t>
+  </si>
+  <si>
+    <t>艾莉薇（韩版）/白色</t>
   </si>
   <si>
     <t>冰月岚 / 面部童颜针</t>
@@ -1292,7 +1304,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -3972,10 +3984,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="21.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3995,10 +4007,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4009,10 +4021,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4023,10 +4035,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4037,10 +4049,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4051,10 +4063,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4073,7 +4085,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4103,7 +4115,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4133,7 +4145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -4163,9 +4175,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4175,72 +4187,72 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4253,10 +4265,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="29.775" customWidth="1"/>
-    <col min="2" max="2" width="15.225" customWidth="1"/>
+    <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4429,28 +4441,60 @@
       </c>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3">
+        <v>260</v>
+      </c>
+      <c r="D13" s="3">
+        <v>260</v>
+      </c>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3">
+        <v>260</v>
+      </c>
+      <c r="D14" s="3">
+        <v>260</v>
+      </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3">
+        <v>260</v>
+      </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3">
+        <v>260</v>
+      </c>
+      <c r="D16" s="3">
+        <v>260</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4462,10 +4506,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="44.5583333333333" customWidth="1"/>
-    <col min="2" max="2" width="34.775" customWidth="1"/>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4485,10 +4529,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
         <v>340</v>
@@ -4499,10 +4543,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3">
         <v>390</v>
@@ -4513,10 +4557,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3">
         <v>390</v>
@@ -4527,10 +4571,10 @@
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3">
         <v>1260</v>
@@ -4541,10 +4585,10 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3">
         <v>1300</v>
@@ -4555,10 +4599,10 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <v>2050</v>
@@ -4577,7 +4621,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5595,7 +5639,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5625,10 +5669,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="30.775" customWidth="1"/>
-    <col min="2" max="2" width="25.775" customWidth="1"/>
+    <col min="1" max="1" width="30.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5648,10 +5692,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5670,7 +5714,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5692,10 +5736,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3">
         <v>1100</v>
@@ -5706,10 +5750,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2">
         <v>1450</v>
@@ -5720,7 +5764,7 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -5734,10 +5778,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2">
         <v>3750</v>
@@ -5748,10 +5792,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3">
         <v>1000</v>
@@ -5762,10 +5806,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>1120</v>
@@ -5776,10 +5820,10 @@
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2">
         <v>1730</v>
@@ -5790,7 +5834,7 @@
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -5812,7 +5856,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5842,7 +5886,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5864,7 +5908,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4448,10 +4448,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="D13" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
@@ -4462,10 +4462,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="D14" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
@@ -4476,10 +4476,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="D15" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
@@ -4490,10 +4490,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="D16" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="10295" activeTab="1"/>
+    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="5" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -234,19 +234,22 @@
     <t>塑然雅（法国）/童颜</t>
   </si>
   <si>
-    <t>瑞蓝（瑞典）/2号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典）/3号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典）/4号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典）/5号</t>
+    <t>瑞蓝（欧版）/基础水光</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/2号</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/4号</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/3号</t>
   </si>
   <si>
     <t>瑞蓝（瑞典）/refyne</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/5号</t>
   </si>
   <si>
     <t>Mounjaro日替/替西泊肽</t>
@@ -4174,7 +4177,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -4253,6 +4256,11 @@
     <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="5" activeTab="13"/>
+    <workbookView windowWidth="18900" windowHeight="10295" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -66,7 +66,7 @@
     <t>乔雅登（韩版）/8号 质颜</t>
   </si>
   <si>
-    <t>瑞蓝（瑞典本土版）/2号</t>
+    <t>瑞蓝（欧版）/2号</t>
   </si>
   <si>
     <t>1ml/支/盒</t>
@@ -75,25 +75,25 @@
     <t>¥580</t>
   </si>
   <si>
-    <t>瑞蓝（瑞典本土版）/3号</t>
+    <t>瑞蓝（欧版）/3号</t>
   </si>
   <si>
     <t>¥620</t>
   </si>
   <si>
-    <t>瑞蓝（瑞典本土版）/4号</t>
+    <t>瑞蓝（欧版）/4号</t>
   </si>
   <si>
     <t>¥640</t>
   </si>
   <si>
-    <t>瑞蓝（瑞典本土版）/5号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典本土版）/6号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典本土版）/refyne</t>
+    <t>瑞蓝（欧版）/5号</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/6号</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/refyne</t>
   </si>
   <si>
     <t>姣兰 / 经典玻尿酸</t>
@@ -232,24 +232,6 @@
   </si>
   <si>
     <t>塑然雅（法国）/童颜</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/基础水光</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/2号</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/4号</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/3号</t>
-  </si>
-  <si>
-    <t>瑞蓝（瑞典）/refyne</t>
-  </si>
-  <si>
-    <t>瑞蓝（欧版）/5号</t>
   </si>
   <si>
     <t>Mounjaro日替/替西泊肽</t>
@@ -4177,7 +4159,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -4231,36 +4213,6 @@
     <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="10295" activeTab="1"/>
+    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="65">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -148,18 +148,6 @@
   </si>
   <si>
     <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
-  </si>
-  <si>
-    <t>弗缦 Pro/0.5版</t>
-  </si>
-  <si>
-    <t>0.5ml/支</t>
-  </si>
-  <si>
-    <t>弗缦 Pro/1.0版</t>
-  </si>
-  <si>
-    <t>1ml/支</t>
   </si>
   <si>
     <t>韩版肤丽美</t>
@@ -3992,10 +3980,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4006,10 +3994,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4020,10 +4008,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4034,10 +4022,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4048,10 +4036,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4172,47 +4160,47 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5673,8 +5661,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5699,41 +5687,41 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="D2" s="3">
-        <v>1100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C3" s="2">
-        <v>1450</v>
+        <v>3750</v>
       </c>
       <c r="D3" s="2">
-        <v>1450</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" s="3">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="D4" s="3">
-        <v>350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
@@ -5741,68 +5729,40 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1120</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="2">
-        <v>3750</v>
-      </c>
-      <c r="D5" s="2">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1000</v>
+      <c r="C6" s="2">
+        <v>1730</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1730</v>
       </c>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2">
-        <v>1120</v>
+        <v>1500</v>
       </c>
       <c r="D7" s="2">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1730</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="9" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1500</v>
-      </c>
-      <c r="D9" s="2">
         <v>1500</v>
       </c>
     </row>
@@ -5868,7 +5828,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>BCN（西班牙）/ADIPO溶脂</t>
-  </si>
-  <si>
-    <t>姣兰/Lips 唇部玻尿酸</t>
   </si>
   <si>
     <t>瑞德喜（欧版）/微晶瓷</t>
@@ -4147,7 +4144,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -4196,11 +4193,6 @@
     <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="4" activeTab="13"/>
+    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>乔雅登（韩版）/6号 朔颜</t>
+  </si>
+  <si>
+    <t>乔雅登（韩版）/7号 缇颜</t>
   </si>
   <si>
     <t>乔雅登（韩版）/8号 质颜</t>
@@ -3977,10 +3980,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3991,10 +3994,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4005,10 +4008,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4019,10 +4022,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4033,10 +4036,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4157,42 +4160,42 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4207,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
@@ -4262,66 +4265,66 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
+        <v>1650</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="5" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6">
         <v>1350</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D5" s="6">
         <v>1350</v>
       </c>
     </row>
-    <row r="5" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="6" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:4">
@@ -4329,27 +4332,27 @@
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>14</v>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:4">
@@ -4357,49 +4360,49 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
         <v>250</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="12" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3">
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3">
         <v>260</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
         <v>260</v>
       </c>
     </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3">
-        <v>160</v>
-      </c>
-      <c r="D13" s="3">
-        <v>160</v>
-      </c>
-    </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3">
         <v>160</v>
@@ -4409,11 +4412,11 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3">
         <v>160</v>
@@ -4423,16 +4426,30 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3">
         <v>160</v>
       </c>
       <c r="D16" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3">
+        <v>160</v>
+      </c>
+      <c r="D17" s="3">
         <v>160</v>
       </c>
     </row>
@@ -4469,10 +4486,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3">
         <v>340</v>
@@ -4483,10 +4500,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3">
         <v>390</v>
@@ -4497,10 +4514,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C4" s="3">
         <v>390</v>
@@ -4511,10 +4528,10 @@
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>1260</v>
@@ -4525,10 +4542,10 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3">
         <v>1300</v>
@@ -4539,10 +4556,10 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
         <v>2050</v>
@@ -5632,10 +5649,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5676,10 +5693,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>350</v>
@@ -5690,10 +5707,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2">
         <v>3750</v>
@@ -5704,10 +5721,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5718,10 +5735,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5732,10 +5749,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5746,10 +5763,10 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
         <v>1500</v>
@@ -5820,7 +5837,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="10295" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="67">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -117,6 +117,9 @@
     <t>艾莉薇（韩版）/白色</t>
   </si>
   <si>
+    <t>奥地利公主VOLUME</t>
+  </si>
+  <si>
     <t>冰月岚 / 面部童颜针</t>
   </si>
   <si>
@@ -180,7 +183,10 @@
     <t>台版双美/肤莱美 肤力原</t>
   </si>
   <si>
-    <t>伊妍仕/少女针(欧版)</t>
+    <t>伊妍仕(欧版）/ELLANSE--M</t>
+  </si>
+  <si>
+    <t>伊妍仕(欧版）/ELLANSE--S</t>
   </si>
   <si>
     <t>韩版 Babyface 绿溶脂（面部）</t>
@@ -3980,10 +3986,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3994,10 +4000,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4008,10 +4014,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4022,10 +4028,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4036,10 +4042,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4160,42 +4166,42 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4207,7 +4213,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
@@ -4451,6 +4457,20 @@
       </c>
       <c r="D17" s="3">
         <v>160</v>
+      </c>
+    </row>
+    <row r="18" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3">
+        <v>600</v>
+      </c>
+      <c r="D18" s="3">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -4486,10 +4506,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
         <v>340</v>
@@ -4500,10 +4520,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3">
         <v>390</v>
@@ -4514,10 +4534,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="3">
         <v>390</v>
@@ -4528,10 +4548,10 @@
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3">
         <v>1260</v>
@@ -4542,10 +4562,10 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
         <v>1300</v>
@@ -4556,10 +4576,10 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <v>2050</v>
@@ -5649,10 +5669,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5693,7 +5713,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5707,10 +5727,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2">
         <v>3750</v>
@@ -5721,10 +5741,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5735,10 +5755,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5749,10 +5769,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5763,7 +5783,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5814,8 +5834,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -5837,7 +5857,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5847,6 +5867,20 @@
       </c>
       <c r="D2" s="4">
         <v>3350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3200</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3200</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="1"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
     <t>3ml/支/盒</t>
   </si>
   <si>
-    <t>塑然雅/塑颜萃 Sculptra（欧版）</t>
+    <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
   </si>
   <si>
     <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
@@ -5648,7 +5648,7 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="30.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
   </cols>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="5"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>（含麻）1.5ml/支/盒</t>
-  </si>
-  <si>
-    <t>3ml/支/盒</t>
   </si>
   <si>
     <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
@@ -3986,10 +3983,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4000,10 +3997,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4014,10 +4011,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4028,10 +4025,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4042,10 +4039,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4166,42 +4163,42 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4482,8 +4479,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
@@ -4572,20 +4569,6 @@
       </c>
       <c r="D6" s="3">
         <v>1300</v>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2050</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2050</v>
       </c>
     </row>
   </sheetData>
@@ -5669,10 +5652,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5713,7 +5696,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5727,10 +5710,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C3" s="2">
         <v>3750</v>
@@ -5741,10 +5724,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5755,10 +5738,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5769,10 +5752,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5783,7 +5766,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5857,7 +5840,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5871,7 +5854,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4282,10 +4282,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="6">
-        <v>1350</v>
+        <v>1540</v>
       </c>
       <c r="D5" s="6">
-        <v>1350</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="2"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -153,6 +153,12 @@
     <t>2 瓶 / 盒 × 367.5mg / 瓶</t>
   </si>
   <si>
+    <t>爱塑美/臻爱塑菲（韩版）/童颜</t>
+  </si>
+  <si>
+    <t>200mg/瓶/盒</t>
+  </si>
+  <si>
     <t>韩版肤丽美</t>
   </si>
   <si>
@@ -219,12 +225,6 @@
     <t>瑞德喜(德国）/微晶瓷</t>
   </si>
   <si>
-    <t>伊妍仕(荷兰）/ELLANSE--S</t>
-  </si>
-  <si>
-    <t>伊妍仕(荷兰）/ELLANSE--M</t>
-  </si>
-  <si>
     <t>塑然雅（法国）/童颜</t>
   </si>
   <si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>瑞德喜（欧版）/微晶瓷</t>
+  </si>
+  <si>
+    <t>爱塑美（韩版）/童颜</t>
   </si>
 </sst>
 </file>
@@ -3983,10 +3986,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3997,10 +4000,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4011,10 +4014,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4025,10 +4028,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4039,10 +4042,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4150,8 +4153,8 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
@@ -4163,42 +4166,37 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5628,8 +5626,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="25.7777777777778" customWidth="1"/>
@@ -5662,6 +5660,20 @@
       </c>
       <c r="D2" s="3">
         <v>2300</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1860</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1860</v>
       </c>
     </row>
   </sheetData>
@@ -5696,7 +5708,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5710,10 +5722,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2">
         <v>3750</v>
@@ -5724,10 +5736,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5738,10 +5750,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5752,10 +5764,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5766,7 +5778,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5840,7 +5852,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5854,7 +5866,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="61">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -120,21 +120,6 @@
     <t>奥地利公主VOLUME</t>
   </si>
   <si>
-    <t>冰月岚 / 面部童颜针</t>
-  </si>
-  <si>
-    <t>350mg+10ml / 盒（粉末 + 液体双剂）</t>
-  </si>
-  <si>
-    <t>冰月岚 / 黑金少女针</t>
-  </si>
-  <si>
-    <t>1ml / 支 / 盒</t>
-  </si>
-  <si>
-    <t>冰月岚 / 粉金少女针</t>
-  </si>
-  <si>
     <t>芮得怡（瑞德喜）/面部填充剂（欧版浅蓝）</t>
   </si>
   <si>
@@ -222,16 +207,13 @@
     <t>5ml*10瓶/盒</t>
   </si>
   <si>
-    <t>瑞德喜(德国）/微晶瓷</t>
-  </si>
-  <si>
     <t>塑然雅（法国）/童颜</t>
   </si>
   <si>
-    <t>Mounjaro日替/替西泊肽</t>
-  </si>
-  <si>
-    <t>Tizaro孟替/替西泊肽</t>
+    <t>日替Mounjaro/替西泊肽</t>
+  </si>
+  <si>
+    <t>孟替Tizaro/替西泊肽</t>
   </si>
   <si>
     <t>BCN（西班牙）/ADIPO溶脂</t>
@@ -3986,10 +3968,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -4000,10 +3982,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4014,10 +3996,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4028,10 +4010,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4042,10 +4024,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4153,8 +4135,8 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
@@ -4166,37 +4148,32 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4477,8 +4454,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
@@ -4507,10 +4484,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>340</v>
+        <v>1260</v>
       </c>
       <c r="D2" s="3">
-        <v>340</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
@@ -4521,51 +4498,9 @@
         <v>29</v>
       </c>
       <c r="C3" s="3">
-        <v>390</v>
+        <v>1300</v>
       </c>
       <c r="D3" s="3">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="3">
-        <v>390</v>
-      </c>
-      <c r="D4" s="3">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1260</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1300</v>
-      </c>
-      <c r="D6" s="3">
         <v>1300</v>
       </c>
     </row>
@@ -5650,10 +5585,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5664,10 +5599,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -5708,7 +5643,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5722,10 +5657,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2">
         <v>3750</v>
@@ -5736,10 +5671,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5750,10 +5685,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5764,10 +5699,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5778,7 +5713,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5852,7 +5787,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5866,7 +5801,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -5663,10 +5663,10 @@
         <v>36</v>
       </c>
       <c r="C3" s="2">
-        <v>3750</v>
+        <v>3030</v>
       </c>
       <c r="D3" s="2">
-        <v>3750</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>（含麻）1.5ml/支/盒</t>
+  </si>
+  <si>
+    <t>芮得怡（瑞德喜）/面部填充剂（韩版浅蓝）</t>
   </si>
   <si>
     <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
@@ -3968,10 +3971,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3982,10 +3985,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -3996,10 +3999,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4010,10 +4013,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4024,10 +4027,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4148,32 +4151,32 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4454,8 +4457,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="34.7777777777778" customWidth="1"/>
@@ -4484,10 +4487,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="D2" s="3">
-        <v>1260</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
@@ -4498,10 +4501,24 @@
         <v>29</v>
       </c>
       <c r="C3" s="3">
-        <v>1300</v>
+        <v>1390</v>
       </c>
       <c r="D3" s="3">
-        <v>1300</v>
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1340</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1340</v>
       </c>
     </row>
   </sheetData>
@@ -5585,10 +5602,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5599,10 +5616,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -5643,7 +5660,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5657,10 +5674,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2">
         <v>3030</v>
@@ -5671,10 +5688,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5685,10 +5702,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5699,10 +5716,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5713,7 +5730,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5787,7 +5804,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5801,7 +5818,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="2"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="63">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>芮得怡（瑞德喜）/面部填充剂（韩版浅蓝）</t>
+  </si>
+  <si>
+    <t>乔雅登SKINVIVE长效水光</t>
   </si>
   <si>
     <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>
@@ -3971,10 +3974,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3985,10 +3988,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -3999,10 +4002,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4013,10 +4016,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4027,10 +4030,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4151,32 +4154,32 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4538,16 +4541,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>870</v>
+      </c>
+      <c r="D2" s="3">
+        <v>870</v>
+      </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2"/>
@@ -5602,10 +5621,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5616,10 +5635,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -5660,7 +5679,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5674,10 +5693,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2">
         <v>3030</v>
@@ -5688,10 +5707,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5702,10 +5721,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5716,10 +5735,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5730,16 +5749,16 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>1500</v>
+        <v>1590</v>
       </c>
       <c r="D7" s="2">
-        <v>1500</v>
+        <v>1590</v>
       </c>
     </row>
   </sheetData>
@@ -5804,7 +5823,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5818,7 +5837,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -135,7 +135,7 @@
     <t>芮得怡（瑞德喜）/面部填充剂（韩版浅蓝）</t>
   </si>
   <si>
-    <t>乔雅登SKINVIVE长效水光</t>
+    <t>乔雅登SKINVIVE长效水光韩版</t>
   </si>
   <si>
     <t>塑然雅/塑颜萃塑妍萃 Sculptra（欧版）</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="3"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>5ml*10瓶/盒</t>
   </si>
   <si>
-    <t>塑然雅（法国）/童颜</t>
-  </si>
-  <si>
     <t>日替Mounjaro/替西泊肽</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>爱塑美（韩版）/童颜</t>
+  </si>
+  <si>
+    <t>塑然雅（欧版）/童颜</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="64">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>瑞蓝（欧版）/refyne</t>
+  </si>
+  <si>
+    <t>瑞蓝（欧版）/Kysse唇部</t>
   </si>
   <si>
     <t>姣兰 / 经典玻尿酸</t>
@@ -3974,10 +3977,10 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2">
         <v>470</v>
@@ -3988,10 +3991,10 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2">
         <v>180</v>
@@ -4002,10 +4005,10 @@
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2">
         <v>840</v>
@@ -4016,10 +4019,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2">
         <v>3000</v>
@@ -4030,10 +4033,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2">
         <v>380</v>
@@ -4154,32 +4157,32 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4191,7 +4194,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.7777777777778" customWidth="1"/>
@@ -4360,43 +4363,43 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
         <v>250</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="13" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3">
-        <v>260</v>
-      </c>
-      <c r="D13" s="3">
-        <v>260</v>
-      </c>
-    </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="D14" s="3">
-        <v>160</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -4410,7 +4413,7 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -4424,7 +4427,7 @@
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -4445,9 +4448,23 @@
         <v>10</v>
       </c>
       <c r="C18" s="3">
+        <v>160</v>
+      </c>
+      <c r="D18" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
         <v>600</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D19" s="3">
         <v>600</v>
       </c>
     </row>
@@ -4484,10 +4501,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
         <v>1360</v>
@@ -4498,10 +4515,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3">
         <v>1390</v>
@@ -4512,10 +4529,10 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3">
         <v>1340</v>
@@ -4556,7 +4573,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5621,10 +5638,10 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3">
         <v>2300</v>
@@ -5635,10 +5652,10 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3">
         <v>1860</v>
@@ -5679,7 +5696,7 @@
     </row>
     <row r="2" ht="22.05" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -5693,24 +5710,24 @@
     </row>
     <row r="3" ht="22.05" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2">
-        <v>3030</v>
+        <v>3430</v>
       </c>
       <c r="D3" s="2">
-        <v>3030</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3">
         <v>1000</v>
@@ -5721,10 +5738,10 @@
     </row>
     <row r="5" ht="22.05" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C5" s="2">
         <v>1120</v>
@@ -5735,10 +5752,10 @@
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>1730</v>
@@ -5749,7 +5766,7 @@
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -5823,7 +5840,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -5837,7 +5854,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="1"/>
+    <workbookView windowWidth="19115" windowHeight="10860" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>5ml*10瓶/盒</t>
+  </si>
+  <si>
+    <t>澳蕾诺消消/黄盒</t>
+  </si>
+  <si>
+    <t>5ml / 盒</t>
+  </si>
+  <si>
+    <t>澳蕾诺赫本/绿盒</t>
   </si>
   <si>
     <t>日替Mounjaro/替西泊肽</t>
@@ -3953,8 +3962,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
@@ -4043,6 +4052,34 @@
       </c>
       <c r="D6" s="2">
         <v>380</v>
+      </c>
+    </row>
+    <row r="7" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2">
+        <v>290</v>
+      </c>
+      <c r="D7" s="2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2">
+        <v>255</v>
+      </c>
+      <c r="D8" s="2">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -4157,32 +4194,32 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" activeTab="9"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
   <si>
     <t>品牌/型号</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>塑然雅（欧版）/童颜</t>
+  </si>
+  <si>
+    <t>澳蕾诺/消消瓶</t>
   </si>
 </sst>
 </file>
@@ -4181,8 +4184,8 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
   </cols>
@@ -4220,6 +4223,11 @@
     <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="13"/>
+    <workbookView windowWidth="19115" windowHeight="10860" firstSheet="4" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="全部" sheetId="1" r:id="rId1"/>
@@ -4079,10 +4079,10 @@
         <v>59</v>
       </c>
       <c r="C8" s="2">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="D8" s="2">
-        <v>255</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
